--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45856</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45936</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46043</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45111</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44607</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46225</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>45609</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>45348</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>46055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45302</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>44607</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45510</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>44970</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>45268</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>44963</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46280</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>44992</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44512</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>45930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>46198</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>45788</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>45376</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>45747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>44602</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45604</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>46176</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>46055</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>45792</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>46133</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>44536</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45777</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>45783</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>44974</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>46107</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45898</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>45629</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44747</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>44607</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>46092</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>44469</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>44979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>45580</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>45539</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45331</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45446</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45373</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44943</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>45538</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>45947</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45302</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>46174</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>46048</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>46049</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>46196</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>44991</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>45758</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>45982</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>45358</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>46230</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45790</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>45679</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>45603</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>43983</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>45013</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>44647</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>45393</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>45790</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>44613</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>44711</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44467</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44579</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>45477</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>44750</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>45177</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45436</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>45295</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>44840</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45272</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45205</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>45730</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>45338</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>45720</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45205</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45764</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45926</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45184</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44557</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>46162</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>46162</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>46013</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>44963</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>46035</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>46048</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>46055</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45751</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>44992</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>46059</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44879</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>46106</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45343</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44893</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>46203</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>45558</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>46252</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>45600</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>46212</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>46211</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45617</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>45201</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44540</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>46279</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>45740</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>45587</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45841</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45842</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>45616</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45846</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>44955</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>44711</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44628</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>45712</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>45712</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45846</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44496</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>44575</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>44487</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>44749</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44749</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>44662</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>44792</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>44487</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44487</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44749</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44881</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>44665</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>44792</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>44538</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>44487</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>44487</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44852</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44498</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44881</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44673</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>44754</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44855</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44476</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>44511</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>44466</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44840</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>44537</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44476</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>44575</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44659</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>44659</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>44711</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>44578</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>44474</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44579</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>44557</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>44616</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>44464</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>44575</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44575</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>44819</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>44819</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>44846</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44523</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>44605</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44711</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>44841</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>44467</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44792</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44830</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>44787</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44825</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>44614</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>44585</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>44711</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>44488</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>44464</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>44498</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>44532</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>44593</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>44729</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>44805</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>44811</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>44853</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>45272</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>44711</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45617</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>45469</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45114</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45764</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45012</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45747</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45404</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45697</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45169</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45048</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45605</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45152</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45111</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>44589</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>44628</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>45145</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>45307</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>45726</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>44998</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45012</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45621</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45621</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45295</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45435</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45092</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>45392</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45645</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45456</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>44938</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>45405</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45405</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>45621</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>44943</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44943</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45757</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45253</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45184</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45116</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45545</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>44949</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44904</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44904</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44897</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44904</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44482</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>44662</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>44861</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44861</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>45406</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>45539</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45373</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45183</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44592</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45547</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44571</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45455</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>45461</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>44622</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>45182</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>44893</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45037</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45600</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>45600</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45701</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45726</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>45215</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45468</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45371</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45682</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44977</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45617</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>44585</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45152</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>45351</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44846</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>44904</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45502</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45189</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45358</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>44882</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>45294</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>44507</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>45079</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>45035</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>44626</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45246</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>45058</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44950</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>45240</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>45119</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45566</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>45566</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>44837</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>45210</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>45502</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44614</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26941,7 +26941,7 @@
         <v>45021</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>44963</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>44935</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44867</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27233,7 +27233,7 @@
         <v>45180</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>44904</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>44575</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>45834</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45558</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>46002</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>45260</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>45008</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45105</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>45887</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>45758</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>45474</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>45124</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>45759</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>45051</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>45887</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45730</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44487</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45841</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>45846</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>45316</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>44631</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>45892</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>45892</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>45892</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>45552</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>45895</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>44483</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45169</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45887</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>45898</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>45679</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>45947</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>45902</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>45764</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>45905</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>44923</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>45908</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>45908</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45908</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30168,7 +30168,7 @@
         <v>45908</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30241,7 +30241,7 @@
         <v>45764</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>45300</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>45734</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>45693</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>45681</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>44659</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>45902</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>45455</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>44889</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>45917</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>45875</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>44853</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45401</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>44988</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45925</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45471</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>45198</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45775</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>45364</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45188</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>45356</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>45181</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>44882</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>44965</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>45749</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>44648</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>45934</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>45194</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45763</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>44943</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>44943</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45587</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45945</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45642</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>45946</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32811,7 +32811,7 @@
         <v>45734</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32884,7 +32884,7 @@
         <v>45946</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>45043</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
         <v>45392</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>45271</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33176,7 +33176,7 @@
         <v>45215</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33249,7 +33249,7 @@
         <v>44803</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>45958</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>45958</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>45958</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>45673</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>44957</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33687,7 +33687,7 @@
         <v>45460</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>45030</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>44977</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>45965</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45034</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>45966</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>45966</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45966</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>45966</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44468</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34417,7 +34417,7 @@
         <v>45966</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>45349</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>45182</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>45968</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>45763</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>45646</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>45974</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34933,7 +34933,7 @@
         <v>45169</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35006,7 +35006,7 @@
         <v>45169</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>45974</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>44704</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>45401</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>45974</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>45974</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>45974</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         <v>45414</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45975</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45974</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45974</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45974</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>45979</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45978</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>45758</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>45470</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36219,7 +36219,7 @@
         <v>45198</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>45198</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>44886</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36438,7 +36438,7 @@
         <v>44658</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45303</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>45580</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>44550</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>45455</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>45130</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>45477</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45547</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37037,7 +37037,7 @@
         <v>45112</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
         <v>45112</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>45174</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45557</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45988</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>44614</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45462</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>44861</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45324</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>45270</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>46162</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45179</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>46162</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38001,7 +38001,7 @@
         <v>44507</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>46162</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>46162</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45618</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>46162</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>45275</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>46162</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>45995</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>46167</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44936</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45538</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>46167</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>46000</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45302</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>45300</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45412</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>46168</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>46009</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>45182</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>46168</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>45267</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>46008</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>45149</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>44943</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45615</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>45615</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>45523</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>46013</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>45958</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>46013</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>46010</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>46009</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>46013</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>46009</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>46009</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>46013</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>46013</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>46009</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>46013</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>46168</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>45281</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>44944</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>44614</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>44729</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>46170</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>44648</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45177</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>44938</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>46026</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>46026</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>45588</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>46029</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>46170</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>44655</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>46031</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>46030</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>46031</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>46170</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>46170</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>46035</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>46174</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42544,7 +42544,7 @@
         <v>44628</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>44839</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>46035</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42768,7 +42768,7 @@
         <v>45092</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42841,7 +42841,7 @@
         <v>44893</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42914,7 +42914,7 @@
         <v>46174</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>46041</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45363</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>46174</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>46038</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43294,7 +43294,7 @@
         <v>46041</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>45314</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>46043</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>46043</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43586,7 +43586,7 @@
         <v>46059</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>46041</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
         <v>44484</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>46044</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43878,7 +43878,7 @@
         <v>45764</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45226</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>44589</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>44578</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>46048</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44243,7 +44243,7 @@
         <v>44735</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>45587</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>44804</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>46048</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>46049</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>46048</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>46049</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44754,7 +44754,7 @@
         <v>46048</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45043</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
         <v>46048</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44973,7 +44973,7 @@
         <v>46048</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45046,7 +45046,7 @@
         <v>46048</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45124,7 +45124,7 @@
         <v>45929</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45197,7 +45197,7 @@
         <v>45113</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>46050</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45343,7 +45343,7 @@
         <v>46055</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>46055</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>46055</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>46055</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>45701</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45708,7 +45708,7 @@
         <v>46059</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>46059</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         <v>45644</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45927,7 +45927,7 @@
         <v>46059</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46000,7 +46000,7 @@
         <v>46059</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
         <v>46059</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46146,7 +46146,7 @@
         <v>46059</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46219,7 +46219,7 @@
         <v>46059</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46292,7 +46292,7 @@
         <v>46059</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46365,7 +46365,7 @@
         <v>44608</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>46062</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>46062</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>46062</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46657,7 +46657,7 @@
         <v>46063</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>46045</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46803,7 +46803,7 @@
         <v>44734</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>44734</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>46069</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>46069</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47105,7 +47105,7 @@
         <v>44904</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>46069</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>46182</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47324,7 +47324,7 @@
         <v>46070</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47397,7 +47397,7 @@
         <v>45197</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47470,7 +47470,7 @@
         <v>45321</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47543,7 +47543,7 @@
         <v>45043</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47616,7 +47616,7 @@
         <v>46070</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47689,7 +47689,7 @@
         <v>46070</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47762,7 +47762,7 @@
         <v>46073</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47835,7 +47835,7 @@
         <v>45545</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>46079</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47986,7 +47986,7 @@
         <v>44711</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48059,7 +48059,7 @@
         <v>45477</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45477</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>46184</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48283,7 +48283,7 @@
         <v>45299</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         <v>44998</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45175</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48502,7 +48502,7 @@
         <v>46189</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>45118</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48648,7 +48648,7 @@
         <v>46087</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>44591</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45708</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48867,7 +48867,7 @@
         <v>45211</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45112</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49013,7 +49013,7 @@
         <v>46188</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49086,7 +49086,7 @@
         <v>45375</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>46090</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45541</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>46091</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>44853</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>45492</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45562</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45477</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49670,7 +49670,7 @@
         <v>45477</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>45359</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49816,7 +49816,7 @@
         <v>46197</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45243</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>45184</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>46101</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>44950</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50186,7 +50186,7 @@
         <v>44950</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50259,7 +50259,7 @@
         <v>46198</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         <v>44930</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50405,7 +50405,7 @@
         <v>45531</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50478,7 +50478,7 @@
         <v>45757</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45462</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50624,7 +50624,7 @@
         <v>45201</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50697,7 +50697,7 @@
         <v>46244</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50770,7 +50770,7 @@
         <v>45201</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>46244</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50916,7 +50916,7 @@
         <v>46244</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>46201</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51062,7 +51062,7 @@
         <v>44719</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45335</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51213,7 +51213,7 @@
         <v>46119</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>46119</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51359,7 +51359,7 @@
         <v>46120</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51432,7 +51432,7 @@
         <v>46120</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>46120</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51578,7 +51578,7 @@
         <v>45092</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51651,7 +51651,7 @@
         <v>46201</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>46201</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>46119</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51870,7 +51870,7 @@
         <v>45099</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51943,7 +51943,7 @@
         <v>44943</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>45201</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>44985</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52167,7 +52167,7 @@
         <v>45245</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52240,7 +52240,7 @@
         <v>46244</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52313,7 +52313,7 @@
         <v>45107</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52386,7 +52386,7 @@
         <v>45314</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>45295</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>46203</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>46203</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52683,7 +52683,7 @@
         <v>45534</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52756,7 +52756,7 @@
         <v>45617</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52829,7 +52829,7 @@
         <v>44564</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52902,7 +52902,7 @@
         <v>45377</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52975,7 +52975,7 @@
         <v>45219</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>46246</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53121,7 +53121,7 @@
         <v>45363</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>45240</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53267,7 +53267,7 @@
         <v>44966</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53345,7 +53345,7 @@
         <v>45194</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53418,7 +53418,7 @@
         <v>45194</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53491,7 +53491,7 @@
         <v>45112</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53564,7 +53564,7 @@
         <v>45107</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53637,7 +53637,7 @@
         <v>45015</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>44904</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53783,7 +53783,7 @@
         <v>45049</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53856,7 +53856,7 @@
         <v>45810</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53929,7 +53929,7 @@
         <v>45338</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54007,7 +54007,7 @@
         <v>46246</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54080,7 +54080,7 @@
         <v>44894</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54153,7 +54153,7 @@
         <v>46247</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>44893</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>46246</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54377,7 +54377,7 @@
         <v>44605</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>46248</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54523,7 +54523,7 @@
         <v>45197</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54601,7 +54601,7 @@
         <v>45406</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54674,7 +54674,7 @@
         <v>44985</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>46206</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54825,7 +54825,7 @@
         <v>45051</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54898,7 +54898,7 @@
         <v>44484</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54971,7 +54971,7 @@
         <v>46206</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>45706</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55127,7 +55127,7 @@
         <v>45671</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55200,7 +55200,7 @@
         <v>45705</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>45740</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55346,7 +55346,7 @@
         <v>45693</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55419,7 +55419,7 @@
         <v>45009</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>46206</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
         <v>45127</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>44677</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55716,7 +55716,7 @@
         <v>45756</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55789,7 +55789,7 @@
         <v>46252</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55862,7 +55862,7 @@
         <v>45324</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55940,7 +55940,7 @@
         <v>45324</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56018,7 +56018,7 @@
         <v>45671</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56091,7 +56091,7 @@
         <v>45414</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>45761</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56237,7 +56237,7 @@
         <v>44741</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56310,7 +56310,7 @@
         <v>45223</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56383,7 +56383,7 @@
         <v>46211</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>46211</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56529,7 +56529,7 @@
         <v>45541</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>46212</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56680,7 +56680,7 @@
         <v>46211</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>46211</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56826,7 +56826,7 @@
         <v>46211</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56899,7 +56899,7 @@
         <v>46255</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56972,7 +56972,7 @@
         <v>45435</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57050,7 +57050,7 @@
         <v>46211</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57128,7 +57128,7 @@
         <v>46212</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57206,7 +57206,7 @@
         <v>46211</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>46211</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57352,7 +57352,7 @@
         <v>46211</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>46211</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57498,7 +57498,7 @@
         <v>44967</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>46212</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>44734</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57722,7 +57722,7 @@
         <v>46211</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>45747</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>45946</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57946,7 +57946,7 @@
         <v>45533</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>45706</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58097,7 +58097,7 @@
         <v>45635</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58170,7 +58170,7 @@
         <v>45541</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58243,7 +58243,7 @@
         <v>45201</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58316,7 +58316,7 @@
         <v>45341</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>44950</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45099</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58535,7 +58535,7 @@
         <v>45681</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58608,7 +58608,7 @@
         <v>45715</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58681,7 +58681,7 @@
         <v>44627</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         <v>45056</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58827,7 +58827,7 @@
         <v>46219</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58900,7 +58900,7 @@
         <v>45842</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58973,7 +58973,7 @@
         <v>45355</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59046,7 +59046,7 @@
         <v>44966</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59124,7 +59124,7 @@
         <v>46220</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>44588</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>44488</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>46262</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59416,7 +59416,7 @@
         <v>45197</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59489,7 +59489,7 @@
         <v>45547</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>46219</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59640,7 +59640,7 @@
         <v>45569</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59713,7 +59713,7 @@
         <v>44897</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59791,7 +59791,7 @@
         <v>45764</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59864,7 +59864,7 @@
         <v>46265</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>45198</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60010,7 +60010,7 @@
         <v>45056</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60083,7 +60083,7 @@
         <v>46267</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60156,7 +60156,7 @@
         <v>45406</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60229,7 +60229,7 @@
         <v>45406</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60302,7 +60302,7 @@
         <v>45440</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60375,7 +60375,7 @@
         <v>45216</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60448,7 +60448,7 @@
         <v>46268</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60521,7 +60521,7 @@
         <v>46230</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60599,7 +60599,7 @@
         <v>46230</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60677,7 +60677,7 @@
         <v>46272</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60750,7 +60750,7 @@
         <v>45667</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60823,7 +60823,7 @@
         <v>46273</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60896,7 +60896,7 @@
         <v>46270</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60969,7 +60969,7 @@
         <v>46272</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61042,7 +61042,7 @@
         <v>46272</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61115,7 +61115,7 @@
         <v>45519</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61188,7 +61188,7 @@
         <v>46272</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61261,7 +61261,7 @@
         <v>46272</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61334,7 +61334,7 @@
         <v>46248</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61407,7 +61407,7 @@
         <v>46274</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61480,7 +61480,7 @@
         <v>46233</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61558,7 +61558,7 @@
         <v>46279</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61636,7 +61636,7 @@
         <v>46234</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61709,7 +61709,7 @@
         <v>45586</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>46279</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61860,7 +61860,7 @@
         <v>46279</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61938,7 +61938,7 @@
         <v>46234</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62011,7 +62011,7 @@
         <v>46234</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62084,7 +62084,7 @@
         <v>46234</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62157,7 +62157,7 @@
         <v>46279</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62235,7 +62235,7 @@
         <v>46233</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62313,7 +62313,7 @@
         <v>46276</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62386,7 +62386,7 @@
         <v>46276</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62459,7 +62459,7 @@
         <v>46238</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62532,7 +62532,7 @@
         <v>45541</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45551</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62678,7 +62678,7 @@
         <v>45350</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62751,7 +62751,7 @@
         <v>45646</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62824,7 +62824,7 @@
         <v>45793</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62897,7 +62897,7 @@
         <v>46282</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62970,7 +62970,7 @@
         <v>45570</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63043,7 +63043,7 @@
         <v>46239</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63116,7 +63116,7 @@
         <v>45727</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63189,7 +63189,7 @@
         <v>46267</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63262,7 +63262,7 @@
         <v>45740</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63335,7 +63335,7 @@
         <v>45735</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63408,7 +63408,7 @@
         <v>45734</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63481,7 +63481,7 @@
         <v>46239</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>46281</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63627,7 +63627,7 @@
         <v>46279</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63705,7 +63705,7 @@
         <v>44992</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45805</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63851,7 +63851,7 @@
         <v>45806</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63924,7 +63924,7 @@
         <v>45597</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63997,7 +63997,7 @@
         <v>45811</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64070,7 +64070,7 @@
         <v>45643</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64143,7 +64143,7 @@
         <v>45561</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64216,7 +64216,7 @@
         <v>45819</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64289,7 +64289,7 @@
         <v>45826</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64362,7 +64362,7 @@
         <v>45756</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64435,7 +64435,7 @@
         <v>45842</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64508,7 +64508,7 @@
         <v>45797</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64581,7 +64581,7 @@
         <v>45587</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64654,7 +64654,7 @@
         <v>45846</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64732,7 +64732,7 @@
         <v>45846</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64810,7 +64810,7 @@
         <v>45751</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64888,7 +64888,7 @@
         <v>45630</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64966,7 +64966,7 @@
         <v>45701</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>45788</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65112,7 +65112,7 @@
         <v>45861</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65185,7 +65185,7 @@
         <v>45788</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65258,7 +65258,7 @@
         <v>45870</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65336,7 +65336,7 @@
         <v>45875</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65414,7 +65414,7 @@
         <v>45734</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65487,7 +65487,7 @@
         <v>45880</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65560,7 +65560,7 @@
         <v>45883</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65633,7 +65633,7 @@
         <v>45883</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65706,7 +65706,7 @@
         <v>45883</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65779,7 +65779,7 @@
         <v>45883</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65852,7 +65852,7 @@
         <v>45313</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65930,7 +65930,7 @@
         <v>44658</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66003,7 +66003,7 @@
         <v>44607</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66076,7 +66076,7 @@
         <v>45131</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66154,7 +66154,7 @@
         <v>44593</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66227,7 +66227,7 @@
         <v>44510</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66300,7 +66300,7 @@
         <v>44956</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66378,7 +66378,7 @@
         <v>45407</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66456,7 +66456,7 @@
         <v>45327</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>44711</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66602,7 +66602,7 @@
         <v>44753</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66675,7 +66675,7 @@
         <v>44998</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66748,7 +66748,7 @@
         <v>45794</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66821,7 +66821,7 @@
         <v>45798</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66894,7 +66894,7 @@
         <v>45712</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66987,7 +66987,7 @@
         <v>45798</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67060,7 +67060,7 @@
         <v>45712</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67133,7 +67133,7 @@
         <v>45817</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67211,7 +67211,7 @@
         <v>45870</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67284,7 +67284,7 @@
         <v>45994</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67357,7 +67357,7 @@
         <v>46047</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45856</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45936</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46043</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>44607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46225</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46055</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>45609</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>45348</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45302</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46288</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44607</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45510</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>44970</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45268</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44963</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>46280</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>45930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44512</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>44992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>45788</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>46198</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45747</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44602</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>46176</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45604</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>46055</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46133</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>44536</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>44530</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>46107</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>45898</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>45777</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45783</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>44974</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44607</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>45629</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44747</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>46092</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44469</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45373</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>45679</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>46048</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>46049</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45580</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>45947</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>44991</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>45446</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>45331</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>45603</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>46174</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>46196</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45358</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>45982</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45758</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>46230</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45538</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>46286</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>45302</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>44943</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>45539</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44979</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45790</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>43983</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44647</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45013</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45393</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45790</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44613</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>44711</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>44467</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44579</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>45338</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>45558</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>45436</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>45477</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45740</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>44840</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45730</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>46035</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>46048</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>45720</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>44557</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>46055</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>45587</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>46059</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45926</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45201</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>46106</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45295</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45343</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44750</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>45205</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>46013</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>45764</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>45751</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>46162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45842</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>46162</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45841</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44893</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>45616</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45177</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>45600</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>45205</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45846</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>46203</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>46252</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>46211</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>46212</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>45272</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>44540</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>44879</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>46286</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>46279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45184</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44963</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>44992</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>45617</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44711</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44628</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>44955</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45029</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>45712</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45712</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45846</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>44496</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>44575</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>44662</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>44487</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>44749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>44749</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>44792</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44487</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44487</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>44749</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>44881</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>44665</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>44792</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>44538</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44487</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>44487</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         <v>44852</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44498</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>44881</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>44673</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>44754</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44476</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44855</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>44511</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>44466</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>44840</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>44537</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>44476</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>44575</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44711</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>44659</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>44659</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44578</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44474</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>44579</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44557</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>44616</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>44575</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>44575</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>44819</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44819</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44523</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>44846</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>44605</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>44711</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44841</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>44467</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>44792</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>44830</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44787</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44825</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44614</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44585</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>44711</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>44488</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>44498</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>44532</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>44593</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44729</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>44805</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>44811</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45197</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45341</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45621</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45621</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45697</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45008</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45531</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45324</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45324</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45406</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44804</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45092</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45321</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>45107</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45299</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45270</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45474</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>44893</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>45114</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>45243</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>44837</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44963</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45314</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45477</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45455</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45455</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45359</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45539</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45533</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45462</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>46013</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45502</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45502</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44853</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45883</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45883</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45145</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44488</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>46026</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>46026</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>44966</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45570</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44936</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>44853</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45169</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45883</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45883</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>44935</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45740</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45735</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45727</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45734</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>46030</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>46029</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>46031</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>46031</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45012</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44482</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45887</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45557</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45887</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45635</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>46035</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>45887</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>45295</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>46035</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>46038</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45892</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>45618</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45414</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45892</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45892</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44589</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>46041</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45895</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>46041</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>46041</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44893</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45545</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>46044</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>45898</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>46059</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>46043</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45538</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>46043</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>46048</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>46048</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>46048</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>46048</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45646</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44648</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>44735</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>46048</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>46048</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>46048</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>45902</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>46049</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>46050</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>46049</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>44550</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>45905</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>46055</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>46055</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>46055</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44589</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>45908</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45908</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>45908</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45908</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>46055</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         <v>44904</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45693</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>44943</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45216</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>46059</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>46059</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>46059</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
         <v>46059</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>46059</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
         <v>46059</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>46059</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>46062</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>46062</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>46062</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>45902</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>45009</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>46059</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>45917</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         <v>46063</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>46045</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45401</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>46069</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>46069</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>46069</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44992</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45566</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>46070</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>46070</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>45105</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>46070</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>45806</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>46073</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>45194</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45925</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>45197</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45021</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>46079</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>44950</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>45043</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>44938</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45805</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44977</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45597</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45934</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>44943</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>44943</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>46087</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>46091</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>45112</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45112</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44930</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45701</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>44575</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44950</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>45363</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>45364</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>44966</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>45945</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>45182</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>44988</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>46101</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45600</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>45600</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>45946</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>45946</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>44711</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>44998</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>45547</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>44894</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>45763</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>45295</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>45958</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45958</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45958</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>45671</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>45617</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>45113</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>45435</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>46119</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>46119</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>46119</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>46120</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>45316</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>46120</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>46120</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45966</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>45966</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45966</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45965</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34456,7 +34456,7 @@
         <v>45966</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>45966</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45968</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45811</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44965</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45706</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44734</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>45671</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>45974</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45974</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45974</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45974</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45015</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>45974</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>45974</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45974</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45974</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>45975</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45643</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>45978</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>45644</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>45979</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>45561</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45210</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>45617</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>45947</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>44614</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45758</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36555,7 +36555,7 @@
         <v>45988</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45693</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44729</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36774,7 +36774,7 @@
         <v>45469</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45558</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>45706</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>45149</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>45201</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>45726</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37227,7 +37227,7 @@
         <v>45995</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45846</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45730</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>44719</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>45035</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>46000</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37670,7 +37670,7 @@
         <v>45188</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37743,7 +37743,7 @@
         <v>44803</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>44882</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>45621</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>45810</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>45182</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>45841</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45708</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>45715</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45764</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>45834</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44627</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>44985</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45819</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46009</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>46009</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>46009</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>46009</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>46010</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>46008</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>46009</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>45958</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>46013</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>46013</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>46013</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>46013</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>46013</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39671,7 +39671,7 @@
         <v>45682</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45875</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         <v>45747</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>45272</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>45260</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>46002</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40109,7 +40109,7 @@
         <v>44886</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>45043</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>45826</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45734</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>44741</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45112</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>45749</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45775</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>45587</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>44468</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>44904</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>45037</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>45079</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>44882</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>45764</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>45355</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45324</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>45470</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>45740</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45183</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>45056</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45757</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>45201</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>46162</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>44483</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>45092</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45049</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45051</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>46162</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>46162</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>45111</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>46162</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>46162</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>45112</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>44950</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42699,7 +42699,7 @@
         <v>44950</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42772,7 +42772,7 @@
         <v>46162</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45842</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45349</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45846</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45846</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>45756</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45797</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>45587</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45119</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>46167</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>46167</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>45116</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45587</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>44957</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>45118</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>46168</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>46168</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45751</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44111,7 +44111,7 @@
         <v>46168</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44189,7 +44189,7 @@
         <v>45630</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44267,7 +44267,7 @@
         <v>45338</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>45562</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>45701</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>45788</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>46170</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45358</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
         <v>44484</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>45281</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>45275</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>46170</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>44628</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>44628</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>45861</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>46170</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>45335</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>46170</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45450,7 +45450,7 @@
         <v>45541</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45523,7 +45523,7 @@
         <v>44507</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45596,7 +45596,7 @@
         <v>46174</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>46174</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>46174</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45830,7 +45830,7 @@
         <v>45929</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45870</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45981,7 +45981,7 @@
         <v>45124</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>45267</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>45747</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>45460</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>46182</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45788</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>44605</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46492,7 +46492,7 @@
         <v>45175</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>46184</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>46189</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45405</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>45405</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45184</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>45547</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>44578</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47086,7 +47086,7 @@
         <v>44592</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45541</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
         <v>46188</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>45412</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47383,7 +47383,7 @@
         <v>45734</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47456,7 +47456,7 @@
         <v>45552</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>45462</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>44585</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47675,7 +47675,7 @@
         <v>45763</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47748,7 +47748,7 @@
         <v>45875</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45645</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>45184</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45681</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48045,7 +48045,7 @@
         <v>46197</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48118,7 +48118,7 @@
         <v>45880</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>44591</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>46201</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>44608</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>45169</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>46201</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>44626</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48629,7 +48629,7 @@
         <v>46201</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>46198</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>46203</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45435</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>46203</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45030</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>45371</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>45617</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>45056</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49291,7 +49291,7 @@
         <v>44564</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49364,7 +49364,7 @@
         <v>45174</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>45726</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49510,7 +49510,7 @@
         <v>44571</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>46206</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>45179</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>46206</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>46252</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49885,7 +49885,7 @@
         <v>46206</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49963,7 +49963,7 @@
         <v>45182</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>46211</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>46211</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>45440</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>46211</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>46211</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>44614</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>46211</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>46211</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>46211</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>46211</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50776,7 +50776,7 @@
         <v>46211</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50849,7 +50849,7 @@
         <v>44839</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>46211</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>46211</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51073,7 +51073,7 @@
         <v>46212</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51146,7 +51146,7 @@
         <v>44659</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45705</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>46255</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>46212</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>46212</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45456</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>45215</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45404</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45523</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>45392</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>44704</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51969,7 +51969,7 @@
         <v>45198</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52042,7 +52042,7 @@
         <v>45198</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>45946</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>44655</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52261,7 +52261,7 @@
         <v>45211</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52334,7 +52334,7 @@
         <v>46219</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52407,7 +52407,7 @@
         <v>44734</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52485,7 +52485,7 @@
         <v>44734</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52563,7 +52563,7 @@
         <v>45194</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45194</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>46219</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52782,7 +52782,7 @@
         <v>45681</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>46262</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45756</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>45169</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>45197</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53147,7 +53147,7 @@
         <v>45759</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53220,7 +53220,7 @@
         <v>45314</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>45303</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45842</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45245</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53517,7 +53517,7 @@
         <v>46220</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53590,7 +53590,7 @@
         <v>45189</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53663,7 +53663,7 @@
         <v>45294</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53741,7 +53741,7 @@
         <v>44904</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>44897</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53892,7 +53892,7 @@
         <v>44904</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53970,7 +53970,7 @@
         <v>45246</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>46265</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54121,7 +54121,7 @@
         <v>45761</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54194,7 +54194,7 @@
         <v>45679</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54267,7 +54267,7 @@
         <v>46267</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>45226</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>46268</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54486,7 +54486,7 @@
         <v>45240</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54559,7 +54559,7 @@
         <v>46270</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54632,7 +54632,7 @@
         <v>46272</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54705,7 +54705,7 @@
         <v>46272</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>46272</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         <v>46272</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54924,7 +54924,7 @@
         <v>46272</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54997,7 +54997,7 @@
         <v>46230</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55075,7 +55075,7 @@
         <v>46230</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55153,7 +55153,7 @@
         <v>46273</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>46276</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>46276</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>46274</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>44889</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55518,7 +55518,7 @@
         <v>45198</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45198</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45201</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>45534</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>46234</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55883,7 +55883,7 @@
         <v>46279</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55961,7 +55961,7 @@
         <v>46279</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56039,7 +56039,7 @@
         <v>46279</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>46233</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>46234</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56268,7 +56268,7 @@
         <v>46234</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56341,7 +56341,7 @@
         <v>45253</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45300</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56487,7 +56487,7 @@
         <v>45215</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56560,7 +56560,7 @@
         <v>45392</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>46233</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>46234</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56784,7 +56784,7 @@
         <v>46267</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56857,7 +56857,7 @@
         <v>46239</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56930,7 +56930,7 @@
         <v>46279</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>44867</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57081,7 +57081,7 @@
         <v>45477</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57154,7 +57154,7 @@
         <v>45477</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>44904</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57300,7 +57300,7 @@
         <v>46239</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>46238</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>46282</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>46286</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45302</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57665,7 +57665,7 @@
         <v>46286</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57738,7 +57738,7 @@
         <v>46286</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57811,7 +57811,7 @@
         <v>46286</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57889,7 +57889,7 @@
         <v>46281</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57962,7 +57962,7 @@
         <v>44893</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58035,7 +58035,7 @@
         <v>45406</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58108,7 +58108,7 @@
         <v>45406</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58181,7 +58181,7 @@
         <v>46286</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58259,7 +58259,7 @@
         <v>44853</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>44484</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>44949</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58478,7 +58478,7 @@
         <v>44648</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>46286</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58624,7 +58624,7 @@
         <v>44861</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         <v>44938</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>45375</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>45180</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58921,7 +58921,7 @@
         <v>46244</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58994,7 +58994,7 @@
         <v>44943</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59067,7 +59067,7 @@
         <v>44614</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>44711</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59213,7 +59213,7 @@
         <v>46279</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>46244</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59364,7 +59364,7 @@
         <v>46244</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59437,7 +59437,7 @@
         <v>44622</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>46244</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59583,7 +59583,7 @@
         <v>45058</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59656,7 +59656,7 @@
         <v>46290</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59734,7 +59734,7 @@
         <v>46246</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59807,7 +59807,7 @@
         <v>44662</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59880,7 +59880,7 @@
         <v>46246</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59953,7 +59953,7 @@
         <v>46246</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60026,7 +60026,7 @@
         <v>46290</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>46290</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60182,7 +60182,7 @@
         <v>45271</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60255,7 +60255,7 @@
         <v>44861</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>44861</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60401,7 +60401,7 @@
         <v>46248</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60474,7 +60474,7 @@
         <v>46247</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60547,7 +60547,7 @@
         <v>46248</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60620,7 +60620,7 @@
         <v>45461</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60693,7 +60693,7 @@
         <v>46290</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60771,7 +60771,7 @@
         <v>45541</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>45043</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60917,7 +60917,7 @@
         <v>44897</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60995,7 +60995,7 @@
         <v>45455</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61073,7 +61073,7 @@
         <v>44507</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61146,7 +61146,7 @@
         <v>45569</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61219,7 +61219,7 @@
         <v>44943</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61292,7 +61292,7 @@
         <v>44943</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61365,7 +61365,7 @@
         <v>45580</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61438,7 +61438,7 @@
         <v>45477</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61511,7 +61511,7 @@
         <v>45547</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61589,7 +61589,7 @@
         <v>45034</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61662,7 +61662,7 @@
         <v>44677</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61735,7 +61735,7 @@
         <v>44658</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61808,7 +61808,7 @@
         <v>45048</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61881,7 +61881,7 @@
         <v>45051</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61954,7 +61954,7 @@
         <v>44846</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62027,7 +62027,7 @@
         <v>45130</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62100,7 +62100,7 @@
         <v>45764</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>45471</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62246,7 +62246,7 @@
         <v>44977</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62319,7 +62319,7 @@
         <v>44998</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62392,7 +62392,7 @@
         <v>45673</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45152</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62538,7 +62538,7 @@
         <v>45401</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62616,7 +62616,7 @@
         <v>45373</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62689,7 +62689,7 @@
         <v>45127</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62762,7 +62762,7 @@
         <v>44967</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62835,7 +62835,7 @@
         <v>45605</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62908,7 +62908,7 @@
         <v>45152</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62981,7 +62981,7 @@
         <v>45092</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63054,7 +63054,7 @@
         <v>45757</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63127,7 +63127,7 @@
         <v>45615</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63200,7 +63200,7 @@
         <v>44631</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63273,7 +63273,7 @@
         <v>45240</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>45642</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63419,7 +63419,7 @@
         <v>45012</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63492,7 +63492,7 @@
         <v>45300</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63565,7 +63565,7 @@
         <v>45588</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63638,7 +63638,7 @@
         <v>44985</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63711,7 +63711,7 @@
         <v>45099</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63784,7 +63784,7 @@
         <v>45363</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63857,7 +63857,7 @@
         <v>45177</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63930,7 +63930,7 @@
         <v>45223</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64003,7 +64003,7 @@
         <v>45181</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64076,7 +64076,7 @@
         <v>44487</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45356</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64227,7 +64227,7 @@
         <v>45107</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64300,7 +64300,7 @@
         <v>44588</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64373,7 +64373,7 @@
         <v>45201</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64451,7 +64451,7 @@
         <v>45545</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64524,7 +64524,7 @@
         <v>45169</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64597,7 +64597,7 @@
         <v>45468</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64670,7 +64670,7 @@
         <v>44904</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64743,7 +64743,7 @@
         <v>44904</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64816,7 +64816,7 @@
         <v>44923</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64889,7 +64889,7 @@
         <v>45414</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64962,7 +64962,7 @@
         <v>45377</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65035,7 +65035,7 @@
         <v>45351</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65113,7 +65113,7 @@
         <v>45219</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65186,7 +65186,7 @@
         <v>45477</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65259,7 +65259,7 @@
         <v>45406</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65332,7 +65332,7 @@
         <v>45492</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65405,7 +65405,7 @@
         <v>45566</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65478,7 +65478,7 @@
         <v>45734</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65551,7 +65551,7 @@
         <v>45615</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65624,7 +65624,7 @@
         <v>45701</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65697,7 +65697,7 @@
         <v>45758</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65775,7 +65775,7 @@
         <v>44944</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65848,7 +65848,7 @@
         <v>45764</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65921,7 +65921,7 @@
         <v>45307</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65994,7 +65994,7 @@
         <v>45099</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66067,7 +66067,7 @@
         <v>45667</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66140,7 +66140,7 @@
         <v>45586</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66213,7 +66213,7 @@
         <v>45519</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66286,7 +66286,7 @@
         <v>45646</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66359,7 +66359,7 @@
         <v>45551</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66432,7 +66432,7 @@
         <v>45541</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66505,7 +66505,7 @@
         <v>45350</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66578,7 +66578,7 @@
         <v>44658</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66651,7 +66651,7 @@
         <v>44607</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66724,7 +66724,7 @@
         <v>44593</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66797,7 +66797,7 @@
         <v>44711</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66870,7 +66870,7 @@
         <v>45313</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66948,7 +66948,7 @@
         <v>45131</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67026,7 +67026,7 @@
         <v>44510</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67099,7 +67099,7 @@
         <v>44956</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67177,7 +67177,7 @@
         <v>45407</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67255,7 +67255,7 @@
         <v>45327</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67328,7 +67328,7 @@
         <v>44753</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67401,7 +67401,7 @@
         <v>44998</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67474,7 +67474,7 @@
         <v>45794</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67547,7 +67547,7 @@
         <v>45798</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67620,7 +67620,7 @@
         <v>45712</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67713,7 +67713,7 @@
         <v>45798</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67786,7 +67786,7 @@
         <v>45712</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67859,7 +67859,7 @@
         <v>45817</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67937,7 +67937,7 @@
         <v>45870</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68010,7 +68010,7 @@
         <v>45994</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68083,7 +68083,7 @@
         <v>46047</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45856</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45936</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46043</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>44607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46225</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46055</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>45609</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>45348</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45302</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46288</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44607</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45510</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>44970</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45268</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44963</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>46280</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>45930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44512</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>44992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>45788</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>46198</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45747</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44602</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>46176</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45604</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>46055</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46133</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>44536</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>44530</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>46107</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>45898</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>45777</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45783</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>44974</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44607</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>45629</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44747</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>46092</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44469</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45373</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>45679</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>46048</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>46049</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45580</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>45947</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>44991</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>45446</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>45331</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>45603</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>46174</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>46196</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45358</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>45982</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45758</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>46230</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45538</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>46286</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>45302</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>44943</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>45539</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44979</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45790</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>43983</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44647</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45013</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45393</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45790</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44613</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>44711</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>44467</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44579</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>45338</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>45558</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>45436</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>45477</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45740</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>44840</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45730</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>46035</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>46048</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>45720</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>44557</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>46055</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>45587</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>46059</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45926</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45201</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>46106</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45295</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45343</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44750</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>45205</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>46013</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>45764</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>45751</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>46162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45842</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>46162</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45841</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44893</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>45616</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45177</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>45600</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>45205</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45846</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>46203</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>46252</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>46211</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>46212</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>45272</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>44540</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>44879</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>46286</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>46279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45184</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44963</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>44992</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>45617</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44711</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44628</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>44955</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45029</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>45712</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45712</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45846</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>44496</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>44575</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>44662</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>44487</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>44749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>44749</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>44792</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44487</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44487</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>44749</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>44881</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>44665</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>44792</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>44538</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44487</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>44487</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         <v>44852</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44498</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>44881</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>44673</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>44754</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44476</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44855</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>44511</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>44466</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>44840</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>44537</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>44476</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>44575</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44711</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>44659</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>44659</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44578</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44474</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>44579</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44557</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>44616</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>44575</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>44575</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>44819</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44819</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44523</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>44846</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>44605</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>44711</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44841</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>44467</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>44792</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>44830</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44787</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44825</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>44614</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44585</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>44711</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>44488</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>44498</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>44532</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>44593</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44729</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>44805</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>44811</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45197</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45341</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45621</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45621</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45697</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45008</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45531</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45324</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45324</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45406</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44804</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45092</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45321</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>45107</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45299</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45270</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45474</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>44893</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>45114</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>45243</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>44837</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44963</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45314</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45477</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45455</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45455</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45359</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45539</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45533</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45462</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>46013</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45502</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45502</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44853</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45883</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45883</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45145</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44488</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>46026</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>46026</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>44966</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45570</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44936</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>44853</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45169</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45883</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45883</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>44935</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45740</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45735</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45727</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45734</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>46030</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>46029</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>46031</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>46031</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45012</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44482</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45887</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45557</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45887</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45635</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>46035</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>45887</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>45295</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>46035</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>46038</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45892</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>45618</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45414</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45892</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45892</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44589</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>46041</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45895</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>46041</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>46041</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44893</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45545</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>46044</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>45898</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>46059</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>46043</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45538</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>46043</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>46048</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>46048</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>46048</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>46048</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45646</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44648</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>44735</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>46048</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>46048</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>46048</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>45902</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>46049</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>46050</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>46049</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>44550</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>45905</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>46055</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>46055</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>46055</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44589</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>45908</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45908</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>45908</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45908</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>46055</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         <v>44904</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45693</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>44943</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45216</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>46059</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>46059</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>46059</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
         <v>46059</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>46059</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
         <v>46059</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>46059</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>46062</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>46062</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>46062</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>45902</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>45009</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>46059</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>45917</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         <v>46063</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>46045</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45401</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>46069</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>46069</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>46069</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44992</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45566</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>46070</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>46070</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>45105</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>46070</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>45806</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>46073</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>45194</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45925</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>45197</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45021</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>46079</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>44950</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>45043</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>44938</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45805</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44977</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45597</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45934</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>44943</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>44943</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>46087</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>46091</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>45112</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45112</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44930</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45701</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>44575</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44950</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>45363</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>45364</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>44966</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>45945</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>45182</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>44988</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>46101</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45600</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>45600</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>45946</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>45946</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>44711</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>44998</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>45547</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>44894</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>45763</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>45295</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>45958</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45958</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45958</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>45671</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>45617</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>45113</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>45435</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>46119</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>46119</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>46119</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>46120</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>45316</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>46120</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>46120</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45966</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>45966</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45966</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45965</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34456,7 +34456,7 @@
         <v>45966</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>45966</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45968</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45811</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44965</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45706</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44734</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>45671</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>45974</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45974</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45974</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45974</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45015</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>45974</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>45974</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45974</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45974</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>45975</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45643</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>45978</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>45644</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>45979</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>45561</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45210</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>45617</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>45947</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>44614</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45758</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36555,7 +36555,7 @@
         <v>45988</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36628,7 +36628,7 @@
         <v>45693</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44729</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36774,7 +36774,7 @@
         <v>45469</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45558</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>45706</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>45149</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>45201</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>45726</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37227,7 +37227,7 @@
         <v>45995</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45846</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45730</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>44719</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>45035</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>46000</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37670,7 +37670,7 @@
         <v>45188</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37743,7 +37743,7 @@
         <v>44803</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>44882</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>45621</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>45810</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>45182</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>45841</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45708</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>45715</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45764</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>45834</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44627</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>44985</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45819</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46009</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>46009</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>46009</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>46009</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>46010</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>46008</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>46009</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>45958</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>46013</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>46013</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>46013</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>46013</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>46013</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39671,7 +39671,7 @@
         <v>45682</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45875</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         <v>45747</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>45272</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>45260</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>46002</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40109,7 +40109,7 @@
         <v>44886</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>45043</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>45826</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45734</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>44741</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45112</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>45749</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45775</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>45587</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>44468</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>44904</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>45037</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>45079</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>44882</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>45764</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>45355</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45324</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>45470</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>45740</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>45183</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>45056</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45757</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>45201</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>46162</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>44483</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>45092</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45049</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45051</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>46162</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>46162</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>45111</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>46162</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>46162</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>45112</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>44950</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42699,7 +42699,7 @@
         <v>44950</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42772,7 +42772,7 @@
         <v>46162</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45842</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45349</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45846</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45846</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>45756</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45797</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>45587</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45119</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>46167</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>46167</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>45116</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45587</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>44957</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>45118</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>46168</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>46168</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45751</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44111,7 +44111,7 @@
         <v>46168</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44189,7 +44189,7 @@
         <v>45630</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44267,7 +44267,7 @@
         <v>45338</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>45562</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>45701</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>45788</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>46170</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45358</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
         <v>44484</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>45281</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>45275</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>46170</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>44628</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>44628</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>45861</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>46170</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>45335</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>46170</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45450,7 +45450,7 @@
         <v>45541</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45523,7 +45523,7 @@
         <v>44507</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45596,7 +45596,7 @@
         <v>46174</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>46174</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>46174</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45830,7 +45830,7 @@
         <v>45929</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45870</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45981,7 +45981,7 @@
         <v>45124</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>45267</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>45747</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>45460</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>46182</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45788</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>44605</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46492,7 +46492,7 @@
         <v>45175</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>46184</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>46189</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45405</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>45405</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45184</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>45547</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>44578</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47086,7 +47086,7 @@
         <v>44592</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45541</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
         <v>46188</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>45412</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47383,7 +47383,7 @@
         <v>45734</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47456,7 +47456,7 @@
         <v>45552</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>45462</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>44585</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47675,7 +47675,7 @@
         <v>45763</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47748,7 +47748,7 @@
         <v>45875</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45645</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>45184</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45681</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48045,7 +48045,7 @@
         <v>46197</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48118,7 +48118,7 @@
         <v>45880</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>44591</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>46201</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>44608</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>45169</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>46201</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>44626</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48629,7 +48629,7 @@
         <v>46201</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>46198</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>46203</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45435</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>46203</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45030</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>45371</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>45617</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>45056</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49291,7 +49291,7 @@
         <v>44564</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49364,7 +49364,7 @@
         <v>45174</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>45726</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49510,7 +49510,7 @@
         <v>44571</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>46206</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>45179</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>46206</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>46252</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49885,7 +49885,7 @@
         <v>46206</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49963,7 +49963,7 @@
         <v>45182</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>46211</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>46211</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>45440</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>46211</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>46211</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>44614</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>46211</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>46211</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>46211</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>46211</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50776,7 +50776,7 @@
         <v>46211</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50849,7 +50849,7 @@
         <v>44839</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>46211</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>46211</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51073,7 +51073,7 @@
         <v>46212</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51146,7 +51146,7 @@
         <v>44659</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45705</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>46255</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>46212</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>46212</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45456</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>45215</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45404</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45523</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>45392</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>44704</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51969,7 +51969,7 @@
         <v>45198</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52042,7 +52042,7 @@
         <v>45198</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>45946</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>44655</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52261,7 +52261,7 @@
         <v>45211</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52334,7 +52334,7 @@
         <v>46219</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52407,7 +52407,7 @@
         <v>44734</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52485,7 +52485,7 @@
         <v>44734</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52563,7 +52563,7 @@
         <v>45194</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45194</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>46219</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52782,7 +52782,7 @@
         <v>45681</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>46262</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45756</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>45169</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>45197</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53147,7 +53147,7 @@
         <v>45759</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53220,7 +53220,7 @@
         <v>45314</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>45303</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45842</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45245</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53517,7 +53517,7 @@
         <v>46220</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53590,7 +53590,7 @@
         <v>45189</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53663,7 +53663,7 @@
         <v>45294</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53741,7 +53741,7 @@
         <v>44904</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>44897</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53892,7 +53892,7 @@
         <v>44904</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53970,7 +53970,7 @@
         <v>45246</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>46265</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54121,7 +54121,7 @@
         <v>45761</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54194,7 +54194,7 @@
         <v>45679</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54267,7 +54267,7 @@
         <v>46267</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>45226</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>46268</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54486,7 +54486,7 @@
         <v>45240</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54559,7 +54559,7 @@
         <v>46270</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54632,7 +54632,7 @@
         <v>46272</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54705,7 +54705,7 @@
         <v>46272</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>46272</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         <v>46272</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54924,7 +54924,7 @@
         <v>46272</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54997,7 +54997,7 @@
         <v>46230</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55075,7 +55075,7 @@
         <v>46230</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55153,7 +55153,7 @@
         <v>46273</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>46276</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>46276</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>46274</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>44889</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55518,7 +55518,7 @@
         <v>45198</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45198</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45201</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>45534</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>46234</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55883,7 +55883,7 @@
         <v>46279</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55961,7 +55961,7 @@
         <v>46279</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56039,7 +56039,7 @@
         <v>46279</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>46233</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>46234</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56268,7 +56268,7 @@
         <v>46234</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56341,7 +56341,7 @@
         <v>45253</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45300</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56487,7 +56487,7 @@
         <v>45215</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56560,7 +56560,7 @@
         <v>45392</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>46233</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>46234</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56784,7 +56784,7 @@
         <v>46267</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56857,7 +56857,7 @@
         <v>46239</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56930,7 +56930,7 @@
         <v>46279</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>44867</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57081,7 +57081,7 @@
         <v>45477</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57154,7 +57154,7 @@
         <v>45477</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>44904</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57300,7 +57300,7 @@
         <v>46239</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>46238</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>46282</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>46286</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45302</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57665,7 +57665,7 @@
         <v>46286</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57738,7 +57738,7 @@
         <v>46286</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57811,7 +57811,7 @@
         <v>46286</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57889,7 +57889,7 @@
         <v>46281</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57962,7 +57962,7 @@
         <v>44893</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58035,7 +58035,7 @@
         <v>45406</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58108,7 +58108,7 @@
         <v>45406</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58181,7 +58181,7 @@
         <v>46286</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58259,7 +58259,7 @@
         <v>44853</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>44484</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>44949</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58478,7 +58478,7 @@
         <v>44648</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>46286</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58624,7 +58624,7 @@
         <v>44861</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         <v>44938</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>45375</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>45180</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58921,7 +58921,7 @@
         <v>46244</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58994,7 +58994,7 @@
         <v>44943</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59067,7 +59067,7 @@
         <v>44614</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59140,7 +59140,7 @@
         <v>44711</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59213,7 +59213,7 @@
         <v>46279</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>46244</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59364,7 +59364,7 @@
         <v>46244</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59437,7 +59437,7 @@
         <v>44622</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>46244</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59583,7 +59583,7 @@
         <v>45058</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59656,7 +59656,7 @@
         <v>46290</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59734,7 +59734,7 @@
         <v>46246</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59807,7 +59807,7 @@
         <v>44662</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59880,7 +59880,7 @@
         <v>46246</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59953,7 +59953,7 @@
         <v>46246</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60026,7 +60026,7 @@
         <v>46290</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>46290</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60182,7 +60182,7 @@
         <v>45271</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60255,7 +60255,7 @@
         <v>44861</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>44861</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60401,7 +60401,7 @@
         <v>46248</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60474,7 +60474,7 @@
         <v>46247</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60547,7 +60547,7 @@
         <v>46248</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60620,7 +60620,7 @@
         <v>45461</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60693,7 +60693,7 @@
         <v>46290</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60771,7 +60771,7 @@
         <v>45541</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>45043</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60917,7 +60917,7 @@
         <v>44897</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60995,7 +60995,7 @@
         <v>45455</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61073,7 +61073,7 @@
         <v>44507</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61146,7 +61146,7 @@
         <v>45569</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61219,7 +61219,7 @@
         <v>44943</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61292,7 +61292,7 @@
         <v>44943</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61365,7 +61365,7 @@
         <v>45580</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61438,7 +61438,7 @@
         <v>45477</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61511,7 +61511,7 @@
         <v>45547</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61589,7 +61589,7 @@
         <v>45034</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61662,7 +61662,7 @@
         <v>44677</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61735,7 +61735,7 @@
         <v>44658</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61808,7 +61808,7 @@
         <v>45048</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61881,7 +61881,7 @@
         <v>45051</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61954,7 +61954,7 @@
         <v>44846</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62027,7 +62027,7 @@
         <v>45130</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62100,7 +62100,7 @@
         <v>45764</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>45471</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62246,7 +62246,7 @@
         <v>44977</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62319,7 +62319,7 @@
         <v>44998</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62392,7 +62392,7 @@
         <v>45673</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45152</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62538,7 +62538,7 @@
         <v>45401</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62616,7 +62616,7 @@
         <v>45373</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62689,7 +62689,7 @@
         <v>45127</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62762,7 +62762,7 @@
         <v>44967</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62835,7 +62835,7 @@
         <v>45605</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62908,7 +62908,7 @@
         <v>45152</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62981,7 +62981,7 @@
         <v>45092</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63054,7 +63054,7 @@
         <v>45757</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63127,7 +63127,7 @@
         <v>45615</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63200,7 +63200,7 @@
         <v>44631</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63273,7 +63273,7 @@
         <v>45240</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>45642</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63419,7 +63419,7 @@
         <v>45012</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63492,7 +63492,7 @@
         <v>45300</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63565,7 +63565,7 @@
         <v>45588</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63638,7 +63638,7 @@
         <v>44985</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63711,7 +63711,7 @@
         <v>45099</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63784,7 +63784,7 @@
         <v>45363</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63857,7 +63857,7 @@
         <v>45177</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63930,7 +63930,7 @@
         <v>45223</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64003,7 +64003,7 @@
         <v>45181</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64076,7 +64076,7 @@
         <v>44487</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45356</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64227,7 +64227,7 @@
         <v>45107</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64300,7 +64300,7 @@
         <v>44588</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64373,7 +64373,7 @@
         <v>45201</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64451,7 +64451,7 @@
         <v>45545</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64524,7 +64524,7 @@
         <v>45169</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64597,7 +64597,7 @@
         <v>45468</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64670,7 +64670,7 @@
         <v>44904</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64743,7 +64743,7 @@
         <v>44904</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64816,7 +64816,7 @@
         <v>44923</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64889,7 +64889,7 @@
         <v>45414</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64962,7 +64962,7 @@
         <v>45377</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65035,7 +65035,7 @@
         <v>45351</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65113,7 +65113,7 @@
         <v>45219</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65186,7 +65186,7 @@
         <v>45477</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65259,7 +65259,7 @@
         <v>45406</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65332,7 +65332,7 @@
         <v>45492</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65405,7 +65405,7 @@
         <v>45566</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65478,7 +65478,7 @@
         <v>45734</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65551,7 +65551,7 @@
         <v>45615</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65624,7 +65624,7 @@
         <v>45701</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65697,7 +65697,7 @@
         <v>45758</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65775,7 +65775,7 @@
         <v>44944</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65848,7 +65848,7 @@
         <v>45764</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65921,7 +65921,7 @@
         <v>45307</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65994,7 +65994,7 @@
         <v>45099</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66067,7 +66067,7 @@
         <v>45667</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66140,7 +66140,7 @@
         <v>45586</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66213,7 +66213,7 @@
         <v>45519</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66286,7 +66286,7 @@
         <v>45646</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66359,7 +66359,7 @@
         <v>45551</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66432,7 +66432,7 @@
         <v>45541</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66505,7 +66505,7 @@
         <v>45350</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66578,7 +66578,7 @@
         <v>44658</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66651,7 +66651,7 @@
         <v>44607</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66724,7 +66724,7 @@
         <v>44593</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66797,7 +66797,7 @@
         <v>44711</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66870,7 +66870,7 @@
         <v>45313</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66948,7 +66948,7 @@
         <v>45131</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67026,7 +67026,7 @@
         <v>44510</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67099,7 +67099,7 @@
         <v>44956</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67177,7 +67177,7 @@
         <v>45407</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67255,7 +67255,7 @@
         <v>45327</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67328,7 +67328,7 @@
         <v>44753</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67401,7 +67401,7 @@
         <v>44998</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67474,7 +67474,7 @@
         <v>45794</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67547,7 +67547,7 @@
         <v>45798</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67620,7 +67620,7 @@
         <v>45712</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67713,7 +67713,7 @@
         <v>45798</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67786,7 +67786,7 @@
         <v>45712</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67859,7 +67859,7 @@
         <v>45817</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67937,7 +67937,7 @@
         <v>45870</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68010,7 +68010,7 @@
         <v>45994</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68083,7 +68083,7 @@
         <v>46047</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45856</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45936</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46043</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45111</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44607</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46225</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>45609</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>45348</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>46055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45302</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46288</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44607</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45510</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>44970</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45268</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44963</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>46280</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>45930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>45788</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>46198</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44512</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45747</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44602</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45604</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46176</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>46055</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46133</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>44536</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>44530</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>46107</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45898</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45777</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>44974</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45783</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45772</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44747</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>44607</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>46092</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45580</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>45790</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45539</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>45331</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45679</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>46048</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>46049</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>45446</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>45947</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>45373</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44943</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>45603</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>45538</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>46174</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>45302</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>46196</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>46230</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>46286</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>44991</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>45758</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>45982</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45358</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>43983</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>45013</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44647</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45393</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45790</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44613</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44711</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44579</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45477</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44750</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45177</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45436</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45295</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44840</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>46013</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>46035</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>45272</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>46048</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>45205</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45740</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>45587</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>46055</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>46059</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>45926</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>46106</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45338</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45841</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45842</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45616</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45205</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45764</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>45846</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45184</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>46162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>46162</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>44557</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>45730</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>44963</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
         <v>46203</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>46212</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>46211</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45751</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44992</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44879</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>46286</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>46279</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45343</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>46294</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>44893</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>46252</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>45558</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>45600</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45617</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45201</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>44540</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>44955</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>45029</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>44711</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44628</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>45712</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45712</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45846</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>44496</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44487</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>44575</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>44662</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>44749</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>44749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>44792</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44487</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44487</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44749</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>44881</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>44665</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>44792</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44538</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>44487</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44487</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>44852</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>44498</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>44881</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>44673</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44754</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>44855</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>44476</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>44511</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>44840</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>44537</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44476</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44575</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>44659</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>44659</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>44578</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>44474</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44711</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44579</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44557</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>44616</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>44575</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>44575</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>44819</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>44819</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>44523</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>44846</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>44605</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44711</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>44841</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>44792</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>44830</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44787</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44825</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>44614</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>44585</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>44711</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44488</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44498</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44532</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>44593</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>44729</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>44805</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>44811</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>44853</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>45435</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45114</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45764</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>44711</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45617</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45469</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>45272</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45747</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45404</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>45697</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>45169</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45012</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>45048</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>45605</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45152</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>44589</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45145</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45111</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>44628</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>45012</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45092</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45726</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45307</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>45405</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21413,7 +21413,7 @@
         <v>45405</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>45621</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>46000</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44943</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>44998</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>45621</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>45621</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>45295</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45392</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>45887</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45456</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45645</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45541</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45757</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>46009</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>46008</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>45551</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>46013</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
         <v>45958</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
         <v>46013</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44938</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>46010</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>46009</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>46013</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>46009</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>46009</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>46013</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>46013</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>44943</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>46009</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>46013</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45350</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>45646</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45253</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45184</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>46026</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45892</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>46026</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45892</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45892</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>46029</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45895</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>46031</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>46030</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>46031</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45898</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45116</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>46035</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>45545</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>45902</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>44949</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>46035</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>45905</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>46041</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>44482</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44662</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44904</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45908</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45908</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>46038</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>46041</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45908</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45908</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>46043</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44904</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>44897</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44904</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>46043</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>46059</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>46041</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>45693</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>44861</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44861</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45570</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>46044</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45406</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>46048</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>44735</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>46048</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>46049</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>46048</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>46049</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>46048</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45740</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46048</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45902</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>46048</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45735</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45734</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>44992</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>44882</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>46050</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>45917</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45805</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45806</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>46055</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>45183</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>46055</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>46055</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>46055</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>45373</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>45925</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>44571</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>45539</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>44592</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45547</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>46059</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>46059</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>46059</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>46059</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>45597</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>46059</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>46059</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>46059</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>46059</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>45811</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45455</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>46062</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>46062</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45182</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>46062</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>46063</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>46045</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>46069</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30540,7 +30540,7 @@
         <v>46069</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>46069</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45461</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44622</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>44893</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>45037</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45934</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>45600</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>45600</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>45701</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>46070</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45726</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>45215</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>46070</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>46070</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>46073</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>45468</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45371</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45945</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>45682</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>44977</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>45946</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>45946</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>45617</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>46079</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>44585</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45152</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45351</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>46087</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45958</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>44846</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>45958</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45958</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>45643</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>45502</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>46091</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>44904</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>45965</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>45966</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33402,7 +33402,7 @@
         <v>45189</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45966</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45966</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45966</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>44507</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>45561</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>45358</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45966</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45294</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45968</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45079</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>45974</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>45035</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45974</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>45974</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>45974</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>45974</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>44950</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>45975</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34819,7 +34819,7 @@
         <v>45240</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>46101</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44626</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>45974</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45974</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35194,7 +35194,7 @@
         <v>45974</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>45979</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45978</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45246</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>45058</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45819</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>45119</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>45566</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>45566</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>45502</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>44837</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>45210</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36080,7 +36080,7 @@
         <v>44614</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36153,7 +36153,7 @@
         <v>46119</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>46119</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>46120</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45021</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>46120</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>46120</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>44963</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>45988</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36737,7 +36737,7 @@
         <v>46119</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>44935</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36883,7 +36883,7 @@
         <v>44867</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45180</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>44904</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>44575</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37175,7 +37175,7 @@
         <v>45995</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37248,7 +37248,7 @@
         <v>45826</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>45260</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45008</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37467,7 +37467,7 @@
         <v>45105</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37540,7 +37540,7 @@
         <v>45474</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37613,7 +37613,7 @@
         <v>45124</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37686,7 +37686,7 @@
         <v>45759</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>45051</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>44487</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>45316</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>44631</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45552</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45810</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>44483</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>45169</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>45679</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>45756</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44923</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>45834</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45842</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>45558</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>45797</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45587</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>46002</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45764</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>45846</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45846</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45300</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45751</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>45681</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>45758</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>44659</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39614,7 +39614,7 @@
         <v>45730</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>45841</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45455</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>45846</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>44889</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39989,7 +39989,7 @@
         <v>44853</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40062,7 +40062,7 @@
         <v>45401</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>44988</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>45471</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45198</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45947</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>45630</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>45701</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>45364</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>45188</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>45356</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40802,7 +40802,7 @@
         <v>45764</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>45181</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>44882</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41021,7 +41021,7 @@
         <v>45788</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>44965</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41167,7 +41167,7 @@
         <v>45861</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45749</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41313,7 +41313,7 @@
         <v>44648</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41386,7 +41386,7 @@
         <v>45734</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>45194</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45763</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>44943</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>44943</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45587</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>45875</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45642</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41970,7 +41970,7 @@
         <v>45775</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>45734</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>45043</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45788</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>45870</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42340,7 +42340,7 @@
         <v>45392</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>45271</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42486,7 +42486,7 @@
         <v>45215</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>44803</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>45673</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>44957</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42778,7 +42778,7 @@
         <v>45460</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>45030</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>44977</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45034</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43070,7 +43070,7 @@
         <v>45470</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>45875</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>45349</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43294,7 +43294,7 @@
         <v>45734</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>45182</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>45763</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45646</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43586,7 +43586,7 @@
         <v>45169</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>45169</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
         <v>46162</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43810,7 +43810,7 @@
         <v>44704</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43883,7 +43883,7 @@
         <v>45401</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>46162</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>45414</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>46162</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>46162</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>46162</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>46162</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>45758</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>46167</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>46167</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>46168</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45880</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>46168</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44877,7 +44877,7 @@
         <v>45198</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44950,7 +44950,7 @@
         <v>45198</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45023,7 +45023,7 @@
         <v>46168</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45096,7 +45096,7 @@
         <v>44886</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>44658</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>45303</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>46170</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>45580</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>44550</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>46170</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45455</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>46170</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45763,7 +45763,7 @@
         <v>46170</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45130</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45477</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>45547</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46060,7 +46060,7 @@
         <v>45112</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>45112</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46206,7 +46206,7 @@
         <v>46174</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46284,7 +46284,7 @@
         <v>45174</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>44628</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>46174</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>46174</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46586,7 +46586,7 @@
         <v>45557</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46659,7 +46659,7 @@
         <v>45883</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>45883</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45883</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>44614</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45883</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>45462</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>44861</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>45929</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45887</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45887</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>45324</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>45270</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47540,7 +47540,7 @@
         <v>45179</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47613,7 +47613,7 @@
         <v>44507</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>46182</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47759,7 +47759,7 @@
         <v>45618</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>45275</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>46184</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>46189</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>44936</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         <v>45538</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>46188</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45302</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>45300</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45412</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48499,7 +48499,7 @@
         <v>45182</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48572,7 +48572,7 @@
         <v>45267</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45149</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44943</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45615</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45615</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>45523</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>46197</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>45281</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>46198</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>44944</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>44614</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>44729</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>44648</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45177</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>46201</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>46201</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49750,7 +49750,7 @@
         <v>46201</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>44938</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49901,7 +49901,7 @@
         <v>45588</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49974,7 +49974,7 @@
         <v>46203</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>44655</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50120,7 +50120,7 @@
         <v>46203</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>46206</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>46206</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>44839</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45092</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>46206</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50578,7 +50578,7 @@
         <v>44893</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50651,7 +50651,7 @@
         <v>45363</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>46211</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         <v>46211</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45314</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50943,7 +50943,7 @@
         <v>46212</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>46211</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51094,7 +51094,7 @@
         <v>46211</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>46211</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>46211</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51318,7 +51318,7 @@
         <v>46212</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>46211</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>46211</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>46211</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
         <v>46211</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51688,7 +51688,7 @@
         <v>46212</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51761,7 +51761,7 @@
         <v>44484</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>46211</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51912,7 +51912,7 @@
         <v>45226</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51985,7 +51985,7 @@
         <v>44589</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>44578</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45946</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52204,7 +52204,7 @@
         <v>45587</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52277,7 +52277,7 @@
         <v>44804</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52350,7 +52350,7 @@
         <v>45043</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52423,7 +52423,7 @@
         <v>45113</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>46219</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52569,7 +52569,7 @@
         <v>45842</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52642,7 +52642,7 @@
         <v>45701</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52715,7 +52715,7 @@
         <v>46220</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52788,7 +52788,7 @@
         <v>45644</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52861,7 +52861,7 @@
         <v>46262</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>46219</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>44608</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>44734</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53158,7 +53158,7 @@
         <v>44734</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53236,7 +53236,7 @@
         <v>44904</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>46265</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53382,7 +53382,7 @@
         <v>45197</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53455,7 +53455,7 @@
         <v>45321</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53528,7 +53528,7 @@
         <v>45043</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53601,7 +53601,7 @@
         <v>46267</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53674,7 +53674,7 @@
         <v>46268</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>46230</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>46230</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53903,7 +53903,7 @@
         <v>46272</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>46273</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54049,7 +54049,7 @@
         <v>46270</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45545</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54200,7 +54200,7 @@
         <v>46272</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54273,7 +54273,7 @@
         <v>46272</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>46272</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>46272</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54492,7 +54492,7 @@
         <v>44711</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45477</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54638,7 +54638,7 @@
         <v>45477</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54711,7 +54711,7 @@
         <v>45299</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54784,7 +54784,7 @@
         <v>44998</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54857,7 +54857,7 @@
         <v>45175</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>46274</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55003,7 +55003,7 @@
         <v>45118</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55076,7 +55076,7 @@
         <v>46233</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>46234</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55227,7 +55227,7 @@
         <v>46279</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55305,7 +55305,7 @@
         <v>46279</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55383,7 +55383,7 @@
         <v>46234</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55456,7 +55456,7 @@
         <v>46234</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>46234</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>46279</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55680,7 +55680,7 @@
         <v>46233</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>46276</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55831,7 +55831,7 @@
         <v>46276</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55904,7 +55904,7 @@
         <v>46238</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55977,7 +55977,7 @@
         <v>44591</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>45708</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45211</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>45112</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>45375</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>46282</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56415,7 +56415,7 @@
         <v>45541</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>44853</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45492</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>46239</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>46267</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>45562</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56853,7 +56853,7 @@
         <v>45477</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56926,7 +56926,7 @@
         <v>45477</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45359</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57072,7 +57072,7 @@
         <v>46239</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>46281</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57218,7 +57218,7 @@
         <v>46279</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57296,7 +57296,7 @@
         <v>45243</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>45184</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57447,7 +57447,7 @@
         <v>46244</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57520,7 +57520,7 @@
         <v>46286</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57598,7 +57598,7 @@
         <v>46286</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57671,7 +57671,7 @@
         <v>46286</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57744,7 +57744,7 @@
         <v>46286</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>44950</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57890,7 +57890,7 @@
         <v>44950</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57963,7 +57963,7 @@
         <v>46244</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58036,7 +58036,7 @@
         <v>46286</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>46244</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>46286</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>44930</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58333,7 +58333,7 @@
         <v>45531</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58406,7 +58406,7 @@
         <v>45757</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58479,7 +58479,7 @@
         <v>45462</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>45201</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58625,7 +58625,7 @@
         <v>45201</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58698,7 +58698,7 @@
         <v>44719</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58771,7 +58771,7 @@
         <v>45335</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58849,7 +58849,7 @@
         <v>45092</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45099</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58995,7 +58995,7 @@
         <v>46246</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59068,7 +59068,7 @@
         <v>46279</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>46246</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59219,7 +59219,7 @@
         <v>46246</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>44943</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59365,7 +59365,7 @@
         <v>45201</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59443,7 +59443,7 @@
         <v>44985</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         <v>46290</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59594,7 +59594,7 @@
         <v>45245</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59667,7 +59667,7 @@
         <v>45107</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59740,7 +59740,7 @@
         <v>46248</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59813,7 +59813,7 @@
         <v>45314</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59886,7 +59886,7 @@
         <v>45295</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59964,7 +59964,7 @@
         <v>46290</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60042,7 +60042,7 @@
         <v>46293</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>46290</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60198,7 +60198,7 @@
         <v>46290</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60276,7 +60276,7 @@
         <v>45534</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60349,7 +60349,7 @@
         <v>46247</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60422,7 +60422,7 @@
         <v>45617</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
         <v>44564</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60568,7 +60568,7 @@
         <v>45377</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60641,7 +60641,7 @@
         <v>45219</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60714,7 +60714,7 @@
         <v>46293</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         <v>45363</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60860,7 +60860,7 @@
         <v>45240</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60933,7 +60933,7 @@
         <v>44966</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61011,7 +61011,7 @@
         <v>45194</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61084,7 +61084,7 @@
         <v>45194</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61157,7 +61157,7 @@
         <v>45112</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45107</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61303,7 +61303,7 @@
         <v>46294</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61376,7 +61376,7 @@
         <v>45015</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61449,7 +61449,7 @@
         <v>46294</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61522,7 +61522,7 @@
         <v>44904</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61595,7 +61595,7 @@
         <v>45049</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61668,7 +61668,7 @@
         <v>45338</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61746,7 +61746,7 @@
         <v>46252</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61819,7 +61819,7 @@
         <v>46294</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61892,7 +61892,7 @@
         <v>46295</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61970,7 +61970,7 @@
         <v>46248</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62043,7 +62043,7 @@
         <v>44894</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62116,7 +62116,7 @@
         <v>44893</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62194,7 +62194,7 @@
         <v>44605</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62267,7 +62267,7 @@
         <v>46255</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62340,7 +62340,7 @@
         <v>46295</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62413,7 +62413,7 @@
         <v>45197</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62491,7 +62491,7 @@
         <v>45406</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62564,7 +62564,7 @@
         <v>44985</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62637,7 +62637,7 @@
         <v>45051</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62710,7 +62710,7 @@
         <v>44484</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45706</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62861,7 +62861,7 @@
         <v>45671</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62934,7 +62934,7 @@
         <v>45705</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63007,7 +63007,7 @@
         <v>46244</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63080,7 +63080,7 @@
         <v>45740</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63153,7 +63153,7 @@
         <v>45693</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63226,7 +63226,7 @@
         <v>45009</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63299,7 +63299,7 @@
         <v>45127</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63372,7 +63372,7 @@
         <v>44677</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63445,7 +63445,7 @@
         <v>45756</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63518,7 +63518,7 @@
         <v>45324</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63596,7 +63596,7 @@
         <v>45324</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63674,7 +63674,7 @@
         <v>45671</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63747,7 +63747,7 @@
         <v>45414</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63820,7 +63820,7 @@
         <v>45761</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63893,7 +63893,7 @@
         <v>44741</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63966,7 +63966,7 @@
         <v>45223</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64039,7 +64039,7 @@
         <v>45541</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64112,7 +64112,7 @@
         <v>45435</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64190,7 +64190,7 @@
         <v>44967</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64263,7 +64263,7 @@
         <v>44734</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64341,7 +64341,7 @@
         <v>45747</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64414,7 +64414,7 @@
         <v>45533</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64487,7 +64487,7 @@
         <v>45706</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64565,7 +64565,7 @@
         <v>45635</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64638,7 +64638,7 @@
         <v>45541</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64711,7 +64711,7 @@
         <v>45201</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64784,7 +64784,7 @@
         <v>45341</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64857,7 +64857,7 @@
         <v>44950</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64930,7 +64930,7 @@
         <v>45099</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65003,7 +65003,7 @@
         <v>45681</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65076,7 +65076,7 @@
         <v>45715</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65149,7 +65149,7 @@
         <v>44627</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65222,7 +65222,7 @@
         <v>45056</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65295,7 +65295,7 @@
         <v>45355</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65368,7 +65368,7 @@
         <v>44966</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65446,7 +65446,7 @@
         <v>44588</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65519,7 +65519,7 @@
         <v>44488</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65592,7 +65592,7 @@
         <v>45197</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65665,7 +65665,7 @@
         <v>45547</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65743,7 +65743,7 @@
         <v>45569</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65816,7 +65816,7 @@
         <v>44897</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65894,7 +65894,7 @@
         <v>45764</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65967,7 +65967,7 @@
         <v>45198</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66040,7 +66040,7 @@
         <v>45056</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66113,7 +66113,7 @@
         <v>45406</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66186,7 +66186,7 @@
         <v>45406</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>45440</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66332,7 +66332,7 @@
         <v>45216</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66405,7 +66405,7 @@
         <v>45667</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66478,7 +66478,7 @@
         <v>45519</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66551,7 +66551,7 @@
         <v>45586</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>45313</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66702,7 +66702,7 @@
         <v>44658</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66775,7 +66775,7 @@
         <v>44607</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66848,7 +66848,7 @@
         <v>45131</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66926,7 +66926,7 @@
         <v>44593</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66999,7 +66999,7 @@
         <v>44510</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67072,7 +67072,7 @@
         <v>44956</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67150,7 +67150,7 @@
         <v>45407</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67228,7 +67228,7 @@
         <v>45327</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67301,7 +67301,7 @@
         <v>44711</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67374,7 +67374,7 @@
         <v>44753</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67447,7 +67447,7 @@
         <v>44998</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67520,7 +67520,7 @@
         <v>45794</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67593,7 +67593,7 @@
         <v>45798</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67666,7 +67666,7 @@
         <v>45712</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67759,7 +67759,7 @@
         <v>45798</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67832,7 +67832,7 @@
         <v>45712</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67905,7 +67905,7 @@
         <v>45817</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67983,7 +67983,7 @@
         <v>45870</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68056,7 +68056,7 @@
         <v>45994</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68129,7 +68129,7 @@
         <v>46047</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45856</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45936</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46043</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45111</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44607</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46225</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>45609</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>45348</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>46055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45302</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46288</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44607</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45510</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>44970</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45268</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44963</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>46280</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>45930</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>45788</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>46198</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44512</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45747</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44602</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45604</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46176</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>46055</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46133</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>44536</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>44530</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>46107</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45898</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45777</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>44974</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45783</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45772</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44747</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>44607</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>46092</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45580</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>45790</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45539</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>45331</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45679</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>46048</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>46049</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>45446</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>45947</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>45373</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44943</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>45603</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>45538</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>46174</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>45302</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>46196</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>46230</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>46286</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>44991</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>45758</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>45982</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45358</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>43983</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>45013</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44647</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45393</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45790</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44613</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44711</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44579</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45477</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44750</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45177</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45436</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45295</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44840</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>46013</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>46035</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>45720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>45272</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>46048</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>45205</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45740</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>45587</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>46055</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>46059</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>45926</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>46106</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45338</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45841</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45842</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45616</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45205</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45764</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>45846</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45184</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>46162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>46162</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>44557</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>45730</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>44963</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
         <v>46203</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>46212</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>46211</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45751</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44992</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44879</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>46286</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>46279</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45343</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>46294</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>44893</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>46252</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>45558</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>45600</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45617</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45201</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>44540</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>44955</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>45029</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>44711</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44628</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>45712</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45712</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45846</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>44496</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44487</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>44575</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>44662</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>44749</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>44749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>44792</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44487</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44487</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44749</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>44881</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>44665</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>44792</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44538</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>44487</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44487</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>44852</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>44498</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>44881</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>44673</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44754</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>44855</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>44476</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>44511</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>44840</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>44537</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44476</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44575</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>44659</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>44659</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>44578</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>44474</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44711</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44579</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44557</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>44616</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>44575</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>44575</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>44819</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>44819</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>44523</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>44846</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>44605</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44711</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>44841</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>44792</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>44830</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>44787</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44825</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>44614</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>44585</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>44711</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44488</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44498</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44532</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>44593</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>44729</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>44805</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>44811</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>44853</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>45435</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45114</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45764</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>44711</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45617</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45469</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>45272</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45747</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45404</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>45697</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>45169</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45012</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>45048</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>45605</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45152</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>44589</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45145</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45111</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>44628</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>45012</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45092</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45726</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45307</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>45405</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21413,7 +21413,7 @@
         <v>45405</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>45621</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>46000</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44943</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>44998</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>45621</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>45621</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>45295</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45392</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>45887</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45456</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45645</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45541</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45757</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>46009</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>46008</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>45551</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>46013</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
         <v>45958</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
         <v>46013</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44938</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>46010</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>46009</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>46013</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>46009</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>46009</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>46013</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>46013</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>44943</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>46009</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>46013</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45350</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>45646</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45253</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45184</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>46026</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45892</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>46026</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45892</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45892</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>46029</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45895</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>46031</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>46030</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>46031</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45898</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45116</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>46035</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>45545</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>45902</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>44949</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>46035</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>45905</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>46041</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>44482</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44662</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44904</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45908</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45908</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>46038</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>46041</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45908</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45908</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>46043</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>44904</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>44897</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44904</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>46043</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>46059</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>46041</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>45693</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>44861</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44861</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45570</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>46044</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45406</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>46048</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>44735</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>46048</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>46049</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>46048</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>46049</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>46048</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45740</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46048</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45902</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>46048</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45735</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45734</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>44992</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>44882</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>46050</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>45917</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45805</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45806</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>46055</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>45183</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>46055</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>46055</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>46055</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>45373</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>45925</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>44571</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>45539</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>44592</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45547</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>46059</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>46059</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>46059</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>46059</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>45597</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>46059</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>46059</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>46059</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>46059</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>45811</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45455</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>46062</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>46062</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45182</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>46062</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>46063</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>46045</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>46069</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30540,7 +30540,7 @@
         <v>46069</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>46069</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45461</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44622</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>44893</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>45037</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45934</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>45600</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>45600</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>45701</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>46070</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45726</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>45215</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>46070</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>46070</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>46073</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>45468</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45371</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45945</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>45682</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>44977</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>45946</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>45946</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>45617</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>46079</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>44585</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45152</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45351</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>46087</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45958</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>44846</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>45958</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45958</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>45643</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>45502</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>46091</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>44904</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>45965</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>45966</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33402,7 +33402,7 @@
         <v>45189</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45966</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45966</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45966</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>44507</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>45561</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>45358</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45966</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45294</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45968</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45079</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>45974</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>45035</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45974</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>45974</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>45974</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>45974</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>44950</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>45975</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34819,7 +34819,7 @@
         <v>45240</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>46101</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44626</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>45974</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45974</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35194,7 +35194,7 @@
         <v>45974</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>45979</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45978</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45246</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>45058</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45819</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>45119</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>45566</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>45566</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>45502</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>44837</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>45210</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36080,7 +36080,7 @@
         <v>44614</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36153,7 +36153,7 @@
         <v>46119</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>46119</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>46120</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45021</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>46120</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>46120</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>44963</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>45988</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36737,7 +36737,7 @@
         <v>46119</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>44935</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36883,7 +36883,7 @@
         <v>44867</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45180</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>44904</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>44575</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37175,7 +37175,7 @@
         <v>45995</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37248,7 +37248,7 @@
         <v>45826</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>45260</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45008</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37467,7 +37467,7 @@
         <v>45105</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37540,7 +37540,7 @@
         <v>45474</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37613,7 +37613,7 @@
         <v>45124</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37686,7 +37686,7 @@
         <v>45759</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>45051</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>44487</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>45316</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>44631</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45552</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45810</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>44483</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>45169</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>45679</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>45756</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44923</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>45834</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45842</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>45558</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>45797</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45587</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>46002</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45764</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>45846</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45846</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45300</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45751</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>45681</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>45758</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>44659</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39614,7 +39614,7 @@
         <v>45730</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>45841</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45455</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>45846</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>44889</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39989,7 +39989,7 @@
         <v>44853</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40062,7 +40062,7 @@
         <v>45401</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>44988</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>45471</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45198</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45947</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>45630</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>45701</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>45364</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>45188</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>45356</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40802,7 +40802,7 @@
         <v>45764</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>45181</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>44882</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41021,7 +41021,7 @@
         <v>45788</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>44965</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41167,7 +41167,7 @@
         <v>45861</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45749</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41313,7 +41313,7 @@
         <v>44648</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41386,7 +41386,7 @@
         <v>45734</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>45194</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45763</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>44943</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>44943</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45587</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>45875</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45642</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41970,7 +41970,7 @@
         <v>45775</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>45734</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>45043</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45788</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>45870</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42340,7 +42340,7 @@
         <v>45392</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>45271</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42486,7 +42486,7 @@
         <v>45215</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>44803</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>45673</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>44957</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42778,7 +42778,7 @@
         <v>45460</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>45030</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>44977</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45034</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43070,7 +43070,7 @@
         <v>45470</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>45875</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>45349</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43294,7 +43294,7 @@
         <v>45734</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>45182</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>45763</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45646</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43586,7 +43586,7 @@
         <v>45169</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>45169</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
         <v>46162</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43810,7 +43810,7 @@
         <v>44704</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43883,7 +43883,7 @@
         <v>45401</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43961,7 +43961,7 @@
         <v>46162</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>45414</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>46162</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>46162</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>46162</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>46162</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>45758</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>46167</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>46167</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>46168</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45880</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>46168</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44877,7 +44877,7 @@
         <v>45198</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44950,7 +44950,7 @@
         <v>45198</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45023,7 +45023,7 @@
         <v>46168</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45096,7 +45096,7 @@
         <v>44886</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>44658</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>45303</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45320,7 +45320,7 @@
         <v>46170</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>45580</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>44550</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>46170</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45455</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>46170</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45763,7 +45763,7 @@
         <v>46170</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>45130</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45477</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>45547</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46060,7 +46060,7 @@
         <v>45112</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>45112</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46206,7 +46206,7 @@
         <v>46174</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46284,7 +46284,7 @@
         <v>45174</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>44628</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>46174</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>46174</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46586,7 +46586,7 @@
         <v>45557</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46659,7 +46659,7 @@
         <v>45883</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>45883</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45883</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>44614</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45883</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>45462</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>44861</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>45929</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45887</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45887</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>45324</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>45270</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47540,7 +47540,7 @@
         <v>45179</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47613,7 +47613,7 @@
         <v>44507</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>46182</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47759,7 +47759,7 @@
         <v>45618</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>45275</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>46184</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>46189</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>44936</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         <v>45538</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>46188</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45302</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>45300</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45412</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48499,7 +48499,7 @@
         <v>45182</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48572,7 +48572,7 @@
         <v>45267</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48645,7 +48645,7 @@
         <v>45149</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44943</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45615</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45615</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>45523</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>46197</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>45281</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>46198</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>44944</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>44614</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>44729</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>44648</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45177</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>46201</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>46201</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49750,7 +49750,7 @@
         <v>46201</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>44938</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49901,7 +49901,7 @@
         <v>45588</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49974,7 +49974,7 @@
         <v>46203</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>44655</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50120,7 +50120,7 @@
         <v>46203</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>46206</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50271,7 +50271,7 @@
         <v>46206</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>44839</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45092</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>46206</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50578,7 +50578,7 @@
         <v>44893</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50651,7 +50651,7 @@
         <v>45363</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>46211</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         <v>46211</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45314</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50943,7 +50943,7 @@
         <v>46212</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>46211</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51094,7 +51094,7 @@
         <v>46211</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>46211</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>46211</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51318,7 +51318,7 @@
         <v>46212</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>46211</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>46211</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>46211</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
         <v>46211</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51688,7 +51688,7 @@
         <v>46212</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51761,7 +51761,7 @@
         <v>44484</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>46211</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51912,7 +51912,7 @@
         <v>45226</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51985,7 +51985,7 @@
         <v>44589</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>44578</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45946</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52204,7 +52204,7 @@
         <v>45587</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52277,7 +52277,7 @@
         <v>44804</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52350,7 +52350,7 @@
         <v>45043</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52423,7 +52423,7 @@
         <v>45113</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>46219</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52569,7 +52569,7 @@
         <v>45842</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52642,7 +52642,7 @@
         <v>45701</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52715,7 +52715,7 @@
         <v>46220</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52788,7 +52788,7 @@
         <v>45644</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52861,7 +52861,7 @@
         <v>46262</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>46219</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>44608</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>44734</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53158,7 +53158,7 @@
         <v>44734</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53236,7 +53236,7 @@
         <v>44904</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>46265</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53382,7 +53382,7 @@
         <v>45197</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53455,7 +53455,7 @@
         <v>45321</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53528,7 +53528,7 @@
         <v>45043</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53601,7 +53601,7 @@
         <v>46267</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53674,7 +53674,7 @@
         <v>46268</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>46230</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53825,7 +53825,7 @@
         <v>46230</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53903,7 +53903,7 @@
         <v>46272</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>46273</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54049,7 +54049,7 @@
         <v>46270</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45545</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54200,7 +54200,7 @@
         <v>46272</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54273,7 +54273,7 @@
         <v>46272</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>46272</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>46272</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54492,7 +54492,7 @@
         <v>44711</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45477</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54638,7 +54638,7 @@
         <v>45477</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54711,7 +54711,7 @@
         <v>45299</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54784,7 +54784,7 @@
         <v>44998</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54857,7 +54857,7 @@
         <v>45175</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>46274</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55003,7 +55003,7 @@
         <v>45118</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55076,7 +55076,7 @@
         <v>46233</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>46234</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55227,7 +55227,7 @@
         <v>46279</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55305,7 +55305,7 @@
         <v>46279</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55383,7 +55383,7 @@
         <v>46234</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55456,7 +55456,7 @@
         <v>46234</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>46234</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>46279</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55680,7 +55680,7 @@
         <v>46233</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>46276</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55831,7 +55831,7 @@
         <v>46276</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55904,7 +55904,7 @@
         <v>46238</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55977,7 +55977,7 @@
         <v>44591</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>45708</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45211</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>45112</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>45375</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>46282</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56415,7 +56415,7 @@
         <v>45541</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>44853</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45492</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>46239</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>46267</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>45562</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56853,7 +56853,7 @@
         <v>45477</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56926,7 +56926,7 @@
         <v>45477</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45359</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57072,7 +57072,7 @@
         <v>46239</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>46281</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57218,7 +57218,7 @@
         <v>46279</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57296,7 +57296,7 @@
         <v>45243</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>45184</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57447,7 +57447,7 @@
         <v>46244</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57520,7 +57520,7 @@
         <v>46286</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57598,7 +57598,7 @@
         <v>46286</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57671,7 +57671,7 @@
         <v>46286</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57744,7 +57744,7 @@
         <v>46286</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>44950</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57890,7 +57890,7 @@
         <v>44950</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57963,7 +57963,7 @@
         <v>46244</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58036,7 +58036,7 @@
         <v>46286</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>46244</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>46286</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>44930</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58333,7 +58333,7 @@
         <v>45531</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58406,7 +58406,7 @@
         <v>45757</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58479,7 +58479,7 @@
         <v>45462</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>45201</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58625,7 +58625,7 @@
         <v>45201</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58698,7 +58698,7 @@
         <v>44719</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58771,7 +58771,7 @@
         <v>45335</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58849,7 +58849,7 @@
         <v>45092</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45099</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58995,7 +58995,7 @@
         <v>46246</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59068,7 +59068,7 @@
         <v>46279</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>46246</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59219,7 +59219,7 @@
         <v>46246</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>44943</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59365,7 +59365,7 @@
         <v>45201</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59443,7 +59443,7 @@
         <v>44985</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         <v>46290</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59594,7 +59594,7 @@
         <v>45245</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59667,7 +59667,7 @@
         <v>45107</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59740,7 +59740,7 @@
         <v>46248</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59813,7 +59813,7 @@
         <v>45314</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59886,7 +59886,7 @@
         <v>45295</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59964,7 +59964,7 @@
         <v>46290</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60042,7 +60042,7 @@
         <v>46293</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>46290</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60198,7 +60198,7 @@
         <v>46290</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60276,7 +60276,7 @@
         <v>45534</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60349,7 +60349,7 @@
         <v>46247</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60422,7 +60422,7 @@
         <v>45617</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
         <v>44564</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60568,7 +60568,7 @@
         <v>45377</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60641,7 +60641,7 @@
         <v>45219</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60714,7 +60714,7 @@
         <v>46293</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         <v>45363</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60860,7 +60860,7 @@
         <v>45240</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60933,7 +60933,7 @@
         <v>44966</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61011,7 +61011,7 @@
         <v>45194</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61084,7 +61084,7 @@
         <v>45194</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61157,7 +61157,7 @@
         <v>45112</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61230,7 +61230,7 @@
         <v>45107</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61303,7 +61303,7 @@
         <v>46294</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61376,7 +61376,7 @@
         <v>45015</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61449,7 +61449,7 @@
         <v>46294</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61522,7 +61522,7 @@
         <v>44904</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61595,7 +61595,7 @@
         <v>45049</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61668,7 +61668,7 @@
         <v>45338</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61746,7 +61746,7 @@
         <v>46252</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61819,7 +61819,7 @@
         <v>46294</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61892,7 +61892,7 @@
         <v>46295</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61970,7 +61970,7 @@
         <v>46248</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62043,7 +62043,7 @@
         <v>44894</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62116,7 +62116,7 @@
         <v>44893</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62194,7 +62194,7 @@
         <v>44605</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62267,7 +62267,7 @@
         <v>46255</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62340,7 +62340,7 @@
         <v>46295</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62413,7 +62413,7 @@
         <v>45197</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62491,7 +62491,7 @@
         <v>45406</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62564,7 +62564,7 @@
         <v>44985</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62637,7 +62637,7 @@
         <v>45051</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62710,7 +62710,7 @@
         <v>44484</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45706</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62861,7 +62861,7 @@
         <v>45671</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62934,7 +62934,7 @@
         <v>45705</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63007,7 +63007,7 @@
         <v>46244</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63080,7 +63080,7 @@
         <v>45740</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63153,7 +63153,7 @@
         <v>45693</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63226,7 +63226,7 @@
         <v>45009</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63299,7 +63299,7 @@
         <v>45127</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63372,7 +63372,7 @@
         <v>44677</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63445,7 +63445,7 @@
         <v>45756</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63518,7 +63518,7 @@
         <v>45324</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63596,7 +63596,7 @@
         <v>45324</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63674,7 +63674,7 @@
         <v>45671</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63747,7 +63747,7 @@
         <v>45414</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63820,7 +63820,7 @@
         <v>45761</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63893,7 +63893,7 @@
         <v>44741</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63966,7 +63966,7 @@
         <v>45223</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64039,7 +64039,7 @@
         <v>45541</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64112,7 +64112,7 @@
         <v>45435</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64190,7 +64190,7 @@
         <v>44967</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64263,7 +64263,7 @@
         <v>44734</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64341,7 +64341,7 @@
         <v>45747</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64414,7 +64414,7 @@
         <v>45533</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64487,7 +64487,7 @@
         <v>45706</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64565,7 +64565,7 @@
         <v>45635</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64638,7 +64638,7 @@
         <v>45541</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64711,7 +64711,7 @@
         <v>45201</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64784,7 +64784,7 @@
         <v>45341</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64857,7 +64857,7 @@
         <v>44950</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64930,7 +64930,7 @@
         <v>45099</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65003,7 +65003,7 @@
         <v>45681</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65076,7 +65076,7 @@
         <v>45715</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65149,7 +65149,7 @@
         <v>44627</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65222,7 +65222,7 @@
         <v>45056</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65295,7 +65295,7 @@
         <v>45355</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65368,7 +65368,7 @@
         <v>44966</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65446,7 +65446,7 @@
         <v>44588</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65519,7 +65519,7 @@
         <v>44488</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65592,7 +65592,7 @@
         <v>45197</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65665,7 +65665,7 @@
         <v>45547</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65743,7 +65743,7 @@
         <v>45569</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65816,7 +65816,7 @@
         <v>44897</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65894,7 +65894,7 @@
         <v>45764</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65967,7 +65967,7 @@
         <v>45198</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66040,7 +66040,7 @@
         <v>45056</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66113,7 +66113,7 @@
         <v>45406</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66186,7 +66186,7 @@
         <v>45406</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>45440</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66332,7 +66332,7 @@
         <v>45216</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66405,7 +66405,7 @@
         <v>45667</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66478,7 +66478,7 @@
         <v>45519</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66551,7 +66551,7 @@
         <v>45586</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>45313</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66702,7 +66702,7 @@
         <v>44658</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66775,7 +66775,7 @@
         <v>44607</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66848,7 +66848,7 @@
         <v>45131</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66926,7 +66926,7 @@
         <v>44593</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66999,7 +66999,7 @@
         <v>44510</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67072,7 +67072,7 @@
         <v>44956</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67150,7 +67150,7 @@
         <v>45407</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67228,7 +67228,7 @@
         <v>45327</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67301,7 +67301,7 @@
         <v>44711</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67374,7 +67374,7 @@
         <v>44753</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67447,7 +67447,7 @@
         <v>44998</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67520,7 +67520,7 @@
         <v>45794</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67593,7 +67593,7 @@
         <v>45798</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67666,7 +67666,7 @@
         <v>45712</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67759,7 +67759,7 @@
         <v>45798</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67832,7 +67832,7 @@
         <v>45712</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67905,7 +67905,7 @@
         <v>45817</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -67983,7 +67983,7 @@
         <v>45870</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68056,7 +68056,7 @@
         <v>45994</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68129,7 +68129,7 @@
         <v>46047</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45856</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45936</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46043</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>44607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46225</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>45609</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>45348</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>46055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45302</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45698</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46288</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44607</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45510</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>44970</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45268</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44963</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>46280</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>44992</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44512</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>45788</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>45930</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>46198</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45747</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44602</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45604</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46176</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>46055</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46133</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>44536</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>44530</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44974</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>45898</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>45777</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45783</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>46107</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44607</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>45629</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44747</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>46092</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>45373</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>45446</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45539</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>45331</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44979</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45790</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>45358</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45679</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>45580</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>45947</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>45758</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>45603</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>45538</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>44991</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45302</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>44943</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>46048</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>46049</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>46174</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>46196</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>46230</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>46286</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45982</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>43983</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44647</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>45013</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45393</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45790</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44613</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44579</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44711</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45338</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>45764</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>45751</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>45558</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44893</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>45436</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>45477</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45617</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>45730</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44840</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>45720</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>44557</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45177</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>45600</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>45926</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45740</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>45587</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45201</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45295</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45343</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44750</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>45842</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45841</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>45616</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45272</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45205</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45846</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>44540</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44879</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>46106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45184</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>46013</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44963</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>44992</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>46048</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>46055</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>46059</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>46162</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>46162</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>46203</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>46211</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>46212</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>46286</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>46279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>46294</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>46252</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>46302</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>44711</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>44628</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>44955</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>45029</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>45712</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45712</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45846</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>44496</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44487</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>44575</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>44662</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>44749</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>44749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>44792</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44487</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44487</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44749</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>44881</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>44665</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>44792</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44487</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>44487</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44538</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>44852</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>44498</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>44881</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>44673</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44855</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>44754</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>44511</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>44840</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>44537</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>44575</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44792</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44830</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>44787</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44575</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>44488</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44711</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>44825</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44614</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44659</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44659</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>44578</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>44585</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>44575</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44819</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>44819</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>44498</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>44846</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>44605</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44523</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>44711</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>44711</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>44579</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44557</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44616</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>44841</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>44532</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44593</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44729</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44805</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44811</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45531</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45406</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>44998</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45673</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45324</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45324</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>44904</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45092</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45152</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>44804</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>45401</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45373</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>45037</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>45621</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45621</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45079</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45127</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45008</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>44967</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>45605</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>44882</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>45764</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>45355</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45341</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45152</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45324</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>45092</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45757</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45615</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45740</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45197</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>44631</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45183</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45056</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>45697</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>45757</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45201</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45240</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45642</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45321</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45107</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45299</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>44483</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>45270</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45474</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45092</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>45012</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>45049</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>45051</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>45300</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>45588</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>44893</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>44985</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23263,7 +23263,7 @@
         <v>45111</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>45112</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44950</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>44950</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>45243</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45099</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45114</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45363</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45349</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45119</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44837</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45477</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45177</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45223</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45181</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45314</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45455</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45455</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>44963</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45116</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>44487</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>45356</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45587</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>44957</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>45118</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>45359</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>45107</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>44588</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45338</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>45562</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45533</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45539</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>45201</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45462</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45545</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45169</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>45468</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45883</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45883</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45502</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>45502</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44853</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45883</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45883</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>44904</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>44904</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>44923</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>45414</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45887</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>45377</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45358</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44484</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>45351</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45145</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>44488</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>45281</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44966</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>45275</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>44936</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45887</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44628</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>45219</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>45887</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45477</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>44853</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>45335</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45541</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45406</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45169</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44935</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>44507</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45892</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45892</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45892</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45895</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45898</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>45012</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44482</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45492</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>45566</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>45557</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>45635</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>45295</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>45734</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>45902</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>45615</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29601,7 +29601,7 @@
         <v>45758</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>45618</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>45414</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>44944</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44589</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>45764</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>44893</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>45545</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45307</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>45538</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>45099</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45905</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>45124</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>45646</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44648</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45908</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45908</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>45908</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45908</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45667</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45267</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45693</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>45747</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45460</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>44550</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44605</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>45586</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>44589</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45519</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45175</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>44904</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>45902</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>44943</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>45216</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>45917</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>45405</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>45405</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>45184</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45009</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45547</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>44578</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>44592</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45541</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45412</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>45552</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>45462</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44585</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45763</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45401</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>45646</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>45566</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>45105</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>45645</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>45551</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>45541</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>45925</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>45184</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>45194</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45197</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33933,7 +33933,7 @@
         <v>45350</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>45021</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>44950</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>45043</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>45681</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34298,7 +34298,7 @@
         <v>45570</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34371,7 +34371,7 @@
         <v>44591</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34444,7 +34444,7 @@
         <v>44938</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>44608</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>45169</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44977</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34741,7 +34741,7 @@
         <v>44626</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45740</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>45735</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>44943</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>44943</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>45734</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>45934</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>45112</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45112</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45435</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>44930</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>45030</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>44575</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45371</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45617</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>45056</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44950</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>44564</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>45174</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45363</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>45364</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>45726</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>44571</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>44966</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44992</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>45179</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>45182</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45806</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>44988</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45805</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45600</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45600</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45597</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45182</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>44711</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44998</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>45440</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45945</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45547</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>44614</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37676,7 +37676,7 @@
         <v>45946</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>44894</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>45946</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>45763</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45295</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44839</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45643</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>45561</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>44659</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45705</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>45671</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45617</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>45113</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45435</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45819</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>45316</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45826</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45456</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45215</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>45404</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45523</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>44965</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>45392</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>44704</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45198</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45706</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>44734</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>45198</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45671</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39823,7 +39823,7 @@
         <v>45958</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45958</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>45958</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45015</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>44655</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45211</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>44734</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40339,7 +40339,7 @@
         <v>44734</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45194</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40490,7 +40490,7 @@
         <v>45681</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40563,7 +40563,7 @@
         <v>45966</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>45966</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>45966</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40782,7 +40782,7 @@
         <v>45644</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>45965</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>45966</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45966</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45210</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>45756</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45169</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>45968</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45197</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>45617</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45842</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>44614</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>45846</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>45846</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45756</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45797</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>45587</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>45759</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>45314</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>45303</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42257,7 +42257,7 @@
         <v>45693</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>44729</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45974</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>45974</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45974</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>45245</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42710,7 +42710,7 @@
         <v>45189</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45469</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>45294</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45974</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>44904</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43090,7 +43090,7 @@
         <v>44897</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>44904</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>45246</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45974</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45974</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45974</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>45761</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>45974</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>45679</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45149</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>45975</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>45201</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>45751</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>45726</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45630</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>44719</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>45701</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45788</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45035</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45226</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44595,7 +44595,7 @@
         <v>45861</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>45188</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>44803</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44814,7 +44814,7 @@
         <v>44882</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>45240</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>45978</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>45621</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45182</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45870</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45788</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45708</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45715</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>44627</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>44985</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45734</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45695,7 +45695,7 @@
         <v>45979</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>45875</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45682</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45919,7 +45919,7 @@
         <v>45880</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>44889</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>45198</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45198</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45747</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46284,7 +46284,7 @@
         <v>45201</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>45272</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>45534</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45260</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>44886</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>46101</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>45253</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>45300</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45215</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>45392</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45043</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>44867</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         <v>44741</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>45477</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45477</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>44904</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45988</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>45112</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45749</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45587</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45302</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47817,7 +47817,7 @@
         <v>46119</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47890,7 +47890,7 @@
         <v>46119</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>46119</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48036,7 +48036,7 @@
         <v>46120</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>46120</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>46120</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>44893</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48328,7 +48328,7 @@
         <v>45406</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45406</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45995</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>44853</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48620,7 +48620,7 @@
         <v>44484</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>44949</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48766,7 +48766,7 @@
         <v>44648</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48839,7 +48839,7 @@
         <v>46000</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48912,7 +48912,7 @@
         <v>44861</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>44938</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49063,7 +49063,7 @@
         <v>45375</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>45180</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49209,7 +49209,7 @@
         <v>44943</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
         <v>44614</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44711</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49428,7 +49428,7 @@
         <v>44622</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>45947</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45058</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         <v>45758</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>44662</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>46009</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49876,7 +49876,7 @@
         <v>46009</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>46009</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50032,7 +50032,7 @@
         <v>46009</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50110,7 +50110,7 @@
         <v>46010</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45558</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45271</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>46008</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50412,7 +50412,7 @@
         <v>46009</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50490,7 +50490,7 @@
         <v>44861</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50563,7 +50563,7 @@
         <v>44861</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45958</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50709,7 +50709,7 @@
         <v>46013</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50782,7 +50782,7 @@
         <v>46013</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50855,7 +50855,7 @@
         <v>46013</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50928,7 +50928,7 @@
         <v>46013</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>46013</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>46013</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51147,7 +51147,7 @@
         <v>45461</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51220,7 +51220,7 @@
         <v>45541</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45846</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51366,7 +51366,7 @@
         <v>45730</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45043</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>46026</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51590,7 +51590,7 @@
         <v>46026</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>44897</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51741,7 +51741,7 @@
         <v>45455</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>44507</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>45569</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51965,7 +51965,7 @@
         <v>44943</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>44943</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52111,7 +52111,7 @@
         <v>45580</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52184,7 +52184,7 @@
         <v>46030</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>46029</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52335,7 +52335,7 @@
         <v>45810</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>46031</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>46031</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>45477</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52627,7 +52627,7 @@
         <v>45841</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>45547</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45034</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45764</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>45834</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>44677</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53070,7 +53070,7 @@
         <v>46035</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>46035</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>46038</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>44658</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53367,7 +53367,7 @@
         <v>46041</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53440,7 +53440,7 @@
         <v>45048</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53513,7 +53513,7 @@
         <v>46041</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>46041</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53659,7 +53659,7 @@
         <v>46059</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>46043</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53805,7 +53805,7 @@
         <v>46043</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45875</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>45051</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54024,7 +54024,7 @@
         <v>46048</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54097,7 +54097,7 @@
         <v>46048</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>46048</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54243,7 +54243,7 @@
         <v>46048</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54321,7 +54321,7 @@
         <v>44735</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>44846</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54467,7 +54467,7 @@
         <v>45130</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>46048</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>46048</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>46002</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>45764</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54832,7 +54832,7 @@
         <v>46049</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>46050</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54978,7 +54978,7 @@
         <v>45471</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>44977</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55124,7 +55124,7 @@
         <v>46049</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>45734</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55270,7 +55270,7 @@
         <v>46055</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>46055</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55416,7 +55416,7 @@
         <v>46055</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55489,7 +55489,7 @@
         <v>46059</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55562,7 +55562,7 @@
         <v>46059</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55635,7 +55635,7 @@
         <v>46059</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>46059</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>46059</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55854,7 +55854,7 @@
         <v>46059</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55927,7 +55927,7 @@
         <v>46059</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>46062</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56073,7 +56073,7 @@
         <v>45775</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>46062</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         <v>46062</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56292,7 +56292,7 @@
         <v>46059</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56365,7 +56365,7 @@
         <v>46063</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56438,7 +56438,7 @@
         <v>46045</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>46069</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56584,7 +56584,7 @@
         <v>46069</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>46069</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56730,7 +56730,7 @@
         <v>46070</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56803,7 +56803,7 @@
         <v>46070</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56876,7 +56876,7 @@
         <v>46070</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56949,7 +56949,7 @@
         <v>46073</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57022,7 +57022,7 @@
         <v>46079</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>45470</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57168,7 +57168,7 @@
         <v>46087</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57241,7 +57241,7 @@
         <v>46091</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57314,7 +57314,7 @@
         <v>46162</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57392,7 +57392,7 @@
         <v>46162</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57470,7 +57470,7 @@
         <v>46162</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57548,7 +57548,7 @@
         <v>46162</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>46162</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57704,7 +57704,7 @@
         <v>46162</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57782,7 +57782,7 @@
         <v>46167</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57855,7 +57855,7 @@
         <v>46167</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>46168</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>46168</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58079,7 +58079,7 @@
         <v>46168</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58157,7 +58157,7 @@
         <v>46170</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58230,7 +58230,7 @@
         <v>46170</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>44628</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58376,7 +58376,7 @@
         <v>46170</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58449,7 +58449,7 @@
         <v>46170</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58522,7 +58522,7 @@
         <v>46174</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58600,7 +58600,7 @@
         <v>46174</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58678,7 +58678,7 @@
         <v>46174</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58756,7 +58756,7 @@
         <v>45929</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58829,7 +58829,7 @@
         <v>46182</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58902,7 +58902,7 @@
         <v>46184</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58980,7 +58980,7 @@
         <v>46189</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59053,7 +59053,7 @@
         <v>46188</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>46197</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59199,7 +59199,7 @@
         <v>46201</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59272,7 +59272,7 @@
         <v>46201</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         <v>46201</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59418,7 +59418,7 @@
         <v>46198</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59491,7 +59491,7 @@
         <v>46203</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59564,7 +59564,7 @@
         <v>46203</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59637,7 +59637,7 @@
         <v>46206</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59715,7 +59715,7 @@
         <v>46206</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59793,7 +59793,7 @@
         <v>46206</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59871,7 +59871,7 @@
         <v>46211</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59944,7 +59944,7 @@
         <v>46211</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60022,7 +60022,7 @@
         <v>46211</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60095,7 +60095,7 @@
         <v>46211</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60168,7 +60168,7 @@
         <v>46211</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60246,7 +60246,7 @@
         <v>46211</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60319,7 +60319,7 @@
         <v>46211</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60392,7 +60392,7 @@
         <v>46211</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60465,7 +60465,7 @@
         <v>46211</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60538,7 +60538,7 @@
         <v>46211</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>46211</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60684,7 +60684,7 @@
         <v>46212</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60757,7 +60757,7 @@
         <v>46212</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60835,7 +60835,7 @@
         <v>46212</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60913,7 +60913,7 @@
         <v>45946</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60986,7 +60986,7 @@
         <v>46219</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61059,7 +61059,7 @@
         <v>46219</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61132,7 +61132,7 @@
         <v>46262</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61205,7 +61205,7 @@
         <v>45842</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61278,7 +61278,7 @@
         <v>46220</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61351,7 +61351,7 @@
         <v>46265</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         <v>46267</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>46268</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>46270</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61643,7 +61643,7 @@
         <v>46272</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61716,7 +61716,7 @@
         <v>46272</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61789,7 +61789,7 @@
         <v>46272</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61862,7 +61862,7 @@
         <v>46272</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61935,7 +61935,7 @@
         <v>46272</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>46230</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62086,7 +62086,7 @@
         <v>46230</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>46273</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>46276</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>46276</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>46274</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>46234</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62529,7 +62529,7 @@
         <v>46279</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>46279</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62685,7 +62685,7 @@
         <v>46279</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62763,7 +62763,7 @@
         <v>46233</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62841,7 +62841,7 @@
         <v>46234</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62914,7 +62914,7 @@
         <v>46234</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>46233</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63065,7 +63065,7 @@
         <v>46234</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63138,7 +63138,7 @@
         <v>46267</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>46239</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63284,7 +63284,7 @@
         <v>46279</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63362,7 +63362,7 @@
         <v>46239</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63435,7 +63435,7 @@
         <v>46238</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63508,7 +63508,7 @@
         <v>46286</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63581,7 +63581,7 @@
         <v>46286</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63654,7 +63654,7 @@
         <v>46286</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63727,7 +63727,7 @@
         <v>46286</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63805,7 +63805,7 @@
         <v>46281</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63878,7 +63878,7 @@
         <v>46286</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63956,7 +63956,7 @@
         <v>46286</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64029,7 +64029,7 @@
         <v>46244</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64102,7 +64102,7 @@
         <v>46279</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64180,7 +64180,7 @@
         <v>46244</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64253,7 +64253,7 @@
         <v>46244</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64326,7 +64326,7 @@
         <v>46290</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64404,7 +64404,7 @@
         <v>46246</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>46246</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64550,7 +64550,7 @@
         <v>46246</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64623,7 +64623,7 @@
         <v>46290</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64701,7 +64701,7 @@
         <v>46290</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64779,7 +64779,7 @@
         <v>46247</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64852,7 +64852,7 @@
         <v>46290</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64930,7 +64930,7 @@
         <v>46293</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65003,7 +65003,7 @@
         <v>46248</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65076,7 +65076,7 @@
         <v>46294</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65149,7 +65149,7 @@
         <v>46293</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65227,7 +65227,7 @@
         <v>46294</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65300,7 +65300,7 @@
         <v>46295</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65373,7 +65373,7 @@
         <v>46294</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65446,7 +65446,7 @@
         <v>46252</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65519,7 +65519,7 @@
         <v>46295</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65597,7 +65597,7 @@
         <v>46244</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65670,7 +65670,7 @@
         <v>46255</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65743,7 +65743,7 @@
         <v>46302</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65816,7 +65816,7 @@
         <v>46248</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65889,7 +65889,7 @@
         <v>46301</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65962,7 +65962,7 @@
         <v>46302</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66035,7 +66035,7 @@
         <v>46302</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66108,7 +66108,7 @@
         <v>46303</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66181,7 +66181,7 @@
         <v>46282</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66254,7 +66254,7 @@
         <v>45701</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66327,7 +66327,7 @@
         <v>44658</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66400,7 +66400,7 @@
         <v>44607</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66473,7 +66473,7 @@
         <v>44593</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66546,7 +66546,7 @@
         <v>44711</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66619,7 +66619,7 @@
         <v>45313</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>45131</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66775,7 +66775,7 @@
         <v>44510</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66848,7 +66848,7 @@
         <v>44956</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66926,7 +66926,7 @@
         <v>45407</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67004,7 +67004,7 @@
         <v>45327</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67077,7 +67077,7 @@
         <v>44753</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67150,7 +67150,7 @@
         <v>44998</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67223,7 +67223,7 @@
         <v>45794</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67296,7 +67296,7 @@
         <v>45798</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67369,7 +67369,7 @@
         <v>45712</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67462,7 +67462,7 @@
         <v>45798</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67535,7 +67535,7 @@
         <v>45712</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67608,7 +67608,7 @@
         <v>45817</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67686,7 +67686,7 @@
         <v>45870</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67759,7 +67759,7 @@
         <v>45994</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67832,7 +67832,7 @@
         <v>46047</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67905,7 +67905,7 @@
         <v>46304</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45856</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45936</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46043</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>44607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46225</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>45609</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>45348</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>46055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45302</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45698</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46288</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44607</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45510</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>44970</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45268</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44963</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>46280</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>44992</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44512</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>45788</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>45930</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>46198</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45747</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44602</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45604</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46176</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>46055</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46133</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>44536</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>44530</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44974</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45772</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>45898</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>45777</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>45783</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>46107</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44607</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>45629</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44747</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>46092</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>45373</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>45446</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45539</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>45331</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44979</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45790</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>45358</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45679</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>45580</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>45947</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>45758</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>45603</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>45538</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>44991</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45302</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>44943</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>46048</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>46049</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>46174</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>46196</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>46230</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>46286</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45982</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>43983</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44647</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>45013</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45393</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45790</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44613</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44579</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44711</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45338</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>45764</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>45751</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>45558</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44893</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>45436</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>45477</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45617</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>45730</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44840</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>45720</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>44557</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45177</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>45600</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>45926</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45740</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>45587</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45201</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45295</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45343</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44750</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>45842</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45841</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>45616</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45272</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45205</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45846</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>44540</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44879</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>46106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45184</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>46013</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44963</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>44992</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>46048</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>46055</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>46059</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>46162</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>46162</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>46203</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>46211</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>46212</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>46286</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>46279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>46294</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>46252</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>46302</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>44711</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>44628</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>44955</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>45029</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>45712</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45712</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45846</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>44496</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44487</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>44575</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>44662</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>44749</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>44749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>44792</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44487</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44487</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44749</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>44881</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>44665</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>44792</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>44487</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>44487</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44538</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>44852</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>44498</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>44881</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>44673</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44855</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>44754</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>44511</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>44840</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>44537</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>44575</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44792</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44830</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>44787</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>44575</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>44488</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44711</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>44825</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44614</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44659</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44659</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>44578</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>44585</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>44575</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44819</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>44819</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>44498</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>44846</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>44605</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44523</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>44711</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>44711</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>44579</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44557</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44616</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>44841</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>44532</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44593</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44729</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44805</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44811</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45531</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45406</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>44998</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45673</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45324</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45324</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>44904</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45092</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45152</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>44804</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>45401</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45373</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>45037</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>45621</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45621</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45079</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45127</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45008</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>44967</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>45605</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>44882</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>45764</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>45355</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45341</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45152</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45324</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>45092</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45757</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45615</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45740</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>45197</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>44631</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45183</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45056</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>45697</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>45757</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45201</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45240</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45642</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45321</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45107</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45299</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>44483</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>45270</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45474</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45092</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>45012</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>45049</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>45051</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>45300</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>45588</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>44893</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>44985</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23263,7 +23263,7 @@
         <v>45111</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>45112</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44950</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>44950</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>45243</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45099</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45114</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45363</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45349</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45119</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>44837</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45477</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45177</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45223</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45181</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45314</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45455</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45455</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>44963</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45116</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>44487</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>45356</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45587</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>44957</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>45118</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>45359</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>45107</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>44588</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45338</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>45562</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45533</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45539</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>45201</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45462</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45545</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45169</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>45468</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45883</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45883</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45502</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>45502</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44853</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45883</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45883</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>44904</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>44904</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>44923</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>45414</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45887</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>45377</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45358</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44484</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>45351</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45145</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>44488</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>45281</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44966</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>45275</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>44936</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45887</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44628</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>45219</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>45887</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45477</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>44853</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>45335</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45541</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45406</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45169</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44935</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>44507</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45892</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45892</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45892</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>45895</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45898</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>45012</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44482</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45492</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>45566</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>45557</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>45635</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>45295</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>45734</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>45902</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>45615</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29601,7 +29601,7 @@
         <v>45758</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>45618</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>45414</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>44944</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44589</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>45764</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>44893</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>45545</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45307</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>45538</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>45099</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45905</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>45124</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>45646</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44648</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45908</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45908</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>45908</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45908</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45667</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45267</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45693</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>45747</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45460</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>44550</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>44605</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>45586</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>44589</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45519</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45175</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>44904</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>45902</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>44943</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>45216</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>45917</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>45405</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>45405</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>45184</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45009</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45547</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>44578</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>44592</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45541</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45412</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>45552</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>45462</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44585</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45763</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45401</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>45646</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>45566</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>45105</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>45645</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>45551</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>45541</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>45925</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>45184</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>45194</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45197</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33933,7 +33933,7 @@
         <v>45350</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>45021</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>44950</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>45043</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>45681</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34298,7 +34298,7 @@
         <v>45570</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34371,7 +34371,7 @@
         <v>44591</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34444,7 +34444,7 @@
         <v>44938</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>44608</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>45169</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44977</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34741,7 +34741,7 @@
         <v>44626</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45740</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>45735</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>44943</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>44943</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>45734</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>45934</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>45112</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45112</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45435</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>44930</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>45030</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>44575</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45371</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45617</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>45056</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44950</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>44564</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>45174</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45363</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>45364</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>45726</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>44571</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>44966</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44992</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>45179</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>45182</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45806</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>44988</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45805</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45600</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45600</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>45597</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>45182</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>44711</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44998</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>45440</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45945</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45547</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>44614</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37676,7 +37676,7 @@
         <v>45946</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>44894</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>45946</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>45763</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45295</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44839</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45643</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>45561</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>44659</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45705</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>45671</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45617</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>45113</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45435</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45819</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>45316</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45826</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45456</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45215</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>45404</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45523</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>44965</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>45392</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>44704</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45198</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45706</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>44734</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>45198</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45671</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39823,7 +39823,7 @@
         <v>45958</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45958</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>45958</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45015</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>44655</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45211</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>44734</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40339,7 +40339,7 @@
         <v>44734</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45194</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40490,7 +40490,7 @@
         <v>45681</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40563,7 +40563,7 @@
         <v>45966</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>45966</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>45966</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40782,7 +40782,7 @@
         <v>45644</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>45965</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>45966</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45966</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45210</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>45756</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45169</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>45968</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45197</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>45617</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45842</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>44614</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>45846</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>45846</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45756</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45797</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>45587</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>45759</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>45314</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>45303</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42257,7 +42257,7 @@
         <v>45693</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>44729</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45974</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>45974</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45974</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>45245</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42710,7 +42710,7 @@
         <v>45189</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45469</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>45294</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45974</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>44904</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43090,7 +43090,7 @@
         <v>44897</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>44904</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>45246</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45974</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45974</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45974</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>45761</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>45974</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>45679</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45149</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>45975</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>45201</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>45751</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>45726</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45630</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>44719</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>45701</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45788</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45035</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45226</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44595,7 +44595,7 @@
         <v>45861</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>45188</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>44803</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44814,7 +44814,7 @@
         <v>44882</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>45240</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>45978</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>45621</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45182</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45870</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45788</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45708</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45715</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>44627</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>44985</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45734</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45695,7 +45695,7 @@
         <v>45979</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>45875</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45682</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45919,7 +45919,7 @@
         <v>45880</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>44889</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>45198</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45198</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45747</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46284,7 +46284,7 @@
         <v>45201</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>45272</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>45534</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45260</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>44886</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>46101</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>45253</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>45300</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45215</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>45392</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45043</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>44867</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         <v>44741</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>45477</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45477</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>44904</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45988</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>45112</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45749</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45587</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45302</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47817,7 +47817,7 @@
         <v>46119</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47890,7 +47890,7 @@
         <v>46119</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>46119</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48036,7 +48036,7 @@
         <v>46120</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>46120</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>46120</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>44893</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48328,7 +48328,7 @@
         <v>45406</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45406</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>45995</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>44853</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48620,7 +48620,7 @@
         <v>44484</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>44949</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48766,7 +48766,7 @@
         <v>44648</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48839,7 +48839,7 @@
         <v>46000</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48912,7 +48912,7 @@
         <v>44861</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>44938</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49063,7 +49063,7 @@
         <v>45375</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>45180</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49209,7 +49209,7 @@
         <v>44943</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
         <v>44614</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44711</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49428,7 +49428,7 @@
         <v>44622</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>45947</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45058</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         <v>45758</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>44662</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>46009</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49876,7 +49876,7 @@
         <v>46009</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>46009</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50032,7 +50032,7 @@
         <v>46009</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50110,7 +50110,7 @@
         <v>46010</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45558</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45271</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>46008</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50412,7 +50412,7 @@
         <v>46009</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50490,7 +50490,7 @@
         <v>44861</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50563,7 +50563,7 @@
         <v>44861</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45958</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50709,7 +50709,7 @@
         <v>46013</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50782,7 +50782,7 @@
         <v>46013</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50855,7 +50855,7 @@
         <v>46013</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50928,7 +50928,7 @@
         <v>46013</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>46013</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>46013</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51147,7 +51147,7 @@
         <v>45461</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51220,7 +51220,7 @@
         <v>45541</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45846</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51366,7 +51366,7 @@
         <v>45730</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45043</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>46026</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51590,7 +51590,7 @@
         <v>46026</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>44897</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51741,7 +51741,7 @@
         <v>45455</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>44507</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>45569</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51965,7 +51965,7 @@
         <v>44943</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>44943</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52111,7 +52111,7 @@
         <v>45580</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52184,7 +52184,7 @@
         <v>46030</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>46029</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52335,7 +52335,7 @@
         <v>45810</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>46031</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>46031</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>45477</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52627,7 +52627,7 @@
         <v>45841</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>45547</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45034</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45764</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>45834</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>44677</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53070,7 +53070,7 @@
         <v>46035</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>46035</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>46038</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>44658</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53367,7 +53367,7 @@
         <v>46041</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53440,7 +53440,7 @@
         <v>45048</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53513,7 +53513,7 @@
         <v>46041</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>46041</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53659,7 +53659,7 @@
         <v>46059</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>46043</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53805,7 +53805,7 @@
         <v>46043</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45875</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53951,7 +53951,7 @@
         <v>45051</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54024,7 +54024,7 @@
         <v>46048</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54097,7 +54097,7 @@
         <v>46048</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>46048</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54243,7 +54243,7 @@
         <v>46048</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54321,7 +54321,7 @@
         <v>44735</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>44846</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54467,7 +54467,7 @@
         <v>45130</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>46048</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>46048</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>46002</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>45764</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54832,7 +54832,7 @@
         <v>46049</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>46050</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54978,7 +54978,7 @@
         <v>45471</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>44977</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55124,7 +55124,7 @@
         <v>46049</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>45734</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55270,7 +55270,7 @@
         <v>46055</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>46055</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55416,7 +55416,7 @@
         <v>46055</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55489,7 +55489,7 @@
         <v>46059</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55562,7 +55562,7 @@
         <v>46059</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55635,7 +55635,7 @@
         <v>46059</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>46059</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>46059</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55854,7 +55854,7 @@
         <v>46059</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55927,7 +55927,7 @@
         <v>46059</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56000,7 +56000,7 @@
         <v>46062</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56073,7 +56073,7 @@
         <v>45775</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>46062</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         <v>46062</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56292,7 +56292,7 @@
         <v>46059</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56365,7 +56365,7 @@
         <v>46063</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56438,7 +56438,7 @@
         <v>46045</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56511,7 +56511,7 @@
         <v>46069</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56584,7 +56584,7 @@
         <v>46069</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>46069</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56730,7 +56730,7 @@
         <v>46070</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56803,7 +56803,7 @@
         <v>46070</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56876,7 +56876,7 @@
         <v>46070</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56949,7 +56949,7 @@
         <v>46073</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57022,7 +57022,7 @@
         <v>46079</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>45470</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57168,7 +57168,7 @@
         <v>46087</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57241,7 +57241,7 @@
         <v>46091</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57314,7 +57314,7 @@
         <v>46162</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57392,7 +57392,7 @@
         <v>46162</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57470,7 +57470,7 @@
         <v>46162</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57548,7 +57548,7 @@
         <v>46162</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>46162</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57704,7 +57704,7 @@
         <v>46162</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57782,7 +57782,7 @@
         <v>46167</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57855,7 +57855,7 @@
         <v>46167</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>46168</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>46168</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58079,7 +58079,7 @@
         <v>46168</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58157,7 +58157,7 @@
         <v>46170</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58230,7 +58230,7 @@
         <v>46170</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>44628</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58376,7 +58376,7 @@
         <v>46170</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58449,7 +58449,7 @@
         <v>46170</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58522,7 +58522,7 @@
         <v>46174</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58600,7 +58600,7 @@
         <v>46174</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58678,7 +58678,7 @@
         <v>46174</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58756,7 +58756,7 @@
         <v>45929</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58829,7 +58829,7 @@
         <v>46182</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58902,7 +58902,7 @@
         <v>46184</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58980,7 +58980,7 @@
         <v>46189</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59053,7 +59053,7 @@
         <v>46188</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>46197</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59199,7 +59199,7 @@
         <v>46201</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59272,7 +59272,7 @@
         <v>46201</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         <v>46201</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59418,7 +59418,7 @@
         <v>46198</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59491,7 +59491,7 @@
         <v>46203</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59564,7 +59564,7 @@
         <v>46203</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59637,7 +59637,7 @@
         <v>46206</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59715,7 +59715,7 @@
         <v>46206</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59793,7 +59793,7 @@
         <v>46206</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59871,7 +59871,7 @@
         <v>46211</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59944,7 +59944,7 @@
         <v>46211</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60022,7 +60022,7 @@
         <v>46211</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60095,7 +60095,7 @@
         <v>46211</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60168,7 +60168,7 @@
         <v>46211</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60246,7 +60246,7 @@
         <v>46211</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60319,7 +60319,7 @@
         <v>46211</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60392,7 +60392,7 @@
         <v>46211</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60465,7 +60465,7 @@
         <v>46211</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60538,7 +60538,7 @@
         <v>46211</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>46211</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60684,7 +60684,7 @@
         <v>46212</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60757,7 +60757,7 @@
         <v>46212</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60835,7 +60835,7 @@
         <v>46212</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60913,7 +60913,7 @@
         <v>45946</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60986,7 +60986,7 @@
         <v>46219</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61059,7 +61059,7 @@
         <v>46219</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61132,7 +61132,7 @@
         <v>46262</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61205,7 +61205,7 @@
         <v>45842</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61278,7 +61278,7 @@
         <v>46220</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61351,7 +61351,7 @@
         <v>46265</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         <v>46267</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>46268</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>46270</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61643,7 +61643,7 @@
         <v>46272</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61716,7 +61716,7 @@
         <v>46272</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61789,7 +61789,7 @@
         <v>46272</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61862,7 +61862,7 @@
         <v>46272</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61935,7 +61935,7 @@
         <v>46272</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>46230</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62086,7 +62086,7 @@
         <v>46230</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>46273</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>46276</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>46276</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>46274</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>46234</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62529,7 +62529,7 @@
         <v>46279</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>46279</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62685,7 +62685,7 @@
         <v>46279</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62763,7 +62763,7 @@
         <v>46233</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62841,7 +62841,7 @@
         <v>46234</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62914,7 +62914,7 @@
         <v>46234</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>46233</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63065,7 +63065,7 @@
         <v>46234</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63138,7 +63138,7 @@
         <v>46267</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>46239</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63284,7 +63284,7 @@
         <v>46279</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63362,7 +63362,7 @@
         <v>46239</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63435,7 +63435,7 @@
         <v>46238</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63508,7 +63508,7 @@
         <v>46286</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63581,7 +63581,7 @@
         <v>46286</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63654,7 +63654,7 @@
         <v>46286</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63727,7 +63727,7 @@
         <v>46286</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63805,7 +63805,7 @@
         <v>46281</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63878,7 +63878,7 @@
         <v>46286</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63956,7 +63956,7 @@
         <v>46286</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64029,7 +64029,7 @@
         <v>46244</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64102,7 +64102,7 @@
         <v>46279</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64180,7 +64180,7 @@
         <v>46244</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64253,7 +64253,7 @@
         <v>46244</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64326,7 +64326,7 @@
         <v>46290</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64404,7 +64404,7 @@
         <v>46246</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>46246</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64550,7 +64550,7 @@
         <v>46246</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64623,7 +64623,7 @@
         <v>46290</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64701,7 +64701,7 @@
         <v>46290</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64779,7 +64779,7 @@
         <v>46247</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64852,7 +64852,7 @@
         <v>46290</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64930,7 +64930,7 @@
         <v>46293</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65003,7 +65003,7 @@
         <v>46248</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65076,7 +65076,7 @@
         <v>46294</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65149,7 +65149,7 @@
         <v>46293</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65227,7 +65227,7 @@
         <v>46294</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65300,7 +65300,7 @@
         <v>46295</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65373,7 +65373,7 @@
         <v>46294</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65446,7 +65446,7 @@
         <v>46252</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65519,7 +65519,7 @@
         <v>46295</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65597,7 +65597,7 @@
         <v>46244</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65670,7 +65670,7 @@
         <v>46255</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65743,7 +65743,7 @@
         <v>46302</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65816,7 +65816,7 @@
         <v>46248</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65889,7 +65889,7 @@
         <v>46301</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65962,7 +65962,7 @@
         <v>46302</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66035,7 +66035,7 @@
         <v>46302</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66108,7 +66108,7 @@
         <v>46303</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66181,7 +66181,7 @@
         <v>46282</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66254,7 +66254,7 @@
         <v>45701</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66327,7 +66327,7 @@
         <v>44658</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66400,7 +66400,7 @@
         <v>44607</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66473,7 +66473,7 @@
         <v>44593</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66546,7 +66546,7 @@
         <v>44711</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66619,7 +66619,7 @@
         <v>45313</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>45131</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66775,7 +66775,7 @@
         <v>44510</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66848,7 +66848,7 @@
         <v>44956</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66926,7 +66926,7 @@
         <v>45407</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67004,7 +67004,7 @@
         <v>45327</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67077,7 +67077,7 @@
         <v>44753</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67150,7 +67150,7 @@
         <v>44998</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67223,7 +67223,7 @@
         <v>45794</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67296,7 +67296,7 @@
         <v>45798</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67369,7 +67369,7 @@
         <v>45712</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67462,7 +67462,7 @@
         <v>45798</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67535,7 +67535,7 @@
         <v>45712</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67608,7 +67608,7 @@
         <v>45817</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67686,7 +67686,7 @@
         <v>45870</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67759,7 +67759,7 @@
         <v>45994</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67832,7 +67832,7 @@
         <v>46047</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67905,7 +67905,7 @@
         <v>46304</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45856</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45936</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46043</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45111</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44607</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46225</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>45609</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>45348</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>46055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45302</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46288</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44607</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45510</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>44970</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45268</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44963</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>46280</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>44992</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>45930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>44512</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>46198</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>45788</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45747</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44602</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45604</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46176</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>46055</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46133</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>44536</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>44530</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>45777</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>45783</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45772</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>44974</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>46107</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>45898</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44747</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>44607</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>46092</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45580</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>45539</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45331</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>45446</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45373</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44943</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45538</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>45947</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>46174</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>45302</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>46048</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>46049</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>46196</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44991</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>46230</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45758</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>46286</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>45358</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>45982</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>45790</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>45679</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45603</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>43983</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>45013</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44647</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45393</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45790</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44613</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44711</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44579</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45477</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44750</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45177</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45436</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44840</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45295</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>45272</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45205</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>45730</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>45720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>45338</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>45926</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>45205</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45764</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>46162</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10940,7 +10940,7 @@
         <v>46162</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>45184</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44557</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>46013</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46048</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>46055</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>46059</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>44963</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45751</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>46106</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>44992</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>46203</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>44879</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>46212</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>46211</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>45343</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>44893</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>45558</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>46286</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>46279</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45600</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45617</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45201</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>46294</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>46252</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>44540</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>46302</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>46302</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45740</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45587</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45841</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>45842</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>45616</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45846</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>44955</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45029</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>44711</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44628</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45712</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45712</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45846</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>44496</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>44575</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44662</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>44487</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>44749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>44749</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>44792</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>44487</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>44487</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44749</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>44881</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>44665</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44792</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>44538</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>44487</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>44487</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>44852</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>44498</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>44881</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>44673</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44754</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>44855</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>44511</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44840</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44537</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>44575</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44711</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>44659</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44659</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44578</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>44579</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44557</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>44616</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44575</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44575</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44819</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>44819</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44523</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>44846</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>44605</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>44711</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>44841</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44792</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44830</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>44787</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>44825</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>44614</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44585</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>44711</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>44488</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>44498</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>44532</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>44593</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>44729</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>44805</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>44811</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>44853</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45435</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45272</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>44711</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45617</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45469</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>45114</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45764</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45012</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45697</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>45169</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45048</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45747</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45605</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45152</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45404</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>44589</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>45111</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>45145</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>44628</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>45307</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>45726</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>45012</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>45092</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>45405</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45405</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45621</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>44998</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>44943</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45456</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>45621</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>45621</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>45757</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>45645</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45295</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>44943</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>44938</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45253</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>45392</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>45184</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45116</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>44949</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45545</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>44662</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>44904</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44904</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44897</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>44904</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44861</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>44861</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>45406</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>44882</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>45373</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>45183</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>45539</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44571</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44592</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45547</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>45461</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45455</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44622</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>44893</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>45726</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>45037</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45600</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45600</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45215</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45468</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45371</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45682</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44977</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45617</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>44585</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45152</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45351</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44846</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45502</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44904</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45358</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>45189</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45182</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45294</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>44507</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>45079</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44626</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>45035</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>45246</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>45058</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>44950</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>45119</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26103,7 +26103,7 @@
         <v>45240</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>45566</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>45566</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>44837</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>45502</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>45834</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>45558</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>46002</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45210</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>44614</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45021</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>44963</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44935</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>44867</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45758</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45730</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45180</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45841</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>44904</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44575</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45887</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45846</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45887</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45260</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45892</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45892</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45892</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45008</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45895</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45105</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45474</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45947</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45887</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>45124</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>45764</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>45759</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>45051</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45898</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>44487</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45734</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45902</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45316</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45905</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>44631</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45875</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>45552</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45908</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45908</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45908</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>45908</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45775</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45693</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45169</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45679</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45902</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>44923</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45917</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45764</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45300</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45925</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45681</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>44659</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45455</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45934</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>44889</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44853</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>45401</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>44988</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45471</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>45198</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>45364</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>45945</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>45188</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45356</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>45181</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44882</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>45946</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44965</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>45946</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>45749</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>44648</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>45470</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>45958</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45958</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>45958</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45194</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45763</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>44943</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>44943</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>45587</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>45642</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>45965</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45966</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>45966</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32995,7 +32995,7 @@
         <v>45966</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33068,7 +33068,7 @@
         <v>45966</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>45734</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>45966</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>45043</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33360,7 +33360,7 @@
         <v>45968</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33433,7 +33433,7 @@
         <v>46162</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45392</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>46162</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>45974</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>45974</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>46162</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45974</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45974</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>45974</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>46162</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>45271</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45975</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45974</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45974</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34510,7 +34510,7 @@
         <v>45974</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34588,7 +34588,7 @@
         <v>45979</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>46162</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>45978</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>45215</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>44803</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>46162</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>45673</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44957</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>46167</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45460</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>46167</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>45030</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44977</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35547,7 +35547,7 @@
         <v>45034</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>45349</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35693,7 +35693,7 @@
         <v>46168</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45182</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45988</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>46168</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45763</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>45646</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>45169</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>45169</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44704</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>46168</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45401</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45414</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45995</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>45758</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>46170</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>46000</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>46170</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>46170</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>46170</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>45198</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45198</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>44886</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>44658</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>45303</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45580</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44550</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>46174</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45455</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>46009</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>44628</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>45130</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45477</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>45547</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>45112</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45112</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>46008</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>45174</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38444,7 +38444,7 @@
         <v>46174</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>46174</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>45557</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>46013</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45958</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>46013</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>46010</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>44614</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>46009</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>46013</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>46009</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>46009</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45462</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>44861</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>46013</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>46013</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>46009</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>46013</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45324</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>45270</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>45179</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>44507</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>46026</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>46026</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40231,7 +40231,7 @@
         <v>46029</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>46031</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40377,7 +40377,7 @@
         <v>45618</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
         <v>46030</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>46031</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>45275</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>45929</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>46035</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>46035</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>46041</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>44936</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45538</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>46038</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>46041</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>46043</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>46043</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>46059</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>46041</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45302</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45300</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45412</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>46048</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>44735</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>46048</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>46049</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>46048</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>46049</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>46182</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>46048</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>46048</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>46048</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45182</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>45267</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45149</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>44943</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>46050</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45615</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>45615</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45523</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>46055</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>46055</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         <v>46055</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>46059</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>46059</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>46059</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>46059</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43614,7 +43614,7 @@
         <v>46059</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>46059</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>46059</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45281</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>46059</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>46184</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>44944</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
         <v>44614</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>46062</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44281,7 +44281,7 @@
         <v>46062</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44354,7 +44354,7 @@
         <v>44729</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>46062</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>46063</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44573,7 +44573,7 @@
         <v>46045</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>46069</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>46069</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>46189</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>46069</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>44648</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45177</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45084,7 +45084,7 @@
         <v>46070</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         <v>44938</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>46070</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>46070</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>45588</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45454,7 +45454,7 @@
         <v>46073</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>44655</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>46188</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>46079</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>44839</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>45092</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45897,7 +45897,7 @@
         <v>44893</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>46087</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45363</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>45314</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46189,7 +46189,7 @@
         <v>46091</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45226</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>44589</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>44578</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46481,7 +46481,7 @@
         <v>45587</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46554,7 +46554,7 @@
         <v>44804</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46627,7 +46627,7 @@
         <v>45043</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46700,7 +46700,7 @@
         <v>46197</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46773,7 +46773,7 @@
         <v>45113</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46846,7 +46846,7 @@
         <v>46101</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45644</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46992,7 +46992,7 @@
         <v>46198</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>44608</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>46119</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47211,7 +47211,7 @@
         <v>46119</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>46120</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47357,7 +47357,7 @@
         <v>44734</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47435,7 +47435,7 @@
         <v>44734</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47513,7 +47513,7 @@
         <v>46120</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>46120</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>46119</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47732,7 +47732,7 @@
         <v>44904</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47805,7 +47805,7 @@
         <v>46201</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47878,7 +47878,7 @@
         <v>45197</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>45321</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45043</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48097,7 +48097,7 @@
         <v>46201</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>46201</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>46203</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>45545</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         <v>44711</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48467,7 +48467,7 @@
         <v>45477</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48540,7 +48540,7 @@
         <v>45477</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>46203</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45299</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>44998</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>45175</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45118</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>44591</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45708</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>45211</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49197,7 +49197,7 @@
         <v>45112</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45810</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49343,7 +49343,7 @@
         <v>46206</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49421,7 +49421,7 @@
         <v>46206</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49499,7 +49499,7 @@
         <v>45375</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         <v>45541</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>44853</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>46206</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45492</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45562</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49942,7 +49942,7 @@
         <v>45477</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50015,7 +50015,7 @@
         <v>45477</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>45359</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>46211</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50234,7 +50234,7 @@
         <v>46211</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>46212</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>45243</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50463,7 +50463,7 @@
         <v>46211</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>46211</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>45184</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50682,7 +50682,7 @@
         <v>46211</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50755,7 +50755,7 @@
         <v>46211</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50833,7 +50833,7 @@
         <v>46212</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50911,7 +50911,7 @@
         <v>46211</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>46211</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51057,7 +51057,7 @@
         <v>46211</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51130,7 +51130,7 @@
         <v>46211</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>46212</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51276,7 +51276,7 @@
         <v>46211</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45946</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51427,7 +51427,7 @@
         <v>44950</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51500,7 +51500,7 @@
         <v>44950</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51573,7 +51573,7 @@
         <v>44930</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51646,7 +51646,7 @@
         <v>45531</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>46219</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51792,7 +51792,7 @@
         <v>45757</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51865,7 +51865,7 @@
         <v>45842</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>46220</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52011,7 +52011,7 @@
         <v>45462</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52084,7 +52084,7 @@
         <v>45201</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52157,7 +52157,7 @@
         <v>46219</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52230,7 +52230,7 @@
         <v>45201</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52303,7 +52303,7 @@
         <v>44719</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52376,7 +52376,7 @@
         <v>45335</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>46230</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>46230</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>46272</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52683,7 +52683,7 @@
         <v>45092</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52756,7 +52756,7 @@
         <v>45099</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52829,7 +52829,7 @@
         <v>46273</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52902,7 +52902,7 @@
         <v>46270</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52975,7 +52975,7 @@
         <v>46272</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>46272</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53121,7 +53121,7 @@
         <v>46272</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>46272</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53267,7 +53267,7 @@
         <v>44943</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53340,7 +53340,7 @@
         <v>45201</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53418,7 +53418,7 @@
         <v>44985</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53491,7 +53491,7 @@
         <v>45245</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53564,7 +53564,7 @@
         <v>46274</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53637,7 +53637,7 @@
         <v>45107</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45314</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53783,7 +53783,7 @@
         <v>45295</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>46233</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53939,7 +53939,7 @@
         <v>45534</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54012,7 +54012,7 @@
         <v>45617</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>44564</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54158,7 +54158,7 @@
         <v>46234</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>46279</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>46279</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54387,7 +54387,7 @@
         <v>45377</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54460,7 +54460,7 @@
         <v>45219</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54533,7 +54533,7 @@
         <v>46234</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54606,7 +54606,7 @@
         <v>46234</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>46234</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>45363</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54825,7 +54825,7 @@
         <v>46279</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54903,7 +54903,7 @@
         <v>45240</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>46233</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>46276</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55127,7 +55127,7 @@
         <v>44966</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55205,7 +55205,7 @@
         <v>46276</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>45194</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55351,7 +55351,7 @@
         <v>45112</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>45107</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55497,7 +55497,7 @@
         <v>45015</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
         <v>46238</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>44904</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55716,7 +55716,7 @@
         <v>45049</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55789,7 +55789,7 @@
         <v>45338</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55867,7 +55867,7 @@
         <v>44894</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55940,7 +55940,7 @@
         <v>44893</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56018,7 +56018,7 @@
         <v>44605</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56091,7 +56091,7 @@
         <v>46239</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>45197</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>45406</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56315,7 +56315,7 @@
         <v>44985</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56388,7 +56388,7 @@
         <v>45051</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56461,7 +56461,7 @@
         <v>45706</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56539,7 +56539,7 @@
         <v>45671</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56612,7 +56612,7 @@
         <v>46239</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>45705</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56758,7 +56758,7 @@
         <v>46281</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>46279</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>45740</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>45693</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57055,7 +57055,7 @@
         <v>45009</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57128,7 +57128,7 @@
         <v>46244</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57201,7 +57201,7 @@
         <v>46286</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>46286</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57352,7 +57352,7 @@
         <v>45127</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>44677</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57498,7 +57498,7 @@
         <v>45756</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>46286</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>46286</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57717,7 +57717,7 @@
         <v>45324</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57795,7 +57795,7 @@
         <v>45324</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>45671</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57946,7 +57946,7 @@
         <v>45414</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>45761</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58092,7 +58092,7 @@
         <v>46244</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58165,7 +58165,7 @@
         <v>44741</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>46286</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58316,7 +58316,7 @@
         <v>46244</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>46286</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45223</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58535,7 +58535,7 @@
         <v>45541</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58608,7 +58608,7 @@
         <v>45435</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58686,7 +58686,7 @@
         <v>44967</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>44734</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58837,7 +58837,7 @@
         <v>46246</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58910,7 +58910,7 @@
         <v>46279</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58988,7 +58988,7 @@
         <v>46246</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59061,7 +59061,7 @@
         <v>46246</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59134,7 +59134,7 @@
         <v>45747</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45533</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59280,7 +59280,7 @@
         <v>46290</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59358,7 +59358,7 @@
         <v>46248</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59431,7 +59431,7 @@
         <v>46290</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59509,7 +59509,7 @@
         <v>46293</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>45635</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59660,7 +59660,7 @@
         <v>46290</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45541</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59811,7 +59811,7 @@
         <v>45201</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59884,7 +59884,7 @@
         <v>45341</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59957,7 +59957,7 @@
         <v>46290</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60035,7 +60035,7 @@
         <v>44950</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60108,7 +60108,7 @@
         <v>45099</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60181,7 +60181,7 @@
         <v>45681</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60254,7 +60254,7 @@
         <v>45715</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60327,7 +60327,7 @@
         <v>46247</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60400,7 +60400,7 @@
         <v>44627</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60473,7 +60473,7 @@
         <v>45056</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>46293</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60619,7 +60619,7 @@
         <v>45355</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60692,7 +60692,7 @@
         <v>44966</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60770,7 +60770,7 @@
         <v>46294</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>46294</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60916,7 +60916,7 @@
         <v>44588</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>44488</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61062,7 +61062,7 @@
         <v>46252</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61135,7 +61135,7 @@
         <v>45197</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61208,7 +61208,7 @@
         <v>46294</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61281,7 +61281,7 @@
         <v>45547</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61359,7 +61359,7 @@
         <v>46295</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45569</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61510,7 +61510,7 @@
         <v>44897</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>45764</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61661,7 +61661,7 @@
         <v>46295</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61734,7 +61734,7 @@
         <v>46244</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61807,7 +61807,7 @@
         <v>45198</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61880,7 +61880,7 @@
         <v>45056</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>45406</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62026,7 +62026,7 @@
         <v>45406</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62099,7 +62099,7 @@
         <v>45440</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62172,7 +62172,7 @@
         <v>45216</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>46255</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62318,7 +62318,7 @@
         <v>45667</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62391,7 +62391,7 @@
         <v>46301</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>45519</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62537,7 +62537,7 @@
         <v>45586</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62610,7 +62610,7 @@
         <v>46302</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62683,7 +62683,7 @@
         <v>46302</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62756,7 +62756,7 @@
         <v>45541</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62829,7 +62829,7 @@
         <v>45551</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45350</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62975,7 +62975,7 @@
         <v>45646</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63048,7 +63048,7 @@
         <v>45570</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63121,7 +63121,7 @@
         <v>46282</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63194,7 +63194,7 @@
         <v>45701</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63267,7 +63267,7 @@
         <v>45740</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63340,7 +63340,7 @@
         <v>46262</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63413,7 +63413,7 @@
         <v>46303</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63486,7 +63486,7 @@
         <v>45735</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63559,7 +63559,7 @@
         <v>45734</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63632,7 +63632,7 @@
         <v>46265</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63705,7 +63705,7 @@
         <v>46308</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>46308</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63851,7 +63851,7 @@
         <v>46308</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63924,7 +63924,7 @@
         <v>44992</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63997,7 +63997,7 @@
         <v>45805</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64070,7 +64070,7 @@
         <v>45806</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64143,7 +64143,7 @@
         <v>45597</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64216,7 +64216,7 @@
         <v>46308</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64289,7 +64289,7 @@
         <v>46309</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64362,7 +64362,7 @@
         <v>46268</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64435,7 +64435,7 @@
         <v>45643</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64508,7 +64508,7 @@
         <v>45561</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64581,7 +64581,7 @@
         <v>46248</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64654,7 +64654,7 @@
         <v>45819</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64727,7 +64727,7 @@
         <v>46310</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64800,7 +64800,7 @@
         <v>46310</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64873,7 +64873,7 @@
         <v>46267</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64946,7 +64946,7 @@
         <v>46267</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65019,7 +65019,7 @@
         <v>45826</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65092,7 +65092,7 @@
         <v>45756</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65165,7 +65165,7 @@
         <v>45842</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65238,7 +65238,7 @@
         <v>45797</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65311,7 +65311,7 @@
         <v>45587</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65384,7 +65384,7 @@
         <v>45846</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65462,7 +65462,7 @@
         <v>45846</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65540,7 +65540,7 @@
         <v>45751</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65618,7 +65618,7 @@
         <v>45630</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65696,7 +65696,7 @@
         <v>45701</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65769,7 +65769,7 @@
         <v>45788</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65842,7 +65842,7 @@
         <v>45861</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65915,7 +65915,7 @@
         <v>45788</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65988,7 +65988,7 @@
         <v>45870</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66066,7 +66066,7 @@
         <v>45875</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66144,7 +66144,7 @@
         <v>45734</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66217,7 +66217,7 @@
         <v>45880</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66290,7 +66290,7 @@
         <v>45883</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66363,7 +66363,7 @@
         <v>45883</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66436,7 +66436,7 @@
         <v>45883</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66509,7 +66509,7 @@
         <v>45883</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66582,7 +66582,7 @@
         <v>45313</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66660,7 +66660,7 @@
         <v>44658</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66733,7 +66733,7 @@
         <v>44607</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66806,7 +66806,7 @@
         <v>45131</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66884,7 +66884,7 @@
         <v>44593</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66957,7 +66957,7 @@
         <v>44510</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67030,7 +67030,7 @@
         <v>44956</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67108,7 +67108,7 @@
         <v>45407</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67186,7 +67186,7 @@
         <v>45327</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67259,7 +67259,7 @@
         <v>44711</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>44753</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67405,7 +67405,7 @@
         <v>44998</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67478,7 +67478,7 @@
         <v>45794</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67551,7 +67551,7 @@
         <v>45798</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67624,7 +67624,7 @@
         <v>45712</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67717,7 +67717,7 @@
         <v>45798</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67790,7 +67790,7 @@
         <v>45712</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67863,7 +67863,7 @@
         <v>45817</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67941,7 +67941,7 @@
         <v>45870</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68014,7 +68014,7 @@
         <v>45994</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68087,7 +68087,7 @@
         <v>46047</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68160,7 +68160,7 @@
         <v>46304</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45856</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45936</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46043</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45111</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44607</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46225</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>45609</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>45348</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>46055</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45302</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46288</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44607</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45510</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>44970</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45268</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44963</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>46280</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>44992</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>45930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>44512</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>46198</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>45788</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45747</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>44602</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45604</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46176</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>46055</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46133</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>44536</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>44530</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>45777</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>45783</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45772</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>44974</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>46107</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>45898</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44747</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>44607</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>46092</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45580</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>45539</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45331</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>45446</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45373</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44943</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45538</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>45947</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>46174</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>45302</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>46048</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>46049</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>46196</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44991</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>46230</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45758</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>46286</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>45358</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>45982</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>45790</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>45679</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45603</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>43983</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>45013</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44647</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45393</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45790</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44613</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44711</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44579</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45477</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44750</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45177</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45436</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44840</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45295</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>45272</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45205</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>45730</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>45720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>45338</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>45926</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>45205</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45764</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>46162</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10940,7 +10940,7 @@
         <v>46162</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>45184</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>44557</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>46013</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>46048</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>46055</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>46059</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>44963</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45751</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>46106</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>44992</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>46203</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>44879</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>46212</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>46211</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>45343</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>44893</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>45558</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>46286</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>46279</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45600</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45617</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45201</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>46294</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>46252</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>44540</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>46302</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>46302</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45740</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45587</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45841</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>45842</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>45616</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45846</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>44955</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45029</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>44711</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44628</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45712</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45712</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45846</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>44496</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>44575</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44662</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>44487</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>44749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>44749</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>44792</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>44487</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>44487</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44749</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>44881</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>44665</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44792</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>44538</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>44487</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>44487</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>44852</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>44498</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>44881</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>44673</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44754</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>44855</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>44511</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44840</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44537</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>44575</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44711</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>44659</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44659</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44578</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>44579</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44557</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>44616</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44575</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44575</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44819</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>44819</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44523</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>44846</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>44605</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>44711</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>44841</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44792</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44830</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>44787</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>44825</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>44614</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44585</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>44711</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>44488</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>44498</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>44532</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>44593</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>44729</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>44805</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>44811</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>44853</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45435</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45272</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>44711</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45617</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45469</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>45114</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45764</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45012</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45697</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>45169</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45048</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45747</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45605</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45152</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45404</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>44589</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>45111</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>45145</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>44628</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>45307</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>45726</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>45012</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>45092</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>45405</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45405</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45621</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>44998</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>44943</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45456</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>45621</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>45621</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>45757</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>45645</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45295</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>44943</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>44938</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45253</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>45392</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>45184</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45116</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>44949</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45545</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>44662</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>44904</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44904</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44897</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>44904</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44861</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>44861</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>45406</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>44882</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>45373</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>45183</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>45539</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44571</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44592</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45547</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>45461</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45455</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44622</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>44893</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>45726</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>45037</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45600</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45600</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45215</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45468</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45371</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45682</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44977</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45617</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>44585</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45152</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45351</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44846</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45502</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44904</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45358</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>45189</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45182</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45294</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>44507</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>45079</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44626</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>45035</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>45246</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>45058</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>44950</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>45119</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26103,7 +26103,7 @@
         <v>45240</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>45566</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>45566</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>44837</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>45502</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>45834</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>45558</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>46002</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45210</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>44614</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45021</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>44963</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44935</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>44867</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45758</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45730</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45180</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45841</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>44904</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44575</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45887</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45846</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45887</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45260</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45892</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45892</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45892</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45008</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45895</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45105</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45474</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45947</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45887</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>45124</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>45764</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>45759</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>45051</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45898</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>44487</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45734</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45902</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45316</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45905</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>44631</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45875</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>45552</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45908</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45908</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45908</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>45908</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45775</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45693</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45169</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45679</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45902</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>44923</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45917</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45764</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45300</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45925</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45681</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>44659</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45455</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45934</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>44889</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>44853</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>45401</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>44988</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45471</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>45198</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>45364</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>45945</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>45188</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45356</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>45181</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44882</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>45946</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44965</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>45946</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>45749</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>44648</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>45470</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>45958</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45958</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>45958</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45194</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45763</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>44943</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>44943</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>45587</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>45642</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>45965</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45966</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>45966</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32995,7 +32995,7 @@
         <v>45966</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33068,7 +33068,7 @@
         <v>45966</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>45734</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>45966</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>45043</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33360,7 +33360,7 @@
         <v>45968</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33433,7 +33433,7 @@
         <v>46162</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45392</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>46162</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>45974</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>45974</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>46162</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45974</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45974</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>45974</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>46162</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>45271</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45975</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45974</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45974</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34510,7 +34510,7 @@
         <v>45974</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34588,7 +34588,7 @@
         <v>45979</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>46162</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>45978</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>45215</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>44803</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>46162</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>45673</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44957</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>46167</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45460</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>46167</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>45030</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44977</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35547,7 +35547,7 @@
         <v>45034</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>45349</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35693,7 +35693,7 @@
         <v>46168</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45182</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45988</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>46168</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45763</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>45646</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>45169</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>45169</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44704</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>46168</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45401</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45414</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45995</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>45758</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>46170</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>46000</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>46170</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>46170</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>46170</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>45198</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45198</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>44886</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>44658</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>45303</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45580</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44550</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>46174</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45455</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>46009</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>44628</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>45130</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45477</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>45547</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>45112</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45112</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>46008</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>45174</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38444,7 +38444,7 @@
         <v>46174</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>46174</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>45557</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>46013</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45958</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>46013</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>46010</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>44614</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>46009</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>46013</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>46009</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>46009</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45462</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>44861</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>46013</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>46013</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>46009</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>46013</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45324</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>45270</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>45179</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>44507</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>46026</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>46026</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40231,7 +40231,7 @@
         <v>46029</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>46031</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40377,7 +40377,7 @@
         <v>45618</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
         <v>46030</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>46031</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>45275</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>45929</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>46035</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>46035</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>46041</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>44936</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45538</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>46038</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>46041</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>46043</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>46043</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>46059</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>46041</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45302</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45300</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45412</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>46048</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>44735</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>46048</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>46049</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>46048</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>46049</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>46182</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>46048</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>46048</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>46048</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45182</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>45267</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45149</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>44943</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>46050</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45615</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>45615</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45523</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>46055</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>46055</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         <v>46055</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>46059</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>46059</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>46059</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>46059</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43614,7 +43614,7 @@
         <v>46059</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>46059</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>46059</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45281</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>46059</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>46184</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>44944</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
         <v>44614</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>46062</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44281,7 +44281,7 @@
         <v>46062</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44354,7 +44354,7 @@
         <v>44729</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>46062</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>46063</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44573,7 +44573,7 @@
         <v>46045</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>46069</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>46069</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>46189</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>46069</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>44648</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45177</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45084,7 +45084,7 @@
         <v>46070</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         <v>44938</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>46070</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>46070</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>45588</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45454,7 +45454,7 @@
         <v>46073</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>44655</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>46188</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>46079</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>44839</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>45092</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45897,7 +45897,7 @@
         <v>44893</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>46087</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45363</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>45314</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46189,7 +46189,7 @@
         <v>46091</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45226</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>44589</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>44578</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46481,7 +46481,7 @@
         <v>45587</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46554,7 +46554,7 @@
         <v>44804</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46627,7 +46627,7 @@
         <v>45043</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46700,7 +46700,7 @@
         <v>46197</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46773,7 +46773,7 @@
         <v>45113</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46846,7 +46846,7 @@
         <v>46101</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46919,7 +46919,7 @@
         <v>45644</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46992,7 +46992,7 @@
         <v>46198</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47065,7 +47065,7 @@
         <v>44608</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>46119</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47211,7 +47211,7 @@
         <v>46119</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>46120</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47357,7 +47357,7 @@
         <v>44734</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47435,7 +47435,7 @@
         <v>44734</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47513,7 +47513,7 @@
         <v>46120</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>46120</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>46119</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47732,7 +47732,7 @@
         <v>44904</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47805,7 +47805,7 @@
         <v>46201</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47878,7 +47878,7 @@
         <v>45197</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>45321</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45043</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48097,7 +48097,7 @@
         <v>46201</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>46201</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>46203</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>45545</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         <v>44711</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48467,7 +48467,7 @@
         <v>45477</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48540,7 +48540,7 @@
         <v>45477</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>46203</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45299</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>44998</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>45175</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45118</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>44591</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45708</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>45211</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49197,7 +49197,7 @@
         <v>45112</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45810</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49343,7 +49343,7 @@
         <v>46206</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49421,7 +49421,7 @@
         <v>46206</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49499,7 +49499,7 @@
         <v>45375</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         <v>45541</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>44853</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>46206</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>45492</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45562</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49942,7 +49942,7 @@
         <v>45477</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50015,7 +50015,7 @@
         <v>45477</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>45359</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>46211</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50234,7 +50234,7 @@
         <v>46211</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>46212</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>45243</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50463,7 +50463,7 @@
         <v>46211</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>46211</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>45184</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50682,7 +50682,7 @@
         <v>46211</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50755,7 +50755,7 @@
         <v>46211</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50833,7 +50833,7 @@
         <v>46212</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50911,7 +50911,7 @@
         <v>46211</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>46211</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51057,7 +51057,7 @@
         <v>46211</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51130,7 +51130,7 @@
         <v>46211</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>46212</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51276,7 +51276,7 @@
         <v>46211</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45946</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51427,7 +51427,7 @@
         <v>44950</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51500,7 +51500,7 @@
         <v>44950</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51573,7 +51573,7 @@
         <v>44930</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51646,7 +51646,7 @@
         <v>45531</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>46219</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51792,7 +51792,7 @@
         <v>45757</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51865,7 +51865,7 @@
         <v>45842</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>46220</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52011,7 +52011,7 @@
         <v>45462</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52084,7 +52084,7 @@
         <v>45201</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52157,7 +52157,7 @@
         <v>46219</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52230,7 +52230,7 @@
         <v>45201</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52303,7 +52303,7 @@
         <v>44719</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52376,7 +52376,7 @@
         <v>45335</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>46230</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
         <v>46230</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52610,7 +52610,7 @@
         <v>46272</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52683,7 +52683,7 @@
         <v>45092</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52756,7 +52756,7 @@
         <v>45099</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52829,7 +52829,7 @@
         <v>46273</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52902,7 +52902,7 @@
         <v>46270</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52975,7 +52975,7 @@
         <v>46272</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>46272</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53121,7 +53121,7 @@
         <v>46272</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>46272</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53267,7 +53267,7 @@
         <v>44943</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53340,7 +53340,7 @@
         <v>45201</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53418,7 +53418,7 @@
         <v>44985</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53491,7 +53491,7 @@
         <v>45245</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53564,7 +53564,7 @@
         <v>46274</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53637,7 +53637,7 @@
         <v>45107</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45314</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53783,7 +53783,7 @@
         <v>45295</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>46233</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53939,7 +53939,7 @@
         <v>45534</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54012,7 +54012,7 @@
         <v>45617</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>44564</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54158,7 +54158,7 @@
         <v>46234</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>46279</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>46279</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54387,7 +54387,7 @@
         <v>45377</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54460,7 +54460,7 @@
         <v>45219</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54533,7 +54533,7 @@
         <v>46234</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54606,7 +54606,7 @@
         <v>46234</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>46234</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>45363</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54825,7 +54825,7 @@
         <v>46279</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54903,7 +54903,7 @@
         <v>45240</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>46233</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>46276</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55127,7 +55127,7 @@
         <v>44966</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55205,7 +55205,7 @@
         <v>46276</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>45194</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55351,7 +55351,7 @@
         <v>45112</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>45107</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55497,7 +55497,7 @@
         <v>45015</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
         <v>46238</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>44904</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55716,7 +55716,7 @@
         <v>45049</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55789,7 +55789,7 @@
         <v>45338</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55867,7 +55867,7 @@
         <v>44894</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55940,7 +55940,7 @@
         <v>44893</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56018,7 +56018,7 @@
         <v>44605</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56091,7 +56091,7 @@
         <v>46239</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>45197</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>45406</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56315,7 +56315,7 @@
         <v>44985</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56388,7 +56388,7 @@
         <v>45051</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56461,7 +56461,7 @@
         <v>45706</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56539,7 +56539,7 @@
         <v>45671</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56612,7 +56612,7 @@
         <v>46239</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>45705</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56758,7 +56758,7 @@
         <v>46281</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>46279</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>45740</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>45693</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57055,7 +57055,7 @@
         <v>45009</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57128,7 +57128,7 @@
         <v>46244</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57201,7 +57201,7 @@
         <v>46286</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>46286</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57352,7 +57352,7 @@
         <v>45127</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>44677</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57498,7 +57498,7 @@
         <v>45756</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>46286</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>46286</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57717,7 +57717,7 @@
         <v>45324</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57795,7 +57795,7 @@
         <v>45324</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>45671</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57946,7 +57946,7 @@
         <v>45414</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>45761</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58092,7 +58092,7 @@
         <v>46244</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58165,7 +58165,7 @@
         <v>44741</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>46286</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58316,7 +58316,7 @@
         <v>46244</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>46286</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45223</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58535,7 +58535,7 @@
         <v>45541</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58608,7 +58608,7 @@
         <v>45435</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58686,7 +58686,7 @@
         <v>44967</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>44734</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58837,7 +58837,7 @@
         <v>46246</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58910,7 +58910,7 @@
         <v>46279</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58988,7 +58988,7 @@
         <v>46246</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59061,7 +59061,7 @@
         <v>46246</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59134,7 +59134,7 @@
         <v>45747</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45533</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59280,7 +59280,7 @@
         <v>46290</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59358,7 +59358,7 @@
         <v>46248</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59431,7 +59431,7 @@
         <v>46290</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59509,7 +59509,7 @@
         <v>46293</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>45635</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59660,7 +59660,7 @@
         <v>46290</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59738,7 +59738,7 @@
         <v>45541</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59811,7 +59811,7 @@
         <v>45201</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59884,7 +59884,7 @@
         <v>45341</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59957,7 +59957,7 @@
         <v>46290</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60035,7 +60035,7 @@
         <v>44950</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60108,7 +60108,7 @@
         <v>45099</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60181,7 +60181,7 @@
         <v>45681</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60254,7 +60254,7 @@
         <v>45715</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60327,7 +60327,7 @@
         <v>46247</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60400,7 +60400,7 @@
         <v>44627</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60473,7 +60473,7 @@
         <v>45056</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>46293</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60619,7 +60619,7 @@
         <v>45355</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60692,7 +60692,7 @@
         <v>44966</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60770,7 +60770,7 @@
         <v>46294</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>46294</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60916,7 +60916,7 @@
         <v>44588</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>44488</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61062,7 +61062,7 @@
         <v>46252</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61135,7 +61135,7 @@
         <v>45197</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61208,7 +61208,7 @@
         <v>46294</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61281,7 +61281,7 @@
         <v>45547</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61359,7 +61359,7 @@
         <v>46295</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45569</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61510,7 +61510,7 @@
         <v>44897</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>45764</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61661,7 +61661,7 @@
         <v>46295</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61734,7 +61734,7 @@
         <v>46244</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61807,7 +61807,7 @@
         <v>45198</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61880,7 +61880,7 @@
         <v>45056</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>45406</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62026,7 +62026,7 @@
         <v>45406</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62099,7 +62099,7 @@
         <v>45440</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62172,7 +62172,7 @@
         <v>45216</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62245,7 +62245,7 @@
         <v>46255</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62318,7 +62318,7 @@
         <v>45667</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62391,7 +62391,7 @@
         <v>46301</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>45519</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62537,7 +62537,7 @@
         <v>45586</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62610,7 +62610,7 @@
         <v>46302</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62683,7 +62683,7 @@
         <v>46302</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62756,7 +62756,7 @@
         <v>45541</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62829,7 +62829,7 @@
         <v>45551</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45350</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62975,7 +62975,7 @@
         <v>45646</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63048,7 +63048,7 @@
         <v>45570</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63121,7 +63121,7 @@
         <v>46282</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63194,7 +63194,7 @@
         <v>45701</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63267,7 +63267,7 @@
         <v>45740</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63340,7 +63340,7 @@
         <v>46262</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63413,7 +63413,7 @@
         <v>46303</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63486,7 +63486,7 @@
         <v>45735</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63559,7 +63559,7 @@
         <v>45734</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63632,7 +63632,7 @@
         <v>46265</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63705,7 +63705,7 @@
         <v>46308</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>46308</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63851,7 +63851,7 @@
         <v>46308</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63924,7 +63924,7 @@
         <v>44992</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63997,7 +63997,7 @@
         <v>45805</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64070,7 +64070,7 @@
         <v>45806</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64143,7 +64143,7 @@
         <v>45597</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64216,7 +64216,7 @@
         <v>46308</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64289,7 +64289,7 @@
         <v>46309</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64362,7 +64362,7 @@
         <v>46268</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64435,7 +64435,7 @@
         <v>45643</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64508,7 +64508,7 @@
         <v>45561</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64581,7 +64581,7 @@
         <v>46248</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64654,7 +64654,7 @@
         <v>45819</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64727,7 +64727,7 @@
         <v>46310</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64800,7 +64800,7 @@
         <v>46310</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64873,7 +64873,7 @@
         <v>46267</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64946,7 +64946,7 @@
         <v>46267</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65019,7 +65019,7 @@
         <v>45826</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65092,7 +65092,7 @@
         <v>45756</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65165,7 +65165,7 @@
         <v>45842</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65238,7 +65238,7 @@
         <v>45797</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65311,7 +65311,7 @@
         <v>45587</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65384,7 +65384,7 @@
         <v>45846</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65462,7 +65462,7 @@
         <v>45846</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65540,7 +65540,7 @@
         <v>45751</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65618,7 +65618,7 @@
         <v>45630</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65696,7 +65696,7 @@
         <v>45701</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65769,7 +65769,7 @@
         <v>45788</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65842,7 +65842,7 @@
         <v>45861</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65915,7 +65915,7 @@
         <v>45788</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65988,7 +65988,7 @@
         <v>45870</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66066,7 +66066,7 @@
         <v>45875</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66144,7 +66144,7 @@
         <v>45734</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66217,7 +66217,7 @@
         <v>45880</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66290,7 +66290,7 @@
         <v>45883</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66363,7 +66363,7 @@
         <v>45883</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66436,7 +66436,7 @@
         <v>45883</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66509,7 +66509,7 @@
         <v>45883</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66582,7 +66582,7 @@
         <v>45313</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66660,7 +66660,7 @@
         <v>44658</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66733,7 +66733,7 @@
         <v>44607</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66806,7 +66806,7 @@
         <v>45131</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66884,7 +66884,7 @@
         <v>44593</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66957,7 +66957,7 @@
         <v>44510</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67030,7 +67030,7 @@
         <v>44956</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67108,7 +67108,7 @@
         <v>45407</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67186,7 +67186,7 @@
         <v>45327</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67259,7 +67259,7 @@
         <v>44711</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>44753</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67405,7 +67405,7 @@
         <v>44998</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67478,7 +67478,7 @@
         <v>45794</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67551,7 +67551,7 @@
         <v>45798</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67624,7 +67624,7 @@
         <v>45712</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67717,7 +67717,7 @@
         <v>45798</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67790,7 +67790,7 @@
         <v>45712</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67863,7 +67863,7 @@
         <v>45817</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67941,7 +67941,7 @@
         <v>45870</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68014,7 +68014,7 @@
         <v>45994</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68087,7 +68087,7 @@
         <v>46047</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68160,7 +68160,7 @@
         <v>46304</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45856</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45936</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46043</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>44607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46225</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>45348</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>46055</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>45609</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>46288</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45698</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>45302</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44607</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45510</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>44970</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45268</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44963</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>46280</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>46198</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>45930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>45788</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44512</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>44992</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45747</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>46176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>46055</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>44602</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45604</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46133</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>44536</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>44530</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44974</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>46107</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>45772</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>45898</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45783</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44607</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>45629</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44747</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>46092</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44943</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>45373</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>46174</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45947</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>45539</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>46196</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>46230</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>45790</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>45679</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>46048</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>46049</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45982</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45603</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>45580</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44991</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>45446</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>45331</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>45358</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>45758</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>45538</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45302</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>43983</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44647</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>45013</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45393</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45790</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44613</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44711</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44579</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45730</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45338</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>45184</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>45720</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>46162</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>44963</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>46162</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>45926</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45558</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45436</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>45617</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45477</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>46203</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>46211</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>46212</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>46013</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>46048</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45740</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>46279</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>45587</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>46055</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>46059</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>46294</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>45842</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>45841</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>46252</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>44840</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>45616</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>46106</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>46302</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>45846</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>44557</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>46286</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>46302</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>46302</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>45201</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>45295</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45343</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44750</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>45205</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45764</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>45751</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44893</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>45177</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45600</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45205</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>45272</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>44540</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>44879</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>44711</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44628</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>44955</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45029</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45712</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>45712</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45846</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44575</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>44662</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44749</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>44792</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44749</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>44881</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44665</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44792</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>44538</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>44852</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44498</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>44881</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>44673</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>44754</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>44855</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44511</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>44840</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>44537</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44575</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44711</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>44659</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44659</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>44578</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>44557</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>44579</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>44616</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>44575</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44575</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44819</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>44819</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>44846</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>44523</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44605</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>44711</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>44841</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>44792</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44830</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>44787</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>44825</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>44614</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>44585</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>44711</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44498</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>44532</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>44593</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>44729</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>44805</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44811</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44622</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45887</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45887</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45887</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45621</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45621</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45008</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>45058</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>45341</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45197</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45697</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45892</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>44662</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45892</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45892</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45895</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45898</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45883</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45883</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45271</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44861</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>44861</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45461</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45902</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>45531</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         <v>45883</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45883</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>45541</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>45406</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45043</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>45905</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>44897</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>46162</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>45908</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>45908</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>45908</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>45908</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>45455</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>44507</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45569</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>44943</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>44943</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45580</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>46162</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>45693</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>46162</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>46162</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>46162</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>46162</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45477</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45547</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45034</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45902</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>44677</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45917</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>46167</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>46167</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>45324</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>45324</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>44658</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>45048</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>46168</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>46168</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>46168</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45925</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>46170</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45092</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>46170</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44628</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45051</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>46170</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>46170</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45934</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44846</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45130</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>46174</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>44804</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45764</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>45471</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>46174</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>44977</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>46174</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44998</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>45929</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>45673</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>45945</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>45321</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>45107</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>45299</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45270</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>45474</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>45152</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>45401</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>45373</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>45946</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26160,7 +26160,7 @@
         <v>44893</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>45946</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>45127</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>45243</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45114</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>44837</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45477</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>44967</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45605</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45152</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45092</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45757</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45615</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>46182</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>44631</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>45240</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45958</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45642</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45958</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45958</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>46184</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45314</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>45012</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45300</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45588</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>44985</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>46189</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>45455</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45455</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45099</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>45363</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45966</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>46188</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>44963</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45966</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>45966</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>45177</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>45965</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>45966</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45966</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>45223</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45181</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45968</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>45356</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>45107</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44588</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45974</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>45974</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>45974</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45974</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>45974</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45974</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>45974</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>45974</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>45201</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>46197</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45545</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45169</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45468</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>46201</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45975</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>46201</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45978</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>46201</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>44904</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>46198</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44904</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>44923</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>45414</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45377</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45351</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>46203</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>45979</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>45359</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45219</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31715,7 +31715,7 @@
         <v>46203</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45477</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45406</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45533</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>46206</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>45988</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>46206</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>45492</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>46206</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>45566</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>46211</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>46211</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>45734</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>45539</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>45615</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>46211</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>46211</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>46211</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>46211</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>46211</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>46211</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>46211</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45758</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>46211</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>46211</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>46212</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45462</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>46212</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>46212</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>44944</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>45995</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>45502</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>45502</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45764</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>45946</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>46219</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45307</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34456,7 +34456,7 @@
         <v>46219</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>45099</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>46000</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45842</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>46220</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45667</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>44853</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>46230</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>46230</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45586</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45519</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>46009</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>46009</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>46009</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>46009</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>46234</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>46010</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>46279</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>46279</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>46008</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>46009</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>46279</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45958</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>46233</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>46013</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>46013</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>46013</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>46013</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>46234</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>46234</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>46013</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>46013</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>46233</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>46234</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37008,7 +37008,7 @@
         <v>46239</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>46279</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>46239</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>46238</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>46026</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>46026</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45646</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>46030</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>46029</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>46031</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>46031</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>45551</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>46286</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>45541</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>46286</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>46035</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38186,7 +38186,7 @@
         <v>46286</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>45350</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>46281</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38405,7 +38405,7 @@
         <v>46035</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>46038</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45145</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>45570</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>46286</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>46041</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>46041</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>46041</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>46244</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>45740</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>46059</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>45735</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>46043</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39359,7 +39359,7 @@
         <v>46043</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39432,7 +39432,7 @@
         <v>45734</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>46048</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>46048</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>46048</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         <v>46048</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44735</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>46279</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>46244</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40026,7 +40026,7 @@
         <v>46048</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         <v>46048</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>46244</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>46049</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>46050</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>44966</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>46049</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>46290</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>46246</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44936</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>46246</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>46246</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>46290</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>44992</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>46290</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>46055</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>46055</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>46055</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>45806</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>45805</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>46247</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>46290</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45597</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>46059</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>46059</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>46059</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>46293</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>46059</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>46059</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>46059</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>46059</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         <v>46062</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>46062</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>46062</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>46059</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>46063</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>46045</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>44853</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>46248</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>46294</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>45643</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>45561</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>46069</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>46069</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>46069</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>46293</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>46070</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>46070</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>46070</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45819</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>46073</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>46294</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>46295</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>46079</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>46294</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>46252</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45826</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>46295</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>46087</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>45169</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>46091</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>44935</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>46244</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>46255</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45842</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>45846</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>45846</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45756</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45797</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45587</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>46101</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45012</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>46302</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>45557</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>45635</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>46301</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>45751</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45295</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45630</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>45701</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45788</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>46302</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>45861</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>46303</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>46119</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>46119</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>46119</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>46120</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45870</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>46120</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>46120</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45788</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45618</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45414</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45734</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45875</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>44589</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45880</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>46308</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>46265</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>44893</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45545</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>45538</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>46282</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47698,7 +47698,7 @@
         <v>45646</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>44648</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>45947</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47917,7 +47917,7 @@
         <v>46308</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>46308</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>44550</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>46262</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>45758</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45701</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>44589</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>46308</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48506,7 +48506,7 @@
         <v>44904</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>46310</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>45558</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48730,7 +48730,7 @@
         <v>44943</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>46309</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>45216</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48949,7 +48949,7 @@
         <v>46267</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>46267</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>46268</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45846</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>45730</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>45009</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>46270</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>45810</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>45401</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45841</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49684,7 +49684,7 @@
         <v>45764</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>46286</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49835,7 +49835,7 @@
         <v>45834</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49908,7 +49908,7 @@
         <v>45566</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49981,7 +49981,7 @@
         <v>45105</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>46286</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>46316</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>46272</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>46272</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50351,7 +50351,7 @@
         <v>46272</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50424,7 +50424,7 @@
         <v>46272</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50497,7 +50497,7 @@
         <v>45194</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45197</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50643,7 +50643,7 @@
         <v>45021</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45875</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50789,7 +50789,7 @@
         <v>46272</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50862,7 +50862,7 @@
         <v>44950</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50935,7 +50935,7 @@
         <v>46273</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51008,7 +51008,7 @@
         <v>45043</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51081,7 +51081,7 @@
         <v>46315</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>44938</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51232,7 +51232,7 @@
         <v>44977</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51305,7 +51305,7 @@
         <v>46274</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>46002</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51451,7 +51451,7 @@
         <v>46317</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>46248</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51602,7 +51602,7 @@
         <v>46276</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>46318</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>44943</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>44943</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>46317</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>46317</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         <v>45734</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>46310</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>46317</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52274,7 +52274,7 @@
         <v>45112</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45112</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>44930</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>46317</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52571,7 +52571,7 @@
         <v>45775</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>44575</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52717,7 +52717,7 @@
         <v>44950</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52790,7 +52790,7 @@
         <v>46276</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>46317</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52941,7 +52941,7 @@
         <v>46318</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>45363</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         <v>45364</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53160,7 +53160,7 @@
         <v>44966</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45182</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>44988</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53384,7 +53384,7 @@
         <v>45600</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53457,7 +53457,7 @@
         <v>45600</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         <v>44711</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>44998</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53676,7 +53676,7 @@
         <v>45547</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>44894</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45470</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45763</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>45295</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45671</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45617</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54197,7 +54197,7 @@
         <v>45113</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54270,7 +54270,7 @@
         <v>45435</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54343,7 +54343,7 @@
         <v>45316</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54416,7 +54416,7 @@
         <v>44965</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54489,7 +54489,7 @@
         <v>45706</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>44734</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45671</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
         <v>45015</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>45644</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54864,7 +54864,7 @@
         <v>45210</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>45617</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55010,7 +55010,7 @@
         <v>44614</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55083,7 +55083,7 @@
         <v>45693</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55156,7 +55156,7 @@
         <v>44729</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>45469</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45149</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55375,7 +55375,7 @@
         <v>45201</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55448,7 +55448,7 @@
         <v>45726</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55526,7 +55526,7 @@
         <v>44719</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55599,7 +55599,7 @@
         <v>45035</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55672,7 +55672,7 @@
         <v>45188</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55745,7 +55745,7 @@
         <v>44803</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>44882</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>45621</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55964,7 +55964,7 @@
         <v>45182</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56037,7 +56037,7 @@
         <v>45708</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56110,7 +56110,7 @@
         <v>45715</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>44627</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56256,7 +56256,7 @@
         <v>44985</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56329,7 +56329,7 @@
         <v>45682</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>45747</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56475,7 +56475,7 @@
         <v>45272</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56548,7 +56548,7 @@
         <v>45260</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56621,7 +56621,7 @@
         <v>44886</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56694,7 +56694,7 @@
         <v>45043</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56767,7 +56767,7 @@
         <v>44741</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56840,7 +56840,7 @@
         <v>45112</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56913,7 +56913,7 @@
         <v>45749</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56986,7 +56986,7 @@
         <v>45587</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>44904</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45037</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         <v>45079</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>44882</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>45764</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>45355</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57502,7 +57502,7 @@
         <v>45324</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57580,7 +57580,7 @@
         <v>45740</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57653,7 +57653,7 @@
         <v>45183</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57726,7 +57726,7 @@
         <v>45056</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57799,7 +57799,7 @@
         <v>45757</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57872,7 +57872,7 @@
         <v>45201</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57945,7 +57945,7 @@
         <v>45092</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45049</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>45051</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58164,7 +58164,7 @@
         <v>45111</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58237,7 +58237,7 @@
         <v>45112</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>44950</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58383,7 +58383,7 @@
         <v>44950</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>45349</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45119</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58602,7 +58602,7 @@
         <v>45116</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58675,7 +58675,7 @@
         <v>45587</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58748,7 +58748,7 @@
         <v>44957</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58821,7 +58821,7 @@
         <v>45118</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58894,7 +58894,7 @@
         <v>45338</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58972,7 +58972,7 @@
         <v>45562</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59045,7 +59045,7 @@
         <v>45358</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59118,7 +59118,7 @@
         <v>45281</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59196,7 +59196,7 @@
         <v>45275</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59269,7 +59269,7 @@
         <v>44628</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59342,7 +59342,7 @@
         <v>45335</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59420,7 +59420,7 @@
         <v>45541</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59493,7 +59493,7 @@
         <v>44507</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59566,7 +59566,7 @@
         <v>45124</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>45267</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59712,7 +59712,7 @@
         <v>45747</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59785,7 +59785,7 @@
         <v>45460</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59858,7 +59858,7 @@
         <v>44605</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59931,7 +59931,7 @@
         <v>45175</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60004,7 +60004,7 @@
         <v>45405</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>45405</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60150,7 +60150,7 @@
         <v>45184</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60223,7 +60223,7 @@
         <v>45547</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60301,7 +60301,7 @@
         <v>44578</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60374,7 +60374,7 @@
         <v>44592</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60447,7 +60447,7 @@
         <v>45541</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60520,7 +60520,7 @@
         <v>45412</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60598,7 +60598,7 @@
         <v>45552</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60671,7 +60671,7 @@
         <v>45462</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60744,7 +60744,7 @@
         <v>44585</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60817,7 +60817,7 @@
         <v>45763</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60890,7 +60890,7 @@
         <v>45645</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>45184</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61036,7 +61036,7 @@
         <v>45681</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61109,7 +61109,7 @@
         <v>44591</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61182,7 +61182,7 @@
         <v>44608</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61255,7 +61255,7 @@
         <v>45169</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61328,7 +61328,7 @@
         <v>44626</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
         <v>45435</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61479,7 +61479,7 @@
         <v>45030</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61552,7 +61552,7 @@
         <v>45371</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61625,7 +61625,7 @@
         <v>45617</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61698,7 +61698,7 @@
         <v>45056</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61771,7 +61771,7 @@
         <v>44564</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61844,7 +61844,7 @@
         <v>45174</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61917,7 +61917,7 @@
         <v>45726</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61990,7 +61990,7 @@
         <v>44571</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62063,7 +62063,7 @@
         <v>45179</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62136,7 +62136,7 @@
         <v>45182</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62209,7 +62209,7 @@
         <v>45440</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62282,7 +62282,7 @@
         <v>44614</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62355,7 +62355,7 @@
         <v>44839</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62433,7 +62433,7 @@
         <v>44659</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62511,7 +62511,7 @@
         <v>45705</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62584,7 +62584,7 @@
         <v>45456</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45215</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62730,7 +62730,7 @@
         <v>45404</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62803,7 +62803,7 @@
         <v>45523</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62881,7 +62881,7 @@
         <v>45392</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62954,7 +62954,7 @@
         <v>44704</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63027,7 +63027,7 @@
         <v>45198</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63100,7 +63100,7 @@
         <v>45198</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63173,7 +63173,7 @@
         <v>44655</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63246,7 +63246,7 @@
         <v>45211</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63319,7 +63319,7 @@
         <v>44734</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63397,7 +63397,7 @@
         <v>44734</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63475,7 +63475,7 @@
         <v>45194</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63548,7 +63548,7 @@
         <v>45681</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63621,7 +63621,7 @@
         <v>45756</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63694,7 +63694,7 @@
         <v>45169</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63767,7 +63767,7 @@
         <v>45197</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63840,7 +63840,7 @@
         <v>45759</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63913,7 +63913,7 @@
         <v>45314</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63986,7 +63986,7 @@
         <v>45303</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64064,7 +64064,7 @@
         <v>45245</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64137,7 +64137,7 @@
         <v>45189</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64210,7 +64210,7 @@
         <v>45294</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64288,7 +64288,7 @@
         <v>44904</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64366,7 +64366,7 @@
         <v>44897</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64439,7 +64439,7 @@
         <v>44904</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64517,7 +64517,7 @@
         <v>45246</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64595,7 +64595,7 @@
         <v>45761</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64668,7 +64668,7 @@
         <v>45679</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64741,7 +64741,7 @@
         <v>45226</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64814,7 +64814,7 @@
         <v>45240</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64887,7 +64887,7 @@
         <v>44889</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64960,7 +64960,7 @@
         <v>45198</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65033,7 +65033,7 @@
         <v>45198</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65106,7 +65106,7 @@
         <v>45201</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65179,7 +65179,7 @@
         <v>45534</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65252,7 +65252,7 @@
         <v>45253</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65325,7 +65325,7 @@
         <v>45300</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65398,7 +65398,7 @@
         <v>45215</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65471,7 +65471,7 @@
         <v>45392</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65544,7 +65544,7 @@
         <v>44867</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65617,7 +65617,7 @@
         <v>45477</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65690,7 +65690,7 @@
         <v>45477</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65763,7 +65763,7 @@
         <v>44904</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65836,7 +65836,7 @@
         <v>45302</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65909,7 +65909,7 @@
         <v>44893</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65982,7 +65982,7 @@
         <v>45406</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66055,7 +66055,7 @@
         <v>45406</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66128,7 +66128,7 @@
         <v>44853</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66201,7 +66201,7 @@
         <v>44949</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66274,7 +66274,7 @@
         <v>44648</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66347,7 +66347,7 @@
         <v>44861</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66420,7 +66420,7 @@
         <v>44938</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66498,7 +66498,7 @@
         <v>45375</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66571,7 +66571,7 @@
         <v>45180</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66644,7 +66644,7 @@
         <v>44943</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66717,7 +66717,7 @@
         <v>44614</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66790,7 +66790,7 @@
         <v>44711</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66863,7 +66863,7 @@
         <v>44658</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66936,7 +66936,7 @@
         <v>44607</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67009,7 +67009,7 @@
         <v>44593</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67082,7 +67082,7 @@
         <v>44711</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67155,7 +67155,7 @@
         <v>45313</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67233,7 +67233,7 @@
         <v>45131</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67311,7 +67311,7 @@
         <v>44510</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67384,7 +67384,7 @@
         <v>44956</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67462,7 +67462,7 @@
         <v>45407</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67540,7 +67540,7 @@
         <v>45327</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67613,7 +67613,7 @@
         <v>44753</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67686,7 +67686,7 @@
         <v>44998</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67759,7 +67759,7 @@
         <v>45794</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67832,7 +67832,7 @@
         <v>45798</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67905,7 +67905,7 @@
         <v>45712</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67998,7 +67998,7 @@
         <v>45798</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68071,7 +68071,7 @@
         <v>45712</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68144,7 +68144,7 @@
         <v>45817</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68222,7 +68222,7 @@
         <v>45870</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>45994</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68368,7 +68368,7 @@
         <v>46047</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68441,7 +68441,7 @@
         <v>46304</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45856</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45936</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>46043</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>44607</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45111</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>46225</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>45348</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>46055</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>45609</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45412</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>46288</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45698</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>45302</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44607</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45510</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>44970</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45268</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44963</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>46280</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>46198</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>45930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>45788</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44512</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>44992</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45747</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>46176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>46055</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>44602</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45604</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45792</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>46133</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>44536</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>44530</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44974</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>46107</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>45772</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>45898</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45783</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>44607</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>45629</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>44747</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>46092</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44943</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>45373</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>46174</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45947</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>45539</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>46196</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>46230</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>46286</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>45790</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>45679</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>46048</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>46049</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45982</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45603</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>45580</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44991</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>45446</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>45331</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>45358</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>45758</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>45538</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45302</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>43983</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44647</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>45013</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45393</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45790</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44613</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44711</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44579</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45730</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45338</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>45184</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>45720</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>46162</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>44963</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>46162</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>45926</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45558</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45436</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>45617</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45477</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>46203</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>46211</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>46212</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>46013</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>46048</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45740</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>46279</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>45587</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>46055</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>46059</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>46294</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>45842</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>45841</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>46252</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>44840</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>45616</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>46106</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>46302</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>45846</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>44557</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>46286</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>46302</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>46302</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>45201</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>45295</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45343</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44750</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>45205</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45764</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>45751</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44893</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>45177</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45600</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45205</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>45272</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>44540</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>44879</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>44711</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44628</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>44955</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45029</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45712</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>45712</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45846</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44575</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>44662</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44749</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>44792</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44749</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>44881</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44665</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44792</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>44538</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>44852</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>44498</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>44881</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>44673</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>44754</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>44855</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44511</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>44840</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>44537</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44575</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44711</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>44659</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44659</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>44578</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>44557</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>44579</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>44616</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>44575</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>44575</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>44819</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>44819</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>44846</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>44523</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44605</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>44711</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>44841</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>44792</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44830</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>44787</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>44825</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>44614</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>44585</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>44711</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44498</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>44532</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>44593</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>44729</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>44805</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44811</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>44622</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45887</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45887</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45887</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45621</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45621</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45008</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>45058</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>45341</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45197</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45697</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45892</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>44662</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45892</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45892</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45895</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45898</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45883</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45883</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45271</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44861</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>44861</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45461</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45902</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>45531</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         <v>45883</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45883</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>45541</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>45406</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45043</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>45905</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>44897</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>46162</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>45908</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>45908</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>45908</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>45908</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>45455</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>44507</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45569</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>44943</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>44943</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45580</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>46162</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>45693</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>46162</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>46162</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>46162</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>46162</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45477</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45547</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45034</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45902</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>44677</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45917</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>46167</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>46167</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>45324</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>45324</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>44658</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>45048</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>46168</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>46168</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>46168</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45925</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>46170</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>45092</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>46170</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44628</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45051</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>46170</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>46170</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45934</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44846</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45130</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>46174</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>44804</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45764</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>45471</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>46174</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>44977</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>46174</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44998</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>45929</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>45673</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>45945</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>45321</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>45107</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>45299</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45270</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>45474</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>45152</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>45401</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>45373</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>45946</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26160,7 +26160,7 @@
         <v>44893</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>45946</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>45127</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>45243</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45114</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>44837</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45477</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>44967</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>45605</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45152</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45092</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45757</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45615</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>46182</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>44631</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>45240</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45958</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45642</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45958</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45958</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>46184</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45314</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>45012</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45300</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45588</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>44985</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>46189</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>45455</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>45455</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45099</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>45363</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45966</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>46188</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>44963</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45966</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>45966</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>45177</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>45965</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>45966</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45966</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>45223</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45181</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45968</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>45356</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>45107</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44588</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45974</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>45974</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>45974</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45974</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>45974</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45974</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>45974</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>45974</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>45201</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>46197</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45545</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45169</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45468</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>46201</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45975</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>46201</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45978</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>46201</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>44904</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>46198</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44904</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>44923</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>45414</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45377</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45351</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>46203</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>45979</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>45359</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45219</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31715,7 +31715,7 @@
         <v>46203</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45477</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45406</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45533</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>46206</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>45988</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>46206</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>45492</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>46206</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>45566</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>46211</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>46211</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>45734</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>45539</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>45615</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>46211</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>46211</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>46211</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>46211</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>46211</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>46211</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>46211</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45758</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>46211</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>46211</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>46212</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45462</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>46212</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>46212</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>44944</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>45995</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>45502</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>45502</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45764</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>45946</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>46219</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45307</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34456,7 +34456,7 @@
         <v>46219</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>45099</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>46000</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45842</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>46220</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45667</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>44853</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>46230</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>46230</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>45586</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45519</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>46009</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>46009</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>46009</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>46009</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>46234</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>46010</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>46279</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>46279</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>46008</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>46009</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>46279</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45958</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>46233</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>46013</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>46013</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>46013</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>46013</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>46234</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>46234</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>46013</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>46013</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>46233</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>46234</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37008,7 +37008,7 @@
         <v>46239</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>46279</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>46239</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>46238</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>46026</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>46026</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45646</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>46030</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>46029</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>46031</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>46031</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>45551</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>46286</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>45541</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>46286</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>46035</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38186,7 +38186,7 @@
         <v>46286</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>45350</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>46281</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38405,7 +38405,7 @@
         <v>46035</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>46038</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45145</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>45570</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>46286</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>46041</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>46041</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>46041</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>46244</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>45740</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>46059</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>45735</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>46043</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39359,7 +39359,7 @@
         <v>46043</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39432,7 +39432,7 @@
         <v>45734</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>46048</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>46048</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>46048</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         <v>46048</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44735</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>46279</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>46244</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40026,7 +40026,7 @@
         <v>46048</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         <v>46048</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>46244</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>46049</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>46050</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>44966</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>46049</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>46290</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>46246</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44936</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>46246</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>46246</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>46290</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>44992</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>46290</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>46055</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>46055</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>46055</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>45806</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>45805</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>46247</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>46290</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45597</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>46059</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>46059</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>46059</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>46293</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>46059</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>46059</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>46059</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>46059</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         <v>46062</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>46062</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>46062</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>46059</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>46063</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>46045</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>44853</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>46248</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>46294</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>45643</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>45561</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>46069</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>46069</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>46069</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>46293</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>46070</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>46070</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>46070</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45819</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>46073</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>46294</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>46295</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>46079</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>46294</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>46252</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45826</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>46295</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>46087</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>45169</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>46091</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>44935</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>46244</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>46255</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45842</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>45846</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>45846</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45756</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45797</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45587</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>46101</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45012</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>46302</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>45557</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>45635</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>46301</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>45751</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45295</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45630</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>45701</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45788</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>46302</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>45861</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>46303</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>46119</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>46119</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>46119</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>46120</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45870</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>46120</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>46120</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45788</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45618</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45414</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45734</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45875</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>44589</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45880</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>46308</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>46265</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>44893</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45545</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>45538</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>46282</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47698,7 +47698,7 @@
         <v>45646</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>44648</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>45947</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47917,7 +47917,7 @@
         <v>46308</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>46308</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>44550</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>46262</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>45758</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45701</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>44589</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>46308</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48506,7 +48506,7 @@
         <v>44904</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>46310</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>45558</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48730,7 +48730,7 @@
         <v>44943</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>46309</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>45216</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48949,7 +48949,7 @@
         <v>46267</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>46267</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>46268</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45846</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>45730</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>45009</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>46270</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>45810</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>45401</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45841</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49684,7 +49684,7 @@
         <v>45764</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>46286</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49835,7 +49835,7 @@
         <v>45834</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49908,7 +49908,7 @@
         <v>45566</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49981,7 +49981,7 @@
         <v>45105</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>46286</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>46316</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>46272</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>46272</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50351,7 +50351,7 @@
         <v>46272</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -50424,7 +50424,7 @@
         <v>46272</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50497,7 +50497,7 @@
         <v>45194</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45197</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50643,7 +50643,7 @@
         <v>45021</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45875</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50789,7 +50789,7 @@
         <v>46272</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50862,7 +50862,7 @@
         <v>44950</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50935,7 +50935,7 @@
         <v>46273</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51008,7 +51008,7 @@
         <v>45043</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51081,7 +51081,7 @@
         <v>46315</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>44938</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51232,7 +51232,7 @@
         <v>44977</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51305,7 +51305,7 @@
         <v>46274</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>46002</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51451,7 +51451,7 @@
         <v>46317</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>46248</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51602,7 +51602,7 @@
         <v>46276</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>46318</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>44943</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>44943</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>46317</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>46317</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         <v>45734</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>46310</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>46317</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52274,7 +52274,7 @@
         <v>45112</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45112</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>44930</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>46317</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52571,7 +52571,7 @@
         <v>45775</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>44575</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52717,7 +52717,7 @@
         <v>44950</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52790,7 +52790,7 @@
         <v>46276</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>46317</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52941,7 +52941,7 @@
         <v>46318</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>45363</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         <v>45364</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53160,7 +53160,7 @@
         <v>44966</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45182</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>44988</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53384,7 +53384,7 @@
         <v>45600</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53457,7 +53457,7 @@
         <v>45600</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         <v>44711</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>44998</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53676,7 +53676,7 @@
         <v>45547</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>44894</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45470</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45763</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>45295</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45671</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45617</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54197,7 +54197,7 @@
         <v>45113</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54270,7 +54270,7 @@
         <v>45435</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54343,7 +54343,7 @@
         <v>45316</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54416,7 +54416,7 @@
         <v>44965</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54489,7 +54489,7 @@
         <v>45706</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>44734</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45671</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
         <v>45015</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>45644</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54864,7 +54864,7 @@
         <v>45210</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>45617</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55010,7 +55010,7 @@
         <v>44614</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55083,7 +55083,7 @@
         <v>45693</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55156,7 +55156,7 @@
         <v>44729</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>45469</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45149</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55375,7 +55375,7 @@
         <v>45201</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55448,7 +55448,7 @@
         <v>45726</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55526,7 +55526,7 @@
         <v>44719</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55599,7 +55599,7 @@
         <v>45035</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55672,7 +55672,7 @@
         <v>45188</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55745,7 +55745,7 @@
         <v>44803</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>44882</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>45621</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55964,7 +55964,7 @@
         <v>45182</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56037,7 +56037,7 @@
         <v>45708</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56110,7 +56110,7 @@
         <v>45715</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>44627</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -56256,7 +56256,7 @@
         <v>44985</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56329,7 +56329,7 @@
         <v>45682</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>45747</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56475,7 +56475,7 @@
         <v>45272</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56548,7 +56548,7 @@
         <v>45260</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56621,7 +56621,7 @@
         <v>44886</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56694,7 +56694,7 @@
         <v>45043</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56767,7 +56767,7 @@
         <v>44741</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56840,7 +56840,7 @@
         <v>45112</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56913,7 +56913,7 @@
         <v>45749</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56986,7 +56986,7 @@
         <v>45587</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>44904</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45037</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         <v>45079</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>44882</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>45764</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>45355</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57502,7 +57502,7 @@
         <v>45324</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57580,7 +57580,7 @@
         <v>45740</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57653,7 +57653,7 @@
         <v>45183</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57726,7 +57726,7 @@
         <v>45056</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57799,7 +57799,7 @@
         <v>45757</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57872,7 +57872,7 @@
         <v>45201</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57945,7 +57945,7 @@
         <v>45092</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45049</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>45051</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58164,7 +58164,7 @@
         <v>45111</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58237,7 +58237,7 @@
         <v>45112</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>44950</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58383,7 +58383,7 @@
         <v>44950</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>45349</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45119</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58602,7 +58602,7 @@
         <v>45116</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58675,7 +58675,7 @@
         <v>45587</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58748,7 +58748,7 @@
         <v>44957</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58821,7 +58821,7 @@
         <v>45118</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58894,7 +58894,7 @@
         <v>45338</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58972,7 +58972,7 @@
         <v>45562</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59045,7 +59045,7 @@
         <v>45358</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59118,7 +59118,7 @@
         <v>45281</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -59196,7 +59196,7 @@
         <v>45275</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59269,7 +59269,7 @@
         <v>44628</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59342,7 +59342,7 @@
         <v>45335</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59420,7 +59420,7 @@
         <v>45541</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59493,7 +59493,7 @@
         <v>44507</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59566,7 +59566,7 @@
         <v>45124</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>45267</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59712,7 +59712,7 @@
         <v>45747</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59785,7 +59785,7 @@
         <v>45460</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59858,7 +59858,7 @@
         <v>44605</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59931,7 +59931,7 @@
         <v>45175</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60004,7 +60004,7 @@
         <v>45405</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>45405</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -60150,7 +60150,7 @@
         <v>45184</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60223,7 +60223,7 @@
         <v>45547</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60301,7 +60301,7 @@
         <v>44578</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60374,7 +60374,7 @@
         <v>44592</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60447,7 +60447,7 @@
         <v>45541</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60520,7 +60520,7 @@
         <v>45412</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60598,7 +60598,7 @@
         <v>45552</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60671,7 +60671,7 @@
         <v>45462</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60744,7 +60744,7 @@
         <v>44585</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60817,7 +60817,7 @@
         <v>45763</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60890,7 +60890,7 @@
         <v>45645</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>45184</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61036,7 +61036,7 @@
         <v>45681</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -61109,7 +61109,7 @@
         <v>44591</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61182,7 +61182,7 @@
         <v>44608</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61255,7 +61255,7 @@
         <v>45169</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61328,7 +61328,7 @@
         <v>44626</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
         <v>45435</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61479,7 +61479,7 @@
         <v>45030</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61552,7 +61552,7 @@
         <v>45371</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61625,7 +61625,7 @@
         <v>45617</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61698,7 +61698,7 @@
         <v>45056</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61771,7 +61771,7 @@
         <v>44564</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61844,7 +61844,7 @@
         <v>45174</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61917,7 +61917,7 @@
         <v>45726</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61990,7 +61990,7 @@
         <v>44571</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62063,7 +62063,7 @@
         <v>45179</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -62136,7 +62136,7 @@
         <v>45182</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62209,7 +62209,7 @@
         <v>45440</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62282,7 +62282,7 @@
         <v>44614</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62355,7 +62355,7 @@
         <v>44839</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62433,7 +62433,7 @@
         <v>44659</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62511,7 +62511,7 @@
         <v>45705</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62584,7 +62584,7 @@
         <v>45456</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45215</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62730,7 +62730,7 @@
         <v>45404</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62803,7 +62803,7 @@
         <v>45523</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62881,7 +62881,7 @@
         <v>45392</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62954,7 +62954,7 @@
         <v>44704</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63027,7 +63027,7 @@
         <v>45198</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -63100,7 +63100,7 @@
         <v>45198</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63173,7 +63173,7 @@
         <v>44655</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63246,7 +63246,7 @@
         <v>45211</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63319,7 +63319,7 @@
         <v>44734</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63397,7 +63397,7 @@
         <v>44734</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63475,7 +63475,7 @@
         <v>45194</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63548,7 +63548,7 @@
         <v>45681</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63621,7 +63621,7 @@
         <v>45756</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63694,7 +63694,7 @@
         <v>45169</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63767,7 +63767,7 @@
         <v>45197</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63840,7 +63840,7 @@
         <v>45759</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63913,7 +63913,7 @@
         <v>45314</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63986,7 +63986,7 @@
         <v>45303</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -64064,7 +64064,7 @@
         <v>45245</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64137,7 +64137,7 @@
         <v>45189</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64210,7 +64210,7 @@
         <v>45294</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64288,7 +64288,7 @@
         <v>44904</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64366,7 +64366,7 @@
         <v>44897</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64439,7 +64439,7 @@
         <v>44904</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64517,7 +64517,7 @@
         <v>45246</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64595,7 +64595,7 @@
         <v>45761</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64668,7 +64668,7 @@
         <v>45679</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64741,7 +64741,7 @@
         <v>45226</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64814,7 +64814,7 @@
         <v>45240</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64887,7 +64887,7 @@
         <v>44889</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64960,7 +64960,7 @@
         <v>45198</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -65033,7 +65033,7 @@
         <v>45198</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -65106,7 +65106,7 @@
         <v>45201</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65179,7 +65179,7 @@
         <v>45534</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65252,7 +65252,7 @@
         <v>45253</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65325,7 +65325,7 @@
         <v>45300</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65398,7 +65398,7 @@
         <v>45215</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65471,7 +65471,7 @@
         <v>45392</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65544,7 +65544,7 @@
         <v>44867</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65617,7 +65617,7 @@
         <v>45477</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65690,7 +65690,7 @@
         <v>45477</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65763,7 +65763,7 @@
         <v>44904</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65836,7 +65836,7 @@
         <v>45302</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65909,7 +65909,7 @@
         <v>44893</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65982,7 +65982,7 @@
         <v>45406</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -66055,7 +66055,7 @@
         <v>45406</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66128,7 +66128,7 @@
         <v>44853</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66201,7 +66201,7 @@
         <v>44949</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66274,7 +66274,7 @@
         <v>44648</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66347,7 +66347,7 @@
         <v>44861</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66420,7 +66420,7 @@
         <v>44938</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66498,7 +66498,7 @@
         <v>45375</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66571,7 +66571,7 @@
         <v>45180</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66644,7 +66644,7 @@
         <v>44943</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66717,7 +66717,7 @@
         <v>44614</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66790,7 +66790,7 @@
         <v>44711</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66863,7 +66863,7 @@
         <v>44658</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66936,7 +66936,7 @@
         <v>44607</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -67009,7 +67009,7 @@
         <v>44593</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67082,7 +67082,7 @@
         <v>44711</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67155,7 +67155,7 @@
         <v>45313</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67233,7 +67233,7 @@
         <v>45131</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67311,7 +67311,7 @@
         <v>44510</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67384,7 +67384,7 @@
         <v>44956</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67462,7 +67462,7 @@
         <v>45407</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67540,7 +67540,7 @@
         <v>45327</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67613,7 +67613,7 @@
         <v>44753</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67686,7 +67686,7 @@
         <v>44998</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67759,7 +67759,7 @@
         <v>45794</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67832,7 +67832,7 @@
         <v>45798</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -67905,7 +67905,7 @@
         <v>45712</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -67998,7 +67998,7 @@
         <v>45798</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -68071,7 +68071,7 @@
         <v>45712</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -68144,7 +68144,7 @@
         <v>45817</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -68222,7 +68222,7 @@
         <v>45870</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -68295,7 +68295,7 @@
         <v>45994</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -68368,7 +68368,7 @@
         <v>46047</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -68441,7 +68441,7 @@
         <v>46304</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
